--- a/excel_ai/CPAT-AI_BugsAndIssues_latest.xlsx
+++ b/excel_ai/CPAT-AI_BugsAndIssues_latest.xlsx
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>Taxes jump in the first projected year when pass-through is between 0 and 1 (none for Egypt: 0 or 1). prototype: Fixed in v4.10 (user rule: bugs are never replicated): the floating part is (1 - pass-through) x (last tax + fall in supply cost), applied once (txf; PriceProjection_Method.md A10); no effect for Egypt (pass-through 0 or 1).</t>
+          <t>Taxes jump in the first projected year when pass-through is between 0 and 1 (none for Egypt: 0 or 1). prototype: Fixed in v4.10 (user rule: bugs are never replicated): the floating part is (1 - pass-through) x (last tax + fall in supply cost), applied once (txf; Methods, chapter Prices A10); no effect for Egypt (pass-through 0 or 1).</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>Non-energy methane is flat and a methane fee on agriculture and waste has no effect. prototype: Fixed in v2.8: the sources grow with income and population and the fee abates them along their curves (GHG_Method.md).</t>
+          <t>Non-energy methane is flat and a methane fee on agriculture and waste has no effect. prototype: Fixed in v2.8: the sources grow with income and population and the fee abates them along their curves (Methods, chapter Emissions).</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline -33.9%, diesel -37.9%, road electricity -52.4%, passenger EV sales share -2.6 points. prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline -33.9%, diesel -37.9%, road electricity -52.4%, passenger EV sales share -2.6 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline +0.0%, diesel +0.0%, road electricity -0.6%, passenger EV sales share -0.1 points. prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline +0.0%, diesel +0.0%, road electricity -0.6%, passenger EV sales share -0.1 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I30" s="9" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline +0.0%, diesel -0.3%, road electricity -16.8%, passenger EV sales share +0.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline +0.0%, diesel -0.3%, road electricity -16.8%, passenger EV sales share +0.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline -0.0%, diesel +0.0%, road electricity -0.3%, passenger EV sales share +0.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline -0.0%, diesel +0.0%, road electricity -0.3%, passenger EV sales share +0.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline -0.0%, diesel -0.2%, road electricity +4.0%, passenger EV sales share +0.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline -0.0%, diesel -0.2%, road electricity +4.0%, passenger EV sales share +0.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline +0.0%, diesel +0.2%, road electricity -1.0%, passenger EV sales share -0.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline +0.0%, diesel +0.2%, road electricity -1.0%, passenger EV sales share -0.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline -0.0%, diesel +0.1%, road electricity +0.2%, passenger EV sales share +0.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline -0.0%, diesel +0.1%, road electricity +0.2%, passenger EV sales share +0.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline -0.1%, diesel -0.0%, road electricity +1.2%, passenger EV sales share +0.5 points. prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline -0.1%, diesel -0.0%, road electricity +1.2%, passenger EV sales share +0.5 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline +5.1%, diesel +3.1%, road electricity -50.7%, passenger EV sales share -10.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline +5.1%, diesel +3.1%, road electricity -50.7%, passenger EV sales share -10.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I42" s="9" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Transport_vs_Legacy.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I43" s="9" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="J135" s="9" t="inlineStr">
         <is>
-          <t>PowerPrices_Method.md 3.9</t>
+          <t>Methods, chapter Power 3.9</t>
         </is>
       </c>
       <c r="K135" s="9" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="J137" s="9" t="inlineStr">
         <is>
-          <t>PowerPrices_Method.md; LegacyDiff</t>
+          <t>Methods, chapter Power; LegacyDiff</t>
         </is>
       </c>
       <c r="K137" s="9" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="J138" s="9" t="inlineStr">
         <is>
-          <t>GDP_Method.md; LegacyDiff 55</t>
+          <t>Methods, chapter Macro and results; LegacyDiff 55</t>
         </is>
       </c>
       <c r="K138" s="9" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="J141" s="9" t="inlineStr">
         <is>
-          <t>PowerPrices_Method.md; LegacyDiff 77</t>
+          <t>Methods, chapter Power; LegacyDiff 77</t>
         </is>
       </c>
       <c r="K141" s="9" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="J142" s="9" t="inlineStr">
         <is>
-          <t>GHG_Method.md; LegacyDiff</t>
+          <t>Methods, chapter Emissions; LegacyDiff</t>
         </is>
       </c>
       <c r="K142" s="9" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="J143" s="9" t="inlineStr">
         <is>
-          <t>PriceProjection_Method.md; LegacyDiff</t>
+          <t>Methods, chapter Prices; LegacyDiff</t>
         </is>
       </c>
       <c r="K143" s="9" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="J144" s="9" t="inlineStr">
         <is>
-          <t>GHG_Method.md</t>
+          <t>Methods, chapter Emissions</t>
         </is>
       </c>
       <c r="K144" s="9" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="J145" s="9" t="inlineStr">
         <is>
-          <t>Plans.md (section Plan_AirPollution)</t>
+          <t>excel_ai/plans/Air_pollution.md</t>
         </is>
       </c>
       <c r="K145" s="9" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="J146" s="9" t="inlineStr">
         <is>
-          <t>Plans.md (section Plan_TransportExternalities)</t>
+          <t>excel_ai/plans/Transport_cobenefits.md</t>
         </is>
       </c>
       <c r="K146" s="9" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="J148" s="9" t="inlineStr">
         <is>
-          <t>legacy_comparison_v6_4.md; PriceProjection_Method.md A7</t>
+          <t>legacy_comparison_v6_4.md; Methods, chapter Prices A7</t>
         </is>
       </c>
       <c r="K148" s="9" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="J149" s="9" t="inlineStr">
         <is>
-          <t>GHG_Method.md (Data); CAVEATS v2.8</t>
+          <t>Methods, chapter Emissions (Data); CAVEATS v2.8</t>
         </is>
       </c>
       <c r="K149" s="9" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="J150" s="9" t="inlineStr">
         <is>
-          <t>CO2Calibration_Method.md; CAVEATS v3.2</t>
+          <t>Methods, chapter Emissions; CAVEATS v3.2</t>
         </is>
       </c>
       <c r="K150" s="9" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="J152" s="9" t="inlineStr">
         <is>
-          <t>ETS_Method.md; ETS_Legacy_Algorithm.md; LegacyDiff</t>
+          <t>Methods, chapter ETS; Methods, chapter ETS; LegacyDiff</t>
         </is>
       </c>
       <c r="K152" s="9" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="J155" s="9" t="inlineStr">
         <is>
-          <t>GHG_Method.md; CAVEATS v2.8</t>
+          <t>Methods, chapter Emissions; CAVEATS v2.8</t>
         </is>
       </c>
       <c r="K155" s="9" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="J156" s="9" t="inlineStr">
         <is>
-          <t>Transport_vs_Legacy.md</t>
+          <t>Methods, chapter Transport</t>
         </is>
       </c>
       <c r="K156" s="9" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="J158" s="9" t="inlineStr">
         <is>
-          <t>ResultsSections_Method.md; CO2Calibration_Method.md; CAVEATS v4.11</t>
+          <t>Methods, chapter Macro and results; Methods, chapter Emissions; CAVEATS v4.11</t>
         </is>
       </c>
       <c r="K158" s="9" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="J159" s="9" t="inlineStr">
         <is>
-          <t>AirPollutants_Method.md; CAVEATS v3.12</t>
+          <t>Methods, chapter Emissions; CAVEATS v3.12</t>
         </is>
       </c>
       <c r="K159" s="9" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="J160" s="9" t="inlineStr">
         <is>
-          <t>ResultsSections_Method.md; CAVEATS v3.15</t>
+          <t>Methods, chapter Macro and results; CAVEATS v3.15</t>
         </is>
       </c>
       <c r="K160" s="9" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="J161" s="9" t="inlineStr">
         <is>
-          <t>ResultsSections_Method.md</t>
+          <t>Methods, chapter Macro and results</t>
         </is>
       </c>
       <c r="K161" s="9" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="J162" s="9" t="inlineStr">
         <is>
-          <t>DataTabs.md; CAVEATS v4.7</t>
+          <t>Methods, chapter Data tabs; CAVEATS v4.7</t>
         </is>
       </c>
       <c r="K162" s="9" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="J163" s="9" t="inlineStr">
         <is>
-          <t>PriceProjection_Method.md 5; LegacyDiff</t>
+          <t>Methods, chapter Prices 5; LegacyDiff</t>
         </is>
       </c>
       <c r="K163" s="9" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="J164" s="9" t="inlineStr">
         <is>
-          <t>Transport_Method.md; LegacyDiff</t>
+          <t>Methods, chapter Transport; LegacyDiff</t>
         </is>
       </c>
       <c r="K164" s="9" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="J165" s="9" t="inlineStr">
         <is>
-          <t>GDP_Method.md; LegacyDiff</t>
+          <t>Methods, chapter Macro and results; LegacyDiff</t>
         </is>
       </c>
       <c r="K165" s="9" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="J166" s="9" t="inlineStr">
         <is>
-          <t>GDP_Method.md</t>
+          <t>Methods, chapter Macro and results</t>
         </is>
       </c>
       <c r="K166" s="9" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="J167" s="9" t="inlineStr">
         <is>
-          <t>GDP_Method.md</t>
+          <t>Methods, chapter Macro and results</t>
         </is>
       </c>
       <c r="K167" s="9" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="J168" s="9" t="inlineStr">
         <is>
-          <t>GDP_Method.md</t>
+          <t>Methods, chapter Macro and results</t>
         </is>
       </c>
       <c r="K168" s="9" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="J169" s="9" t="inlineStr">
         <is>
-          <t>GDP_Method.md</t>
+          <t>Methods, chapter Macro and results</t>
         </is>
       </c>
       <c r="K169" s="9" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="J171" s="9" t="inlineStr">
         <is>
-          <t>PriceProjection_Method.md 6</t>
+          <t>Methods, chapter Prices 6</t>
         </is>
       </c>
       <c r="K171" s="9" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="J172" s="9" t="inlineStr">
         <is>
-          <t>PriceProjection_Method.md 6</t>
+          <t>Methods, chapter Prices 6</t>
         </is>
       </c>
       <c r="K172" s="9" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="J173" s="9" t="inlineStr">
         <is>
-          <t>PriceProjection_Method.md 5; LegacyDiff 66</t>
+          <t>Methods, chapter Prices 5; LegacyDiff 66</t>
         </is>
       </c>
       <c r="K173" s="9" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="J175" s="9" t="inlineStr">
         <is>
-          <t>PowerModel_Method.md; LegacyDiff 75</t>
+          <t>Methods, chapter Power; LegacyDiff 75</t>
         </is>
       </c>
       <c r="K175" s="9" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="J176" s="9" t="inlineStr">
         <is>
-          <t>PowerPrices_Method.md; LegacyDiff 76</t>
+          <t>Methods, chapter Power; LegacyDiff 76</t>
         </is>
       </c>
       <c r="K176" s="9" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="J177" s="9" t="inlineStr">
         <is>
-          <t>PowerPrices_Method.md; LegacyDiff 77</t>
+          <t>Methods, chapter Power; LegacyDiff 77</t>
         </is>
       </c>
       <c r="K177" s="9" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="J178" s="9" t="inlineStr">
         <is>
-          <t>PowerModel_Method.md; LegacyDiff 78</t>
+          <t>Methods, chapter Power; LegacyDiff 78</t>
         </is>
       </c>
       <c r="K178" s="9" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="J179" s="9" t="inlineStr">
         <is>
-          <t>PowerPrices_Method.md</t>
+          <t>Methods, chapter Power</t>
         </is>
       </c>
       <c r="K179" s="9" t="inlineStr">
@@ -10773,7 +10773,7 @@
       </c>
       <c r="J180" s="9" t="inlineStr">
         <is>
-          <t>PowerPrices_Method.md</t>
+          <t>Methods, chapter Power</t>
         </is>
       </c>
       <c r="K180" s="9" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="J181" s="9" t="inlineStr">
         <is>
-          <t>Transport_Method.md; TODO</t>
+          <t>Methods, chapter Transport; TODO</t>
         </is>
       </c>
       <c r="K181" s="9" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="J182" s="9" t="inlineStr">
         <is>
-          <t>PriceProjection_Method.md; TODO</t>
+          <t>Methods, chapter Prices; TODO</t>
         </is>
       </c>
       <c r="K182" s="9" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="J183" s="9" t="inlineStr">
         <is>
-          <t>PriceProjection_Method.md; TODO</t>
+          <t>Methods, chapter Prices; TODO</t>
         </is>
       </c>
       <c r="K183" s="9" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="J184" s="9" t="inlineStr">
         <is>
-          <t>GHG_Method.md</t>
+          <t>Methods, chapter Emissions</t>
         </is>
       </c>
       <c r="K184" s="9" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="J185" s="9" t="inlineStr">
         <is>
-          <t>GHG_Method.md</t>
+          <t>Methods, chapter Emissions</t>
         </is>
       </c>
       <c r="K185" s="9" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="J186" s="9" t="inlineStr">
         <is>
-          <t>Equations.md E53-E56; PriceProjection_Method.md</t>
+          <t>Equations.md E53-E56; Methods, chapter Prices</t>
         </is>
       </c>
       <c r="K186" s="9" t="inlineStr">
@@ -11139,12 +11139,12 @@
       <c r="H187" s="9" t="inlineStr"/>
       <c r="I187" s="9" t="inlineStr">
         <is>
-          <t>Stated as a rule (user 2026-10-20): GDP_Method.md section Timing rule and NORMS (circular references): revenue of year t moves GDP only from year t+1, the fiscal space reads revenue of year t only, and no same-year GDP effect reaches same-year demand. Recommendation to the CPAT team: state it in the legacy method too.</t>
+          <t>Stated as a rule (user 2026-10-20): Methods, chapter Macro and results section Timing rule and NORMS (circular references): revenue of year t moves GDP only from year t+1, the fiscal space reads revenue of year t only, and no same-year GDP effect reaches same-year demand. Recommendation to the CPAT team: state it in the legacy method too.</t>
         </is>
       </c>
       <c r="J187" s="9" t="inlineStr">
         <is>
-          <t>GDP_Method.md; NORMS (circular references)</t>
+          <t>Methods, chapter Macro and results; NORMS (circular references)</t>
         </is>
       </c>
       <c r="K187" s="9" t="inlineStr">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="F204" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Section 5b of every scenario group, every row live (Transport_Workbook_Notes.md); TrModel default Elasticity, Engineer by switch; the 17 legacy bugs of Transport_vs_Legacy.md section 3 fixed (B1-B23)</t>
+          <t>Departs from legacy: Section 5b of every scenario group, every row live (Methods, chapter Transport); TrModel default Elasticity, Engineer by switch; the 17 legacy bugs of Methods, chapter Transport section 3 fixed (B1-B23)</t>
         </is>
       </c>
       <c r="G204" s="9" t="inlineStr">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="H204" s="9" t="inlineStr">
         <is>
-          <t>None by default; with Engineer: road fuel use and EV shares as in Transport_vs_Legacy.md section 4</t>
+          <t>None by default; with Engineer: road fuel use and EV shares as in Methods, chapter Transport section 4</t>
         </is>
       </c>
       <c r="I204" s="9" t="inlineStr"/>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="J213" s="9" t="inlineStr">
         <is>
-          <t>TODO; Scenarios_Method.md</t>
+          <t>TODO; Methods, chapter Macro and results</t>
         </is>
       </c>
       <c r="K213" s="9" t="inlineStr">
@@ -12667,7 +12667,7 @@
       <c r="I218" s="9" t="inlineStr"/>
       <c r="J218" s="9" t="inlineStr">
         <is>
-          <t>check report section 1; PowerModel_Method.md</t>
+          <t>check report section 1; Methods, chapter Power</t>
         </is>
       </c>
       <c r="K218" s="9" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="J228" s="9" t="inlineStr">
         <is>
-          <t>GHG_Method.md</t>
+          <t>Methods, chapter Emissions</t>
         </is>
       </c>
       <c r="K228" s="9" t="inlineStr">
@@ -14869,7 +14869,7 @@
       <c r="I260" s="9" t="inlineStr"/>
       <c r="J260" s="9" t="inlineStr">
         <is>
-          <t>Distribution_Method.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K260" s="9" t="inlineStr">
@@ -14914,7 +14914,7 @@
       <c r="I261" s="9" t="inlineStr"/>
       <c r="J261" s="9" t="inlineStr">
         <is>
-          <t>Distribution_Method.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K261" s="9" t="inlineStr">
@@ -14959,7 +14959,7 @@
       <c r="I262" s="9" t="inlineStr"/>
       <c r="J262" s="9" t="inlineStr">
         <is>
-          <t>Distribution_Method.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K262" s="9" t="inlineStr">
@@ -15004,7 +15004,7 @@
       <c r="I263" s="9" t="inlineStr"/>
       <c r="J263" s="9" t="inlineStr">
         <is>
-          <t>Distribution_Method.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K263" s="9" t="inlineStr">
@@ -15049,7 +15049,7 @@
       <c r="I264" s="9" t="inlineStr"/>
       <c r="J264" s="9" t="inlineStr">
         <is>
-          <t>Distribution_Method.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K264" s="9" t="inlineStr">
@@ -15094,7 +15094,7 @@
       <c r="I265" s="9" t="inlineStr"/>
       <c r="J265" s="9" t="inlineStr">
         <is>
-          <t>Distribution_Method.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K265" s="9" t="inlineStr">
@@ -15139,7 +15139,7 @@
       <c r="I266" s="9" t="inlineStr"/>
       <c r="J266" s="9" t="inlineStr">
         <is>
-          <t>Distribution_Method.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K266" s="9" t="inlineStr">
@@ -15184,7 +15184,7 @@
       <c r="I267" s="9" t="inlineStr"/>
       <c r="J267" s="9" t="inlineStr">
         <is>
-          <t>Distribution_Method.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K267" s="9" t="inlineStr">
@@ -15229,7 +15229,7 @@
       <c r="I268" s="9" t="inlineStr"/>
       <c r="J268" s="9" t="inlineStr">
         <is>
-          <t>Distribution_Method.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K268" s="9" t="inlineStr">
@@ -15274,7 +15274,7 @@
       <c r="I269" s="9" t="inlineStr"/>
       <c r="J269" s="9" t="inlineStr">
         <is>
-          <t>Distribution_Method.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K269" s="9" t="inlineStr">

--- a/excel_ai/CPAT-AI_BugsAndIssues_latest.xlsx
+++ b/excel_ai/CPAT-AI_BugsAndIssues_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUGSandISSUES" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BUGSandISSUES'!$A$3:$K$283</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BUGSandISSUES'!$A$3:$L$283</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -505,7 +505,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BUGSandISSUES: CPAT-AI-Mitigation-Prototype v7.0 against legacy CPAT</t>
+          <t>BUGSandISSUES: CPAT-AI-Mitigation-Prototype v8.2 against legacy CPAT</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +538,7 @@
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Source: BUGS.md and ISSUES.md (generated from issues_register.py). Not included: potential upgrades (U), and bugs found and fixed in the prototype during development (M); both are in the Word register CPAT-AI_BugsAndIssues_v7.0.docx. Details and effects of the legacy bugs: LegacyBugFixes.md.</t>
+          <t>Source: BUGS.md and ISSUES.md (generated from issues_register.py). Not included: potential upgrades (U), and bugs found and fixed in the prototype during development (M); both are in the Word register CPAT-AI_BugsAndIssues_latest.docx. Details and effects of the legacy bugs: LegacyBugFixes.md. Column "Status in legacy 465": the legacy bugs in the latest CPAT file (CPAT 1.0pre_465), where the CPAT team fixed part of them (checked cell by cell); cell references are 465 rows.</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K283"/>
+  <dimension ref="A1:L283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -801,12 +801,13 @@
     <col width="52" customWidth="1" min="9" max="9"/>
     <col width="38" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bugs and issues of legacy CPAT and whether CPAT-AI-Mitigation-Prototype v7.0 replicates them</t>
+          <t>Bugs and issues of legacy CPAT and whether CPAT-AI-Mitigation-Prototype v8.2 replicates them</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -819,6 +820,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -876,6 +878,11 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>Status in legacy 465</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -933,6 +940,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -990,6 +1002,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -1047,6 +1064,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -1104,6 +1126,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -1161,6 +1188,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -1218,6 +1250,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -1275,6 +1312,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -1332,6 +1374,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -1389,6 +1436,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -1446,6 +1498,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -1503,6 +1560,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -1560,6 +1622,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -1617,6 +1684,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -1674,6 +1746,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -1731,6 +1808,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -1788,6 +1870,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>Fixed with caveats</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -1822,7 +1909,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Livestock, rice and waste CH4 are the inventory values divided by the GWP, constant over time; the abatement shares of the methane fee are computed (rows 6182, 6194, 6206) but not applied, so a methane fee on agriculture and waste has no effect.</t>
+          <t>Livestock, rice and waste CH4 are the inventory values divided by the GWP, constant over time; the abatement shares of the methane fee are computed (rows 6168, 6180, 6192) but not applied, so a methane fee on agriculture and waste has no effect.</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
@@ -1832,17 +1919,22 @@
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>Grow livestock, rice and waste methane with their drivers (income, population) and apply the abatement shares already computed in rows 6182, 6194, 6206.</t>
+          <t>Grow livestock, rice and waste methane with their drivers (income, population) and apply the abatement shares already computed in rows 6168, 6180, 6192.</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 6172-6227 (livestock, rice, waste)</t>
+          <t>Mitigation rows 6158-6213 (livestock, rice, waste)</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1894,12 +1986,17 @@
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 6155-6156</t>
+          <t>Mitigation rows 6141-6142</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1959,6 +2056,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -1993,7 +2095,7 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>The abatement share of waste equals that of livestock (=M6182) instead of the waste curve of CH4Inputs.</t>
+          <t>The abatement share of waste equals that of livestock (=M6168) instead of the waste curve of CH4Inputs.</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -2003,17 +2105,22 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>Use the waste curve of CH4Inputs for waste (row 6206 now = M6182, the livestock share).</t>
+          <t>Use the waste curve of CH4Inputs for waste (row 6192 now = M6168, the livestock share).</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>Mitigation row 6206</t>
+          <t>Mitigation row 6192</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2073,6 +2180,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -2122,12 +2234,17 @@
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 6704, 6806, ... (total emissions of each pollutant)</t>
+          <t>Mitigation rows 6690, 6792, ... (total emissions of each pollutant)</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2296,17 @@
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 2443-2446, 8288</t>
+          <t>Mitigation rows 2443-2446, 8274</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2244,6 +2366,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -2301,6 +2428,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -2358,6 +2490,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -2415,6 +2552,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
@@ -2472,6 +2614,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
@@ -2529,6 +2676,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
@@ -2586,6 +2738,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
@@ -2643,6 +2800,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
@@ -2700,6 +2862,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
@@ -2757,6 +2924,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
@@ -2814,6 +2986,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
@@ -2871,6 +3048,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
@@ -2928,6 +3110,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
@@ -2985,6 +3172,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L40" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
@@ -3042,6 +3234,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L41" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
@@ -3099,6 +3296,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L42" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
@@ -3156,6 +3358,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
@@ -3213,6 +3420,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
@@ -3247,7 +3459,7 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>The income factor points to the blank row 2440, so other energy use never grows with GDP; rows 6077-6084 have no additional-efficiency term.</t>
+          <t>The income factor points to the blank row 2440, so other energy use never grows with GDP; rows 6063-6070 have no additional-efficiency term.</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
@@ -3262,12 +3474,17 @@
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 6077-6085</t>
+          <t>Mitigation rows 6063-6071</t>
         </is>
       </c>
       <c r="K45" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3327,6 +3544,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
@@ -3384,6 +3606,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L47" s="9" t="inlineStr">
+        <is>
+          <t>Fixed with caveats</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
@@ -3441,6 +3668,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
@@ -3498,6 +3730,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
@@ -3555,6 +3792,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
@@ -3604,12 +3846,17 @@
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 18177-18181, 742</t>
+          <t>Mitigation rows 18162-18166, 742</t>
         </is>
       </c>
       <c r="K51" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3661,12 +3908,17 @@
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 18195-18213</t>
+          <t>Mitigation rows 18180-18198</t>
         </is>
       </c>
       <c r="K52" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3726,6 +3978,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
@@ -3783,6 +4040,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
@@ -3840,6 +4102,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
@@ -3897,6 +4164,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L56" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
@@ -3954,6 +4226,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
@@ -4011,6 +4288,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L58" s="9" t="inlineStr">
+        <is>
+          <t>Fixed with caveats</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
@@ -4068,6 +4350,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
@@ -4117,12 +4404,17 @@
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 15900-16700 (GAINS factor lookups)</t>
+          <t>Mitigation rows 15885-16685 (GAINS factor lookups)</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4451,7 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>A fuel that its GAINS subsector has no factor for gets 0, although it burns: Egypt 2022 residential LPG (3,182 ktoe), other mining diesel (3,819), food &amp; forestry diesel (927), fuel transformation LPG (2,466); food &amp; forestry shows about 1 t of NOx (legacy row 15939).</t>
+          <t>A fuel that its GAINS subsector has no factor for gets 0, although it burns: Egypt 2022 residential LPG (3,182 ktoe), other mining diesel (3,819), food &amp; forestry diesel (927), fuel transformation LPG (2,466); food &amp; forestry shows about 1 t of NOx (legacy row 15924).</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
@@ -4174,12 +4466,17 @@
       </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 15900-16700 (GAINS factor lookups; sheet EF_PM)</t>
+          <t>Mitigation rows 15885-16685 (GAINS factor lookups; sheet EF_PM)</t>
         </is>
       </c>
       <c r="K61" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4239,6 +4536,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
@@ -4296,6 +4598,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L63" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
@@ -4353,6 +4660,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>Not fixed (marked fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
@@ -4410,6 +4722,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>Not fixed (marked fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
@@ -4467,6 +4784,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
@@ -4524,6 +4846,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
@@ -4581,6 +4908,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
@@ -4638,6 +4970,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
@@ -4687,12 +5024,17 @@
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 8267-8288 (policy 14584-14605)</t>
+          <t>Mitigation rows 8253-8274 (policy 14569-14590)</t>
         </is>
       </c>
       <c r="K70" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4729,7 +5071,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>The excise (revenue) use of the first cohort looks up L$8127, a baseline-block cell (0), instead of the cohort's own row (L14387); the contractionary effect of the first year's revenue is dropped (Egypt about 3e-5 of GDP).</t>
+          <t>The excise (revenue) use of the first cohort looks up L$8113, a baseline-block cell (0), instead of the cohort's own row (L14372); the contractionary effect of the first year's revenue is dropped (Egypt about 3e-5 of GDP).</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
@@ -4739,17 +5081,22 @@
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>Match the first cohort's excise use on its own row (L14387, baseline L8070), not L$8127.</t>
+          <t>Match the first cohort's excise use on its own row (L14372, baseline L8056), not L$8113.</t>
         </is>
       </c>
       <c r="J71" s="9" t="inlineStr">
         <is>
-          <t>Mitigation row 8071 (policy 14388)</t>
+          <t>Mitigation row 8057 (policy 14373)</t>
         </is>
       </c>
       <c r="K71" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4786,7 +5133,7 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>The additional excise of gas in industry is the coal industry tax (R2512) x coal industry use (R6436).</t>
+          <t>The additional excise of gas in industry is the coal industry tax (R2512) x coal industry use (R6422).</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
@@ -4796,17 +5143,22 @@
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
-          <t>Use the gas industry excise rate (row 2581) and gas industry use in row 7761.</t>
+          <t>Use the gas industry excise rate (row 2581) and gas industry use in row 7747.</t>
         </is>
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>Mitigation row 7761 (policy 14078)</t>
+          <t>Mitigation row 7747 (policy 14063)</t>
         </is>
       </c>
       <c r="K72" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4853,17 +5205,22 @@
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>Multiply by _conv_ktoe_to_gj in rows 7805, 7819, 7873.</t>
+          <t>Multiply by _conv_ktoe_to_gj in rows 7791, 7805, 7859.</t>
         </is>
       </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 7805, 7819, 7873</t>
+          <t>Mitigation rows 7791, 7805, 7859</t>
         </is>
       </c>
       <c r="K73" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L73" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4910,17 +5267,22 @@
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>Read column R (the year) in rows 7671 and 7756.</t>
+          <t>Read column R (the year) in rows 7657 and 7742.</t>
         </is>
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 7671, 7756</t>
+          <t>Mitigation rows 7657, 7742</t>
         </is>
       </c>
       <c r="K74" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4957,7 +5319,7 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>Gas industry coverage divides by R6041 instead of the industry gas total (6442); kerosene power coverage multiplies power by domestic shipping (R2270 x R2273).</t>
+          <t>Gas industry coverage divides by R6027 instead of the industry gas total (6428); kerosene power coverage multiplies power by domestic shipping (R2270 x R2273).</t>
         </is>
       </c>
       <c r="H75" s="9" t="inlineStr">
@@ -4967,17 +5329,22 @@
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>Divide by the industry gas total (6442) in row 7691; use power x kerosene coverage (R2265 x R2270) in row 7718.</t>
+          <t>Divide by the industry gas total (6428) in row 7677; use power x kerosene coverage (R2265 x R2270) in row 7704.</t>
         </is>
       </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 7691 (policy 14008), 7718</t>
+          <t>Mitigation rows 7677 (policy 13993), 7704</t>
         </is>
       </c>
       <c r="K75" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L75" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5029,12 +5396,17 @@
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 17160-17164, 17190, 17201</t>
+          <t>Mitigation rows 17145-17149, 17175, 17186</t>
         </is>
       </c>
       <c r="K76" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L76" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5094,6 +5466,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
@@ -5128,7 +5505,7 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>The "indexed vs 2022" rows read rows 16331-16338 (electricity industry, electricity residential, coal industry, ...) under the labels electricity, coal, gas, oil, ...; E16317 tests the policy gas total instead of the baseline one; labels say 2022 = 100 where baseline = 100.</t>
+          <t>The "indexed vs 2022" rows read rows 16316-16323 (electricity industry, electricity residential, coal industry, ...) under the labels electricity, coal, gas, oil, ...; E16302 tests the policy gas total instead of the baseline one; labels say 2022 = 100 where baseline = 100.</t>
         </is>
       </c>
       <c r="H78" s="9" t="inlineStr">
@@ -5138,17 +5515,22 @@
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
-          <t>Point rows 16398-16405 to the average-price rows of each fuel; test the baseline gas total in E16317; relabel "baseline = 100".</t>
+          <t>Point rows 16383-16390 to the average-price rows of each fuel; test the baseline gas total in E16302; relabel "baseline = 100".</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 16317, 16389-16405</t>
+          <t>Mitigation rows 16302, 16374-16390</t>
         </is>
       </c>
       <c r="K78" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5208,6 +5590,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L79" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
@@ -5257,12 +5644,17 @@
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 2322-2325 (policy 8653-8656), 7789-7792</t>
+          <t>Mitigation rows 2322-2325 (policy 8638-8641), 7775-7778</t>
         </is>
       </c>
       <c r="K80" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L80" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5322,6 +5714,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L81" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
@@ -5379,6 +5776,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
@@ -5436,6 +5838,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L83" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
@@ -5493,6 +5900,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L84" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
@@ -5550,6 +5962,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L85" s="9" t="inlineStr">
+        <is>
+          <t>Fixed with caveats</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
@@ -5599,12 +6016,17 @@
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>Mitigation row 7820</t>
+          <t>Mitigation row 7806</t>
         </is>
       </c>
       <c r="K86" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L86" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -5664,6 +6086,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L87" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
@@ -5721,6 +6148,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L88" s="9" t="inlineStr">
+        <is>
+          <t>Fixed with caveats</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
@@ -5778,6 +6210,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L89" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
@@ -5835,6 +6272,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L90" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
@@ -5892,6 +6334,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L91" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
@@ -5949,6 +6396,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L92" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
@@ -6006,6 +6458,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L93" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
@@ -6063,6 +6520,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L94" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
@@ -6120,6 +6582,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L95" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
@@ -6177,6 +6644,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L96" s="9" t="inlineStr">
+        <is>
+          <t>Fixed with caveats</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
@@ -6226,12 +6698,17 @@
       </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>Mitigation C2199:C2201 ('Tax in nominal or real terms?', 'Exponential option or linear' twice) beside K2199:M2201 (road, residential, industrial additional efficiency, MTInputs F243-F245); E2385 (LPG 'Road'), E2386 (kerosene 'Industry') on all-sector rows (codes shp.lpg.all, shp.ker.all); D5615, D5722, D6072, D6083 'Other oil pinducts'</t>
+          <t>Mitigation C2199:C2201 ('Tax in nominal or real terms?', 'Exponential option or linear' twice) beside K2199:M2201 (road, residential, industrial additional efficiency, MTInputs F243-F245); E2385 (LPG 'Road'), E2386 (kerosene 'Industry') on all-sector rows (codes shp.lpg.all, shp.ker.all); D5615, D5711, D6058, D6069 'Other oil pinducts'</t>
         </is>
       </c>
       <c r="K97" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L97" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6745,7 @@
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>An EF-weighted average price (5714), an elasticity table (5668-5676) and 'Fuel'/'Average' demand and efficiency multiples (5727-5728) are computed but referenced nowhere; M5667 takes next year's GDP growth (N2446).</t>
+          <t>An EF-weighted average price (5703), an elasticity table (5668-5676) and 'Fuel'/'Average' demand and efficiency multiples (5727-5728) are computed but referenced nowhere; M5667 takes next year's GDP growth (N2446).</t>
         </is>
       </c>
       <c r="H98" s="9" t="inlineStr">
@@ -6283,12 +6760,17 @@
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 5667-5676, 5714, 5727-5728 (iron &amp; steel block; M5667 = N2446)</t>
+          <t>Mitigation rows 5667-5676, 5703, 5727-5728 (iron &amp; steel block; M5667 = N2446)</t>
         </is>
       </c>
       <c r="K98" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L98" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6348,6 +6830,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L99" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
@@ -6405,6 +6892,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L100" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
@@ -6462,6 +6954,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L101" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
@@ -6519,6 +7016,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L102" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
@@ -6576,6 +7078,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L103" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
@@ -6610,7 +7117,7 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>The SCC block of Manual inputs is read by nothing; the Manual option of NSCCSource / GSCCSource takes the path typed on Mitigation row 17683.</t>
+          <t>The SCC block of Manual inputs is read by nothing; the Manual option of NSCCSource / GSCCSource takes the path typed on Mitigation row 17668.</t>
         </is>
       </c>
       <c r="H104" s="9" t="inlineStr">
@@ -6620,17 +7127,22 @@
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
-          <t>Mitigation row 17683 = 'Manual inputs'!J237 (NSCC) / J240 (GSCC).</t>
+          <t>Mitigation row 17668 = 'Manual inputs'!J237 (NSCC) / J240 (GSCC).</t>
         </is>
       </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>Manual inputs rows 234-240; Mitigation row 17683</t>
+          <t>Manual inputs rows 234-240; Mitigation row 17668</t>
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L104" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -6690,6 +7202,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L105" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
@@ -6747,6 +7264,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L106" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
@@ -6804,6 +7326,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L107" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
@@ -6838,7 +7365,7 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>The additional renewable subsidy (MTInputs 355) starts in the year the consumer fuel subsidies start to be phased out; it has no start-year input of its own.</t>
+          <t>The additional renewable subsidy (MTInputs 353) starts in the year the consumer fuel subsidies start to be phased out; it has no start-year input of its own.</t>
         </is>
       </c>
       <c r="H108" s="9" t="inlineStr">
@@ -6853,12 +7380,17 @@
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>Mitigation E2736 (policy E9067) = row 270 = MTInputs F132 (YearConsSubPha)</t>
+          <t>Mitigation E2736 (policy E9052) = row 270 = MTInputs F132 (YearConsSubPha)</t>
         </is>
       </c>
       <c r="K108" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L108" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -6895,7 +7427,7 @@
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>Rows 7897-7900 = (row 2743 + row 2745) x generation, but row 2745 already equals row 2743 minus the additional subsidy, so the base subsidy enters twice; hydro (7899) ignores RenewableSubsidyHydro; biomass has no row; 7903 enters total revenue (row 8023).</t>
+          <t>Rows 7883-7886 = (row 2743 + row 2745) x generation, but row 2745 already equals row 2743 minus the additional subsidy, so the base subsidy enters twice; hydro (7885) ignores RenewableSubsidyHydro; biomass has no row; 7889 enters total revenue (row 8009).</t>
         </is>
       </c>
       <c r="H109" s="9" t="inlineStr">
@@ -6905,17 +7437,22 @@
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>Rows 7897-7901 = the subsidy by type (rows 3148-3152) x generation.</t>
+          <t>Rows 7883-7887 = the subsidy by type (rows 3148-3152) x generation.</t>
         </is>
       </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 7897-7903 (policy +6317)</t>
+          <t>Mitigation rows 7883-7889 (policy +6316)</t>
         </is>
       </c>
       <c r="K109" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L109" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -6975,6 +7512,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L110" s="9" t="inlineStr">
+        <is>
+          <t>Fixed with caveats</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
@@ -7009,7 +7551,7 @@
       </c>
       <c r="G111" s="9" t="inlineStr">
         <is>
-          <t>The rebate includes VAT (carbon cost x pass-through x (1 + VAT)) and enters total revenue through row 7749, while the VAT on the carbon cost is never counted as revenue.</t>
+          <t>The rebate includes VAT (carbon cost x pass-through x (1 + VAT)) and enters total revenue through row 7735, while the VAT on the carbon cost is never counted as revenue.</t>
         </is>
       </c>
       <c r="H111" s="9" t="inlineStr">
@@ -7024,12 +7566,17 @@
       </c>
       <c r="J111" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 3615, 3644, 3663, 7888, 7749 (policy +6331 / +6317)</t>
+          <t>Mitigation rows 3615, 3644, 3663, 7874, 7735 (policy +6316 / +6316)</t>
         </is>
       </c>
       <c r="K111" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L111" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -7066,7 +7613,7 @@
       </c>
       <c r="G112" s="9" t="inlineStr">
         <is>
-          <t>The revenue memo 3660 (and 7762) = manual excise x consumption in every year, while the price includes only the change since the last historical year x pass-through.</t>
+          <t>The revenue memo 3660 (and 7748) = manual excise x consumption in every year, while the price includes only the change since the last historical year x pass-through.</t>
         </is>
       </c>
       <c r="H112" s="9" t="inlineStr">
@@ -7081,12 +7628,17 @@
       </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 3602, 3631, 3660, 7885, 7762</t>
+          <t>Mitigation rows 3602, 3631, 3660, 7871, 7748</t>
         </is>
       </c>
       <c r="K112" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L112" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -7133,17 +7685,22 @@
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
-          <t>In rows 8708-8719 refer to the policy block ($D$8700, L$8706) instead of $D$2369 and L$2375.</t>
+          <t>In rows 8693-8704 refer to the policy block ($D$8685, L$8691) instead of $D$2369 and L$2375.</t>
         </is>
       </c>
       <c r="J113" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 8708-8719 (policy copies of 2377-2388)</t>
+          <t>Mitigation rows 8693-8704 (policy copies of 2377-2388)</t>
         </is>
       </c>
       <c r="K113" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L113" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -7203,6 +7760,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L114" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
@@ -7237,7 +7799,7 @@
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
-          <t>MTInputs 354-355 are labelled $/kWh nominal but enter the real cost and revenue without deflation (row 2743 = -E2734). A formula that contradicts its label: reclassified as a bug by the user (2026-10-19).</t>
+          <t>MTInputs 352-353 are labelled $/kWh nominal but enter the real cost and revenue without deflation (row 2743 = -E2734). A formula that contradicts its label: reclassified as a bug by the user (2026-10-19).</t>
         </is>
       </c>
       <c r="H115" s="9" t="inlineStr">
@@ -7247,17 +7809,22 @@
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
-          <t>Deflate the nominal inputs (rows 2734-2735) by the CPI index before they enter row 2743, or relabel MTInputs 354-355 as real.</t>
+          <t>Deflate the nominal inputs (rows 2734-2735) by the CPI index before they enter row 2743, or relabel MTInputs 352-353 as real.</t>
         </is>
       </c>
       <c r="J115" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 2734-2735, 2743, 2745 (MTInputs 354-355)</t>
+          <t>Mitigation rows 2734-2735, 2743, 2745 (MTInputs 352-353)</t>
         </is>
       </c>
       <c r="K115" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L115" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -7304,17 +7871,22 @@
       </c>
       <c r="I116" s="9" t="inlineStr">
         <is>
-          <t>Point row 2555 (and policy 8886) at the residential gas ETS row 1715.</t>
+          <t>Point row 2555 (and policy 8871) at the residential gas ETS row 1715.</t>
         </is>
       </c>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>Mitigation row 2555 (policy 8886)</t>
+          <t>Mitigation row 2555 (policy 8871)</t>
         </is>
       </c>
       <c r="K116" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L116" s="9" t="inlineStr">
+        <is>
+          <t>Fixed with caveats</t>
         </is>
       </c>
     </row>
@@ -7374,6 +7946,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L117" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
@@ -7431,6 +8008,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L118" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
@@ -7488,6 +8070,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L119" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
@@ -7522,7 +8109,7 @@
       </c>
       <c r="G120" s="9" t="inlineStr">
         <is>
-          <t>F18414 = IF(target year &lt; 2030, (2030 - base)/(target year - base), 1) is at least 1, so the "&lt;1" branches of the Fixed and Historical blocks (rows 18441-18443, 18458-18460) never run, while the BAU block multiplies both the reduction (18422) and the level (18425: BAU x (1 - reduction x adj) x adj) by it: a 2025 BAU target is scaled up twice and the other types not at all. Found by the item 8 plan (v5.7).</t>
+          <t>F18399 = IF(target year &lt; 2030, (2030 - base)/(target year - base), 1) is at least 1, so the "&lt;1" branches of the Fixed and Historical blocks (rows 18426-18428, 18443-18445) never run, while the BAU block multiplies both the reduction (18407) and the level (18410: BAU x (1 - reduction x adj) x adj) by it: a 2025 BAU target is scaled up twice and the other types not at all. Found by the item 8 plan (v5.7).</t>
         </is>
       </c>
       <c r="H120" s="9" t="inlineStr">
@@ -7537,12 +8124,17 @@
       </c>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 18414, 18422-18427, 18441-18443, 18458-18460</t>
+          <t>Mitigation rows 18399, 18407-18412, 18426-18428, 18443-18445</t>
         </is>
       </c>
       <c r="K120" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L120" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -7579,7 +8171,7 @@
       </c>
       <c r="G121" s="9" t="inlineStr">
         <is>
-          <t>Rows 18497-18498 divide the start-year emissions by the target (G18446/F18494) while row 18499 divides the target by the start-year emissions; the chart rows 18509-18510 read 18499 for the unconditional line and 18498 (inverted) for the conditional one. Found by the item 8 plan (v5.7).</t>
+          <t>Rows 18482-18483 divide the start-year emissions by the target (G18431/F18479) while row 18484 divides the target by the start-year emissions; the chart rows 18494-18495 read 18484 for the unconditional line and 18483 (inverted) for the conditional one. Found by the item 8 plan (v5.7).</t>
         </is>
       </c>
       <c r="H121" s="9" t="inlineStr">
@@ -7589,17 +8181,22 @@
       </c>
       <c r="I121" s="9" t="inlineStr">
         <is>
-          <t>Use target / start-year emissions in rows 18497-18498, as 18499.</t>
+          <t>Use target / start-year emissions in rows 18482-18483, as 18484.</t>
         </is>
       </c>
       <c r="J121" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 18497-18499</t>
+          <t>Mitigation rows 18482-18484</t>
         </is>
       </c>
       <c r="K121" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L121" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -7636,7 +8233,7 @@
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>Rows 18458-18460 return the cut (F18455 x adj) when adj &lt; 1 and the level otherwise; harmless today only because adj &lt; 1 never happens (L119). Found by the item 8 plan (v5.7).</t>
+          <t>Rows 18443-18445 return the cut (F18440 x adj) when adj &lt; 1 and the level otherwise; harmless today only because adj &lt; 1 never happens (L119). Found by the item 8 plan (v5.7).</t>
         </is>
       </c>
       <c r="H122" s="9" t="inlineStr">
@@ -7646,17 +8243,22 @@
       </c>
       <c r="I122" s="9" t="inlineStr">
         <is>
-          <t>Return F18452 - F18455 x adj (the level), as the Fixed block.</t>
+          <t>Return F18437 - F18440 x adj (the level), as the Fixed block.</t>
         </is>
       </c>
       <c r="J122" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 18458-18460</t>
+          <t>Mitigation rows 18443-18445</t>
         </is>
       </c>
       <c r="K122" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L122" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -7693,7 +8295,7 @@
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>The excludes-LULUCF branch adds $J$18465 where the LULUCF emissions are in column I (I18465 = G - F). J18465 is not blank: it holds the non-CO2 emissions (F - H, 254.9 Mt for Egypt), so non-CO2 is counted twice and LULUCF is missed (cell plan 2026-10-20 corrected the register). Found by the item 8 plan (v5.7).</t>
+          <t>The excludes-LULUCF branch adds $J$18450 where the LULUCF emissions are in column I (I18450 = G - F). J18450 is not blank: it holds the non-CO2 emissions (F - H, 254.9 Mt for Egypt), so non-CO2 is counted twice and LULUCF is missed (cell plan 2026-10-20 corrected the register). Found by the item 8 plan (v5.7).</t>
         </is>
       </c>
       <c r="H123" s="9" t="inlineStr">
@@ -7703,17 +8305,22 @@
       </c>
       <c r="I123" s="9" t="inlineStr">
         <is>
-          <t>Add I18465 (LULUCF) instead of J18465 (non-CO2).</t>
+          <t>Add I18450 (LULUCF) instead of J18450 (non-CO2).</t>
         </is>
       </c>
       <c r="J123" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 18476-18477</t>
+          <t>Mitigation rows 18461-18462</t>
         </is>
       </c>
       <c r="K123" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L123" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -7765,12 +8372,17 @@
       </c>
       <c r="J124" s="9" t="inlineStr">
         <is>
-          <t>Mitigation row 18466</t>
+          <t>Mitigation row 18451</t>
         </is>
       </c>
       <c r="K124" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L124" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -7830,6 +8442,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L125" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
@@ -7887,6 +8504,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L126" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
@@ -7944,6 +8566,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L127" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
@@ -8001,6 +8628,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L128" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
@@ -8035,27 +8667,32 @@
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
-          <t>The net revenue rows (USD and % of GDP) read the next column of rows 8038 and 8043 (K6252 = L8038 ... AD6252 = AE8038), so each year shows the next year's net revenue. Report only (rows 6253, 6258 read them). Found by the read-of-later-years scan of legacy (v6.2, user 2026-10-20).</t>
+          <t>The net revenue rows (USD and % of GDP) read the next column of rows 8024 and 8029 (K6238 = L8024 ... AD6238 = AE8024), so each year shows the next year's net revenue. Report only (rows 6239, 6244 read them). Found by the read-of-later-years scan of legacy (v6.2, user 2026-10-20).</t>
         </is>
       </c>
       <c r="H129" s="9" t="inlineStr">
         <is>
-          <t>Each year reports the next year's net revenue (USD and % of GDP). prototype: Not in the prototype (its revenue rows read the same year; reporting rebuilt). Legacy fix: K6252 =K8038 and K6257 =K8043, filled K:AD.</t>
+          <t>Each year reports the next year's net revenue (USD and % of GDP). prototype: Not in the prototype (its revenue rows read the same year; reporting rebuilt). Legacy fix: K6238 =K8024 and K6243 =K8029, filled K:AD.</t>
         </is>
       </c>
       <c r="I129" s="9" t="inlineStr">
         <is>
-          <t>K6252 =K8038 and K6257 =K8043, filled K:AD; policy rows 12569, 12574 the same (+6,317).</t>
+          <t>K6238 =K8024 and K6243 =K8029, filled K:AD; policy rows 12554, 12559 the same (+6,316).</t>
         </is>
       </c>
       <c r="J129" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 6252, 6257 (policy 12569, 12574)</t>
+          <t>Mitigation rows 6238, 6243 (policy 12554, 12559)</t>
         </is>
       </c>
       <c r="K129" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L129" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -8092,27 +8729,32 @@
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>The rows add L2743 + L2745, but L2745 already includes L2743, so the baseline renewable subsidy is counted twice. Only when MTInputs row 354 (RenewableSubsidyBL) is not zero; 0 for Egypt. Found by the cell plans (user 2026-10-20: a bug).</t>
+          <t>The rows add L2743 + L2745, but L2745 already includes L2743, so the baseline renewable subsidy is counted twice. Only when MTInputs row 352 (RenewableSubsidyBL) is not zero; 0 for Egypt. Found by the cell plans (user 2026-10-20: a bug).</t>
         </is>
       </c>
       <c r="H130" s="9" t="inlineStr">
         <is>
-          <t>With a baseline renewable subsidy (MTInputs 354) the subsidy cost is counted twice. prototype: Fixed (prototype: one renewable subsidy row rnsp = baseline + additional, counted once).</t>
+          <t>With a baseline renewable subsidy (MTInputs 352) the subsidy cost is counted twice. prototype: Fixed (prototype: one renewable subsidy row rnsp = baseline + additional, counted once).</t>
         </is>
       </c>
       <c r="I130" s="9" t="inlineStr">
         <is>
-          <t>In rows 2785-2788, 2947-2951 and 7897-7900 drop the + L2743 term (L2745 already includes it); policy rows the same (+6,331).</t>
+          <t>In rows 2785-2788, 2947-2951 and 7883-7886 drop the + L2743 term (L2745 already includes it); policy rows the same (+6,316).</t>
         </is>
       </c>
       <c r="J130" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 2785-2788, 2947-2951, 7897-7900 (against 2743, 2745)</t>
+          <t>Mitigation rows 2785-2788, 2947-2951, 7883-7886 (against 2743, 2745)</t>
         </is>
       </c>
       <c r="K130" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L130" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8149,7 +8791,7 @@
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>F18471 (conditional) applies the cut to the target-year BAU intensity (F18469); F18470 (unconditional) applies it to the reference-year intensity (F18468). Found by the cell plans (user 2026-10-20: a bug).</t>
+          <t>F18456 (conditional) applies the cut to the target-year BAU intensity (F18454); F18455 (unconditional) applies it to the reference-year intensity (F18453). Found by the cell plans (user 2026-10-20: a bug).</t>
         </is>
       </c>
       <c r="H131" s="9" t="inlineStr">
@@ -8159,17 +8801,22 @@
       </c>
       <c r="I131" s="9" t="inlineStr">
         <is>
-          <t>F18471: apply the cut to the reference-year intensity F18468, as F18470 does.</t>
+          <t>F18456: apply the cut to the reference-year intensity F18453, as F18455 does.</t>
         </is>
       </c>
       <c r="J131" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 18470-18471</t>
+          <t>Mitigation rows 18455-18456</t>
         </is>
       </c>
       <c r="K131" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L131" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8221,12 +8868,17 @@
       </c>
       <c r="J132" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 466, 2442, 16185 (gdp.pre.lvl); 7736, 7756, 7999 (sub.new.usd); 7652-13977 (rev.ctr.coa)</t>
+          <t>Mitigation rows 466, 2442, 16170 (gdp.pre.lvl); 7722, 7742, 7985 (sub.new.usd); 7638-13962 (rev.ctr.coa)</t>
         </is>
       </c>
       <c r="K132" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L132" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8278,12 +8930,17 @@
       </c>
       <c r="J133" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 7620, 13937 (oc.tot.); em.pm2.All.&lt;sector&gt; rows</t>
+          <t>Mitigation rows 7606, 13922 (oc.tot.); em.pm2.All.&lt;sector&gt; rows</t>
         </is>
       </c>
       <c r="K133" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L133" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8335,12 +8992,17 @@
       </c>
       <c r="J134" s="9" t="inlineStr">
         <is>
-          <t>Mitigation rows 7620, 13937 and the GHG total rows (nox.tot)</t>
+          <t>Mitigation rows 7606, 13922 and the GHG total rows (nox.tot)</t>
         </is>
       </c>
       <c r="K134" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L134" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -8396,6 +9058,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L135" s="9" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
@@ -8449,6 +9112,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L136" s="9" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
@@ -8502,6 +9166,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L137" s="9" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
@@ -8536,7 +9201,7 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>Legacy counts the methane fee in total revenue (row 8024) and so in the fiscal space, on the scenario's own activity. The prototype counts it too, but with the stored scenario-1 activity of downstream gas and biomass use (v6.2, user decision 2026-10-20: no vulnerability to circular references through the GDP feedback). Differs from legacy only when a policy changes gas or biomass use and a methane fee applies. None for Egypt (no methane fee in the scenarios).</t>
+          <t>Legacy counts the methane fee in total revenue (row 8010) and so in the fiscal space, on the scenario's own activity. The prototype counts it too, but with the stored scenario-1 activity of downstream gas and biomass use (v6.2, user decision 2026-10-20: no vulnerability to circular references through the GDP feedback). Differs from legacy only when a policy changes gas or biomass use and a methane fee applies. None for Egypt (no methane fee in the scenarios).</t>
         </is>
       </c>
       <c r="H138" s="9" t="inlineStr"/>
@@ -8555,6 +9220,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L138" s="9" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
@@ -8608,6 +9274,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L139" s="9" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
@@ -8661,6 +9328,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L140" s="9" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
@@ -8714,6 +9382,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L141" s="9" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
@@ -8767,6 +9436,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L142" s="9" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
@@ -8820,6 +9490,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L143" s="9" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
@@ -8854,7 +9525,7 @@
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>Legacy row 18464 H uses 5665 (Mt CO2) for China instead of the data (row 889). The prototype reads sheet GHGHist (or the model where the reference year is modelled); China's latest NDC is a Historical target (ref 2024, modelled), so the value is not used.</t>
+          <t>Legacy row 18449 H uses 5665 (Mt CO2) for China instead of the data (row 889). The prototype reads sheet GHGHist (or the model where the reference year is modelled); China's latest NDC is a Historical target (ref 2024, modelled), so the value is not used.</t>
         </is>
       </c>
       <c r="H144" s="9" t="inlineStr"/>
@@ -8873,6 +9544,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L144" s="9" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
@@ -8926,6 +9598,7 @@
           <t>Dropped</t>
         </is>
       </c>
+      <c r="L145" s="9" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
@@ -8979,6 +9652,7 @@
           <t>Dropped</t>
         </is>
       </c>
+      <c r="L146" s="9" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
@@ -9032,6 +9706,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L147" s="9" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
@@ -9085,6 +9760,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L148" s="9" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
@@ -9138,6 +9814,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L149" s="9" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
@@ -9191,6 +9868,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L150" s="9" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
@@ -9244,6 +9922,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L151" s="9" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
@@ -9297,6 +9976,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L152" s="9" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
@@ -9350,6 +10030,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L153" s="9" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
@@ -9390,7 +10071,7 @@
       <c r="H154" s="9" t="inlineStr"/>
       <c r="I154" s="9" t="inlineStr">
         <is>
-          <t>Traced (v5.6): legacy process emissions = 2023 inventory x the year-on-year growth of industrial energy CO2 (row 6590; 2024: +16.8%, the rebound after the 2023 demand shock, so 56.9 -&gt; 66.5). The prototype floored that growth at 0 (a departure: removed in v5.6, as legacy). The remaining gap is the industrial energy CO2 path, part of the fuel-use gap (I14).</t>
+          <t>Traced (v5.6): legacy process emissions = 2023 inventory x the year-on-year growth of industrial energy CO2 (row 6576; 2024: +16.8%, the rebound after the 2023 demand shock, so 56.9 -&gt; 66.5). The prototype floored that growth at 0 (a departure: removed in v5.6, as legacy). The remaining gap is the industrial energy CO2 path, part of the fuel-use gap (I14).</t>
         </is>
       </c>
       <c r="J154" s="9" t="inlineStr">
@@ -9403,6 +10084,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L154" s="9" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
@@ -9443,7 +10125,7 @@
       <c r="H155" s="9" t="inlineStr"/>
       <c r="I155" s="9" t="inlineStr">
         <is>
-          <t>Checked (v5.6): energy N2O moves with energy CO2 as legacy (row 7563 = previous x CO2 ratio). Production for fuel-supply methane differs: now issue I66.</t>
+          <t>Checked (v5.6): energy N2O moves with energy CO2 as legacy (row 7549 = previous x CO2 ratio). Production for fuel-supply methane differs: now issue I66.</t>
         </is>
       </c>
       <c r="J155" s="9" t="inlineStr">
@@ -9456,6 +10138,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L155" s="9" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
@@ -9509,6 +10192,7 @@
           <t>Dropped</t>
         </is>
       </c>
+      <c r="L156" s="9" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
@@ -9562,6 +10246,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L157" s="9" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
@@ -9596,7 +10281,7 @@
       </c>
       <c r="G158" s="9" t="inlineStr">
         <is>
-          <t>Legacy row 7534 ("Adjust EFs to match energy-related CO2 to UNFCCC inventories?", Yes* by default) multiplies every CO2 EF by the inventory energy CO2 of the year before the base year over the estimate from the base-year energy balance (Egypt: 2021 inventory against 2022, 0.930), so CO2 is about 7% below uncalibrated EFs in every sector. The inventory has a break between 2021 and 2022 (I17: 211 to 252 Mt), which legacy carries into the factor. v4.11 replicates legacy (user 2026-10-18: go with legacy); before, the prototype calibrated in 2024 and kept the switch off (user decisions v3.2, v3.4).</t>
+          <t>Legacy row 7520 ("Adjust EFs to match energy-related CO2 to UNFCCC inventories?", Yes* by default) multiplies every CO2 EF by the inventory energy CO2 of the year before the base year over the estimate from the base-year energy balance (Egypt: 2021 inventory against 2022, 0.930), so CO2 is about 7% below uncalibrated EFs in every sector. The inventory has a break between 2021 and 2022 (I17: 211 to 252 Mt), which legacy carries into the factor. v4.11 replicates legacy (user 2026-10-18: go with legacy); before, the prototype calibrated in 2024 and kept the switch off (user decisions v3.2, v3.4).</t>
         </is>
       </c>
       <c r="H158" s="9" t="inlineStr"/>
@@ -9615,6 +10300,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L158" s="9" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
@@ -9649,7 +10335,7 @@
       </c>
       <c r="G159" s="9" t="inlineStr">
         <is>
-          <t>Legacy rows 7297-7321 feed the air-pollution module CH4 by sector: oil and gas extraction methane under "other", agriculture and waste methane under "food &amp; forestry" (waste is not food or forestry), no combustion CH4 (no factors in legacy). v3.12 replicates the allocation and adds the combustion CH4 of each sector (GAINS factors, section 14), with all fossil fuel supply methane (extraction, downstream gas, coal mining, biomass) under "other".</t>
+          <t>Legacy rows 7283-7307 feed the air-pollution module CH4 by sector: oil and gas extraction methane under "other", agriculture and waste methane under "food &amp; forestry" (waste is not food or forestry), no combustion CH4 (no factors in legacy). v3.12 replicates the allocation and adds the combustion CH4 of each sector (GAINS factors, section 14), with all fossil fuel supply methane (extraction, downstream gas, coal mining, biomass) under "other".</t>
         </is>
       </c>
       <c r="H159" s="9" t="inlineStr"/>
@@ -9668,6 +10354,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L159" s="9" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
@@ -9702,7 +10389,7 @@
       </c>
       <c r="G160" s="9" t="inlineStr">
         <is>
-          <t>Legacy's effective carbon rate (row 16662) and total carbon price (F5d) divide revenue net of subsidies, VAT included, by CO2; the OECD effective carbon rate counts carbon taxes, fuel excises and permit prices only. The prototype replicates the legacy definition (section 17, v3.15) and says so in the note; Egypt has negative rates (subsidies exceed taxes).</t>
+          <t>Legacy's effective carbon rate (row 16647) and total carbon price (F5d) divide revenue net of subsidies, VAT included, by CO2; the OECD effective carbon rate counts carbon taxes, fuel excises and permit prices only. The prototype replicates the legacy definition (section 17, v3.15) and says so in the note; Egypt has negative rates (subsidies exceed taxes).</t>
         </is>
       </c>
       <c r="H160" s="9" t="inlineStr"/>
@@ -9721,6 +10408,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L160" s="9" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
@@ -9774,6 +10462,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L161" s="9" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
@@ -9827,6 +10516,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L162" s="9" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
@@ -9880,6 +10570,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L163" s="9" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
@@ -9933,6 +10624,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L164" s="9" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
@@ -9967,7 +10659,7 @@
       </c>
       <c r="G165" s="9" t="inlineStr">
         <is>
-          <t>Legacy row 14356 takes the yearly change of the revenue gain in USD over the current GDP, not the change of the gain as a share of GDP: with GDP growing, a constant share of GDP keeps giving impulses (Egypt: impulses sum to 4.9% of GDP against a final fiscal space of 3.5%). Replicated in v4.15 (user 2026-10-18: replicate legacy, note issues).</t>
+          <t>Legacy row 14341 takes the yearly change of the revenue gain in USD over the current GDP, not the change of the gain as a share of GDP: with GDP growing, a constant share of GDP keeps giving impulses (Egypt: impulses sum to 4.9% of GDP against a final fiscal space of 3.5%). Replicated in v4.15 (user 2026-10-18: replicate legacy, note issues).</t>
         </is>
       </c>
       <c r="H165" s="9" t="inlineStr"/>
@@ -9986,6 +10678,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L165" s="9" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
@@ -10039,6 +10732,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L166" s="9" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
@@ -10092,6 +10786,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L167" s="9" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
@@ -10145,6 +10840,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L168" s="9" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
@@ -10198,6 +10894,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L169" s="9" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
@@ -10232,13 +10929,13 @@
       </c>
       <c r="G170" s="9" t="inlineStr">
         <is>
-          <t>Legacy total revenue (row 8026) includes the transport revenues of the engineer road model (customs and VAT on vehicles, feebates, vehicle and charging subsidies, distance tax; rows 7913-7999) and the renewable subsidy cost (from the elasticity power model even where the engineer model is used, rows 7896-7904). The prototype 12e block has both rows at 0 (road engineer revenues parked; no renewable subsidy policy). Egypt: transport +0.04 bn in 2030 against baseline.</t>
+          <t>Legacy total revenue (row 8012) includes the transport revenues of the engineer road model (customs and VAT on vehicles, feebates, vehicle and charging subsidies, distance tax; rows 7899-7985) and the renewable subsidy cost (from the elasticity power model even where the engineer model is used, rows 7882-7890). The prototype 12e block has both rows at 0 (road engineer revenues parked; no renewable subsidy policy). Egypt: transport +0.04 bn in 2030 against baseline.</t>
         </is>
       </c>
       <c r="H170" s="9" t="inlineStr"/>
       <c r="I170" s="9" t="inlineStr">
         <is>
-          <t>Renewable subsidies: in the power model since v5.4 (prrns), counted in rsub, rtot and block 12e row rpol.ren, as legacy rows 7896-7904. Transport revenues: dropped with the engineer road model (I61, user 2026-10-20); row rpol.trs stays 0.</t>
+          <t>Renewable subsidies: in the power model since v5.4 (prrns), counted in rsub, rtot and block 12e row rpol.ren, as legacy rows 7882-7890. Transport revenues: dropped with the engineer road model (I61, user 2026-10-20); row rpol.trs stays 0.</t>
         </is>
       </c>
       <c r="J170" s="9" t="inlineStr">
@@ -10251,6 +10948,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L170" s="9" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
@@ -10304,6 +11002,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L171" s="9" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
@@ -10357,6 +11056,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L172" s="9" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
@@ -10410,6 +11110,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L173" s="9" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
@@ -10463,6 +11164,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L174" s="9" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
@@ -10516,6 +11218,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L175" s="9" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
@@ -10550,7 +11253,7 @@
       </c>
       <c r="G176" s="9" t="inlineStr">
         <is>
-          <t>MTInputs 354-355 are labelled $/kWh nominal and enter the real cost and revenue without deflation (Mitigation row 2743). Replicated (rows rnsp, rns).</t>
+          <t>MTInputs 352-353 are labelled $/kWh nominal and enter the real cost and revenue without deflation (Mitigation row 2743). Replicated (rows rnsp, rns).</t>
         </is>
       </c>
       <c r="H176" s="9" t="inlineStr"/>
@@ -10569,6 +11272,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L176" s="9" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
@@ -10622,6 +11326,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L177" s="9" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
@@ -10675,6 +11380,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L178" s="9" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
@@ -10728,6 +11434,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L179" s="9" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
@@ -10781,6 +11488,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L180" s="9" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
@@ -10834,6 +11542,7 @@
           <t>Dropped</t>
         </is>
       </c>
+      <c r="L181" s="9" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="9" t="inlineStr">
@@ -10887,6 +11596,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L182" s="9" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
@@ -10940,6 +11650,7 @@
           <t>Dropped</t>
         </is>
       </c>
+      <c r="L183" s="9" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
@@ -10974,7 +11685,7 @@
       </c>
       <c r="G184" s="9" t="inlineStr">
         <is>
-          <t>Legacy grows crude oil, natural gas and coal production (rows 6146-6149) from 2024 with the producer-price response to the methane fee (rows 6137-6144: price increase x pass-through, Manual inputs J190:J194 elasticities) and the growth of world demand of the global demand scenario (Prices_int rows 323-333, lagged one year). The prototype holds production at the base year (rows ch4.act og, cm). Found 2026-10-19 checking I26.</t>
+          <t>Legacy grows crude oil, natural gas and coal production (rows 6132-6135) from 2024 with the producer-price response to the methane fee (rows 6123-6130: price increase x pass-through, Manual inputs J190:J194 elasticities) and the growth of world demand of the global demand scenario (Prices_int rows 323-333, lagged one year). The prototype holds production at the base year (rows ch4.act og, cm). Found 2026-10-19 checking I26.</t>
         </is>
       </c>
       <c r="H184" s="9" t="inlineStr"/>
@@ -10993,6 +11704,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L184" s="9" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
@@ -11046,6 +11758,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L185" s="9" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
@@ -11099,6 +11812,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L186" s="9" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
@@ -11133,7 +11847,7 @@
       </c>
       <c r="G187" s="9" t="inlineStr">
         <is>
-          <t>Legacy and the prototype let revenue of year t move GDP only from year t+1 (legacy row 8776 reads the previous column; prototype gdp.lvl = 1 + last year's gdp.eff), and the fiscal space reads revenue of year t only. This lag is what keeps the model free of circular references whatever the revenue lines read; it is not stated anywhere. Recommendation to the CPAT team: make it an explicit rule of the method and keep it when the GDP block changes. Replicated.</t>
+          <t>Legacy and the prototype let revenue of year t move GDP only from year t+1 (legacy row 8761 reads the previous column; prototype gdp.lvl = 1 + last year's gdp.eff), and the fiscal space reads revenue of year t only. This lag is what keeps the model free of circular references whatever the revenue lines read; it is not stated anywhere. Recommendation to the CPAT team: make it an explicit rule of the method and keep it when the GDP block changes. Replicated.</t>
         </is>
       </c>
       <c r="H187" s="9" t="inlineStr"/>
@@ -11152,6 +11866,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L187" s="9" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
@@ -11201,6 +11916,7 @@
         </is>
       </c>
       <c r="K188" s="9" t="inlineStr"/>
+      <c r="L188" s="9" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
@@ -11250,6 +11966,7 @@
         </is>
       </c>
       <c r="K189" s="9" t="inlineStr"/>
+      <c r="L189" s="9" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
@@ -11299,6 +12016,7 @@
         </is>
       </c>
       <c r="K190" s="9" t="inlineStr"/>
+      <c r="L190" s="9" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
@@ -11348,6 +12066,7 @@
         </is>
       </c>
       <c r="K191" s="9" t="inlineStr"/>
+      <c r="L191" s="9" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
@@ -11397,6 +12116,7 @@
         </is>
       </c>
       <c r="K192" s="9" t="inlineStr"/>
+      <c r="L192" s="9" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
@@ -11446,6 +12166,7 @@
         </is>
       </c>
       <c r="K193" s="9" t="inlineStr"/>
+      <c r="L193" s="9" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
@@ -11495,6 +12216,7 @@
         </is>
       </c>
       <c r="K194" s="9" t="inlineStr"/>
+      <c r="L194" s="9" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
@@ -11544,6 +12266,7 @@
         </is>
       </c>
       <c r="K195" s="9" t="inlineStr"/>
+      <c r="L195" s="9" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
@@ -11593,6 +12316,7 @@
         </is>
       </c>
       <c r="K196" s="9" t="inlineStr"/>
+      <c r="L196" s="9" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
@@ -11642,6 +12366,7 @@
         </is>
       </c>
       <c r="K197" s="9" t="inlineStr"/>
+      <c r="L197" s="9" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
@@ -11691,6 +12416,7 @@
         </is>
       </c>
       <c r="K198" s="9" t="inlineStr"/>
+      <c r="L198" s="9" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
@@ -11740,6 +12466,7 @@
         </is>
       </c>
       <c r="K199" s="9" t="inlineStr"/>
+      <c r="L199" s="9" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
@@ -11789,6 +12516,7 @@
         </is>
       </c>
       <c r="K200" s="9" t="inlineStr"/>
+      <c r="L200" s="9" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
@@ -11838,6 +12566,7 @@
         </is>
       </c>
       <c r="K201" s="9" t="inlineStr"/>
+      <c r="L201" s="9" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="9" t="inlineStr">
@@ -11887,6 +12616,7 @@
         </is>
       </c>
       <c r="K202" s="9" t="inlineStr"/>
+      <c r="L202" s="9" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
@@ -11936,6 +12666,7 @@
         </is>
       </c>
       <c r="K203" s="9" t="inlineStr"/>
+      <c r="L203" s="9" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="9" t="inlineStr">
@@ -11985,6 +12716,7 @@
         </is>
       </c>
       <c r="K204" s="9" t="inlineStr"/>
+      <c r="L204" s="9" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
@@ -12034,6 +12766,7 @@
         </is>
       </c>
       <c r="K205" s="9" t="inlineStr"/>
+      <c r="L205" s="9" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="9" t="inlineStr">
@@ -12083,6 +12816,7 @@
         </is>
       </c>
       <c r="K206" s="9" t="inlineStr"/>
+      <c r="L206" s="9" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
@@ -12132,6 +12866,7 @@
         </is>
       </c>
       <c r="K207" s="9" t="inlineStr"/>
+      <c r="L207" s="9" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="9" t="inlineStr">
@@ -12181,6 +12916,7 @@
         </is>
       </c>
       <c r="K208" s="9" t="inlineStr"/>
+      <c r="L208" s="9" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
@@ -12230,6 +12966,7 @@
         </is>
       </c>
       <c r="K209" s="9" t="inlineStr"/>
+      <c r="L209" s="9" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="9" t="inlineStr">
@@ -12279,6 +13016,7 @@
         </is>
       </c>
       <c r="K210" s="9" t="inlineStr"/>
+      <c r="L210" s="9" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
@@ -12328,6 +13066,7 @@
         </is>
       </c>
       <c r="K211" s="9" t="inlineStr"/>
+      <c r="L211" s="9" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
@@ -12377,6 +13116,7 @@
         </is>
       </c>
       <c r="K212" s="9" t="inlineStr"/>
+      <c r="L212" s="9" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="9" t="inlineStr">
@@ -12430,6 +13170,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L213" s="9" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="9" t="inlineStr">
@@ -12479,6 +13220,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L214" s="9" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
@@ -12528,6 +13270,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L215" s="9" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="9" t="inlineStr">
@@ -12577,6 +13320,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L216" s="9" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
@@ -12626,6 +13370,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L217" s="9" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="9" t="inlineStr">
@@ -12675,6 +13420,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L218" s="9" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="9" t="inlineStr">
@@ -12724,6 +13470,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L219" s="9" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="9" t="inlineStr">
@@ -12773,6 +13520,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L220" s="9" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
@@ -12826,6 +13574,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L221" s="9" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="9" t="inlineStr">
@@ -12875,6 +13624,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L222" s="9" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="9" t="inlineStr">
@@ -12924,6 +13674,7 @@
           <t>Accepted</t>
         </is>
       </c>
+      <c r="L223" s="9" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
@@ -12977,6 +13728,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L224" s="9" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="9" t="inlineStr">
@@ -13030,6 +13782,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L225" s="9" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="9" t="inlineStr">
@@ -13083,6 +13836,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L226" s="9" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="9" t="inlineStr">
@@ -13136,6 +13890,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L227" s="9" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="9" t="inlineStr">
@@ -13176,7 +13931,7 @@
       <c r="H228" s="9" t="inlineStr"/>
       <c r="I228" s="9" t="inlineStr">
         <is>
-          <t>Legacy checked: no bug. The source allocation uses energy-balance data (row 894) and the energy CH4 calibration (row 7562) uses the first two years and applies the factor from the third (it reads only earlier years). The prototype calibrated on GHGYear (2024) in every year (its own design) and now reads stored scenario-1 values; the fiscal space uses the stored scenario-1 activity (I47).</t>
+          <t>Legacy checked: no bug. The source allocation uses energy-balance data (row 894) and the energy CH4 calibration (row 7548) uses the first two years and applies the factor from the third (it reads only earlier years). The prototype calibrated on GHGYear (2024) in every year (its own design) and now reads stored scenario-1 values; the fiscal space uses the stored scenario-1 activity (I47).</t>
         </is>
       </c>
       <c r="J228" s="9" t="inlineStr">
@@ -13189,6 +13944,7 @@
           <t>Resolved</t>
         </is>
       </c>
+      <c r="L228" s="9" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="9" t="inlineStr">
@@ -13242,6 +13998,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L229" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="9" t="inlineStr">
@@ -13295,6 +14056,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L230" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="9" t="inlineStr">
@@ -13348,6 +14114,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L231" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="9" t="inlineStr">
@@ -13401,6 +14172,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L232" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="9" t="inlineStr">
@@ -13454,6 +14230,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L233" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="9" t="inlineStr">
@@ -13507,6 +14288,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L234" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="9" t="inlineStr">
@@ -13560,6 +14346,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L235" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="9" t="inlineStr">
@@ -13613,6 +14404,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L236" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="9" t="inlineStr">
@@ -13666,6 +14462,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L237" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="9" t="inlineStr">
@@ -13719,6 +14520,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L238" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="9" t="inlineStr">
@@ -13772,6 +14578,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L239" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="9" t="inlineStr">
@@ -13825,6 +14636,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L240" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="9" t="inlineStr">
@@ -13878,6 +14694,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L241" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="9" t="inlineStr">
@@ -13931,6 +14752,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L242" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="9" t="inlineStr">
@@ -13984,6 +14810,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L243" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="9" t="inlineStr">
@@ -14037,6 +14868,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L244" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
@@ -14090,6 +14926,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L245" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="9" t="inlineStr">
@@ -14143,6 +14984,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L246" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="9" t="inlineStr">
@@ -14196,6 +15042,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L247" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="9" t="inlineStr">
@@ -14249,6 +15100,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L248" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="9" t="inlineStr">
@@ -14302,6 +15158,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L249" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="9" t="inlineStr">
@@ -14355,6 +15216,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L250" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="9" t="inlineStr">
@@ -14408,6 +15274,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L251" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="9" t="inlineStr">
@@ -14461,6 +15332,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L252" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
@@ -14514,6 +15390,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L253" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="9" t="inlineStr">
@@ -14567,6 +15448,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L254" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="9" t="inlineStr">
@@ -14620,6 +15506,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L255" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="9" t="inlineStr">
@@ -14673,6 +15564,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L256" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="9" t="inlineStr">
@@ -14726,6 +15622,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L257" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="9" t="inlineStr">
@@ -14779,6 +15680,11 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L258" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="9" t="inlineStr">
@@ -14830,6 +15736,11 @@
       <c r="K259" s="9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="L259" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -14877,6 +15788,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L260" s="9" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
@@ -14922,6 +15834,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L261" s="9" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="9" t="inlineStr">
@@ -14967,6 +15880,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L262" s="9" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="9" t="inlineStr">
@@ -15012,6 +15926,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L263" s="9" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="9" t="inlineStr">
@@ -15057,6 +15972,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L264" s="9" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="9" t="inlineStr">
@@ -15102,6 +16018,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L265" s="9" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="9" t="inlineStr">
@@ -15147,6 +16064,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L266" s="9" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="9" t="inlineStr">
@@ -15192,6 +16110,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L267" s="9" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="9" t="inlineStr">
@@ -15237,6 +16156,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L268" s="9" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="9" t="inlineStr">
@@ -15282,6 +16202,7 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="L269" s="9" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="9" t="inlineStr">
@@ -15331,6 +16252,7 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L270" s="9" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="9" t="inlineStr">
@@ -15380,6 +16302,7 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L271" s="9" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="9" t="inlineStr">
@@ -15429,6 +16352,7 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L272" s="9" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="9" t="inlineStr">
@@ -15478,6 +16402,7 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L273" s="9" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="9" t="inlineStr">
@@ -15527,6 +16452,7 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L274" s="9" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="9" t="inlineStr">
@@ -15576,6 +16502,7 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L275" s="9" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="9" t="inlineStr">
@@ -15625,6 +16552,7 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L276" s="9" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="9" t="inlineStr">
@@ -15674,6 +16602,7 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L277" s="9" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="9" t="inlineStr">
@@ -15723,6 +16652,7 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L278" s="9" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="9" t="inlineStr">
@@ -15772,6 +16702,7 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L279" s="9" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="9" t="inlineStr">
@@ -15821,6 +16752,7 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L280" s="9" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="9" t="inlineStr">
@@ -15870,6 +16802,7 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L281" s="9" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="9" t="inlineStr">
@@ -15919,6 +16852,7 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L282" s="9" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="9" t="inlineStr">
@@ -15968,9 +16902,10 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L283" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K283"/>
+  <autoFilter ref="A3:L283"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/excel_ai/CPAT-AI_BugsAndIssues_latest.xlsx
+++ b/excel_ai/CPAT-AI_BugsAndIssues_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUGSandISSUES" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BUGSandISSUES'!$A$3:$L$283</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BUGSandISSUES'!$A$3:$L$284</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -505,7 +505,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BUGSandISSUES: CPAT-AI-Mitigation-Prototype v8.2 against legacy CPAT</t>
+          <t>BUGSandISSUES: CPAT-AI-Mitigation-Prototype v8.3 against legacy CPAT</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +538,7 @@
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Source: BUGS.md and ISSUES.md (generated from issues_register.py). Not included: potential upgrades (U), and bugs found and fixed in the prototype during development (M); both are in the Word register CPAT-AI_BugsAndIssues_latest.docx. Details and effects of the legacy bugs: LegacyBugFixes.md. Column "Status in legacy 465": the legacy bugs in the latest CPAT file (CPAT 1.0pre_465), where the CPAT team fixed part of them (checked cell by cell); cell references are 465 rows.</t>
+          <t>Source: the register (issues_register.py; the same content as BUGS.md and ISSUES.md). Not included: potential upgrades (U), and bugs found and fixed in the prototype during development (M); both are in the Word register CPAT-AI_BugsAndIssues_latest.docx. Details and effects of the legacy bugs: LegacyBugFixes.md. Column "Status in legacy 465": the legacy bugs in the latest CPAT file (CPAT 1.0pre_465), where the CPAT team fixed part of them (checked cell by cell); cell references are 465 rows.</t>
         </is>
       </c>
     </row>
@@ -586,13 +586,13 @@
         <v>0</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -787,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L283"/>
+  <dimension ref="A1:L284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -807,7 +807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bugs and issues of legacy CPAT and whether CPAT-AI-Mitigation-Prototype v8.2 replicates them</t>
+          <t>Bugs and issues of legacy CPAT and whether CPAT-AI-Mitigation-Prototype v8.3 replicates them</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9009,22 +9009,22 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>I6</t>
+          <t>L134</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Issue (departure from legacy)</t>
+          <t>Legacy bug</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>Electricity subsidy gap is signed</t>
+          <t>Price-increase units: other oil products "$/bbn", default "$/liter" for other oil products and biomass</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
@@ -9034,36 +9034,44 @@
       </c>
       <c r="F135" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy by decision</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G135" s="9" t="inlineStr">
         <is>
-          <t>Subsidies are negative (v2.4): the gap is negative when the tariff is below the modelled supply cost and positive when it is above; fuel subsidies count the negative part of the existing taxes only.</t>
-        </is>
-      </c>
-      <c r="H135" s="9" t="inlineStr"/>
+          <t>The unit labels of the price-increase inputs read "$/bbn" (for $/bbl) for other oil products, and the default column says "$/liter" for other oil products and biomass, whose prices are per barrel and per GJ. No formula reads the labels (Mitigation rows 168-180 use the amounts in G and H only), so no value changes; a user typing an increase per liter for these fuels gets a wrong price path. Found by the tracker leads (2026-10-23).</t>
+        </is>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>Labels only: no value changes; a user may type an increase in the wrong unit. prototype: Fixed (v8.3): the prototype's ScenarioDefinition rows 182-183 read $/bbl and $/GJ, defaults included.</t>
+        </is>
+      </c>
       <c r="I135" s="9" t="inlineStr">
         <is>
-          <t>Exception by decision (v2.4): sign convention only, values as legacy.</t>
+          <t>Label the price-increase units USD/bbl (other oil products) and USD/GJ (biomass) in columns E and G of MTInputs rows 182-183.</t>
         </is>
       </c>
       <c r="J135" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Power 3.9</t>
+          <t>MTInputs rows 182-183 (columns E and G); Mitigation I177, I180</t>
         </is>
       </c>
       <c r="K135" s="9" t="inlineStr">
         <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="L135" s="9" t="inlineStr"/>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="L135" s="9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>I14</t>
+          <t>I6</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
@@ -9073,12 +9081,12 @@
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Distance to the legacy cached baseline</t>
+          <t>Electricity subsidy gap is signed</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
@@ -9093,18 +9101,18 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>The prototype baseline differs from the cached legacy run, mainly through the fuel-use shock (I22), jet fuel (I19), the electricity price data (I20) and the fixed legacy bugs.</t>
+          <t>Subsidies are negative (v2.4): the gap is negative when the tariff is below the modelled supply cost and positive when it is above; fuel subsidies count the negative part of the existing taxes only.</t>
         </is>
       </c>
       <c r="H136" s="9" t="inlineStr"/>
       <c r="I136" s="9" t="inlineStr">
         <is>
-          <t>v5.7: I25 closed (v5.6); the remaining distance is the documented data and bug-fix differences (legacy_comparison, LegacyDiff).</t>
+          <t>Exception by decision (v2.4): sign convention only, values as legacy.</t>
         </is>
       </c>
       <c r="J136" s="9" t="inlineStr">
         <is>
-          <t>legacy_comparison_v6_4.md</t>
+          <t>Methods, chapter Power 3.9</t>
         </is>
       </c>
       <c r="K136" s="9" t="inlineStr">
@@ -9117,7 +9125,7 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>I20</t>
+          <t>I14</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
@@ -9132,7 +9140,7 @@
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>Electricity price data differ from legacy</t>
+          <t>Distance to the legacy cached baseline</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
@@ -9147,18 +9155,18 @@
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>The corrected Egypt block supplied by the user (2026-10-09) gives residential 0.054, 0.048, 0.043 $/kWh nominal for 2022-2024; the legacy vintage has 0.097 in 2022. Electricity prices, power demand and the subsidy gap differ from legacy.</t>
+          <t>The prototype baseline differs from the cached legacy run, mainly through the fuel-use shock (I22), jet fuel (I19), the electricity price data (I20) and the fixed legacy bugs.</t>
         </is>
       </c>
       <c r="H137" s="9" t="inlineStr"/>
       <c r="I137" s="9" t="inlineStr">
         <is>
-          <t>Exception by user decision (corrected data, 2026-10-09).</t>
+          <t>v5.7: I25 closed (v5.6); the remaining distance is the documented data and bug-fix differences (legacy_comparison, LegacyDiff).</t>
         </is>
       </c>
       <c r="J137" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Power; LegacyDiff</t>
+          <t>legacy_comparison_v6_4.md</t>
         </is>
       </c>
       <c r="K137" s="9" t="inlineStr">
@@ -9171,7 +9179,7 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>I47</t>
+          <t>I20</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
@@ -9181,12 +9189,12 @@
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>GDP effects: methane fee in the fiscal space on stored scenario-1 gas and biomass activity</t>
+          <t>Electricity price data differ from legacy</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
@@ -9201,18 +9209,18 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>Legacy counts the methane fee in total revenue (row 8010) and so in the fiscal space, on the scenario's own activity. The prototype counts it too, but with the stored scenario-1 activity of downstream gas and biomass use (v6.2, user decision 2026-10-20: no vulnerability to circular references through the GDP feedback). Differs from legacy only when a policy changes gas or biomass use and a methane fee applies. None for Egypt (no methane fee in the scenarios).</t>
+          <t>The corrected Egypt block supplied by the user (2026-10-09) gives residential 0.054, 0.048, 0.043 $/kWh nominal for 2022-2024; the legacy vintage has 0.097 in 2022. Electricity prices, power demand and the subsidy gap differ from legacy.</t>
         </is>
       </c>
       <c r="H138" s="9" t="inlineStr"/>
       <c r="I138" s="9" t="inlineStr">
         <is>
-          <t>v6.2 (user 2026-10-20: as close to legacy as possible with no vulnerability to circular references): the fee revenue is in the fiscal space (fis.rev + ch4.revf). ch4.revf is the legacy fee revenue with the stored scenario-1 activity of downstream gas and biomass use (sheet BaselineCO2 rows dg, bm, refreshed by the build; check row ch4bs.chk = 0 in scenario 1); fee, abatement and the other sources are the scenario's own. So the fiscal space reads no fuel use, and no later change to the power or demand blocks can close a loop through it. Reported revenue (rmf, rtot, 12e) keeps the own activity. The v6.0-v6.1 loop came from price-block average ranges that ran into section 11 (fixed v6.2), not from the L67 fix. No effect in the shipped scenarios (no methane fee).</t>
+          <t>Exception by user decision (corrected data, 2026-10-09).</t>
         </is>
       </c>
       <c r="J138" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Macro and results; LegacyDiff 55</t>
+          <t>Methods, chapter Power; LegacyDiff</t>
         </is>
       </c>
       <c r="K138" s="9" t="inlineStr">
@@ -9225,7 +9233,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>I52</t>
+          <t>I47</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
@@ -9240,7 +9248,7 @@
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>ETS inclusion: construction, fuel transformation and other energy use follow the buildings flag</t>
+          <t>GDP effects: methane fee in the fiscal space on stored scenario-1 gas and biomass activity</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
@@ -9255,18 +9263,18 @@
       </c>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>Manual inputs V11:X11 read Dashboard Q30 (buildings) for construction, fuel transformation and other energy use: a grouping choice. The prototype types ETS coverage per scenario (MTInputs rows 99-115).</t>
+          <t>Legacy counts the methane fee in total revenue (row 8010) and so in the fiscal space, on the scenario's own activity. The prototype counts it too, but with the stored scenario-1 activity of downstream gas and biomass use (v6.2, user decision 2026-10-20: no vulnerability to circular references through the GDP feedback). Differs from legacy only when a policy changes gas or biomass use and a methane fee applies. None for Egypt (no methane fee in the scenarios).</t>
         </is>
       </c>
       <c r="H139" s="9" t="inlineStr"/>
       <c r="I139" s="9" t="inlineStr">
         <is>
-          <t>Conditional: nothing to replicate now (the prototype types ETS coverage per sector). Decided (user 2026-10-19): replicate the legacy grouping when ETS coverage by Dashboard groups is built.</t>
+          <t>v6.2 (user 2026-10-20: as close to legacy as possible with no vulnerability to circular references): the fee revenue is in the fiscal space (fis.rev + ch4.revf). ch4.revf is the legacy fee revenue with the stored scenario-1 activity of downstream gas and biomass use (sheet BaselineCO2 rows dg, bm, refreshed by the build; check row ch4bs.chk = 0 in scenario 1); fee, abatement and the other sources are the scenario's own. So the fiscal space reads no fuel use, and no later change to the power or demand blocks can close a loop through it. Reported revenue (rmf, rtot, 12e) keeps the own activity. The v6.0-v6.1 loop came from price-block average ranges that ran into section 11 (fixed v6.2), not from the L67 fix. No effect in the shipped scenarios (no methane fee).</t>
         </is>
       </c>
       <c r="J139" s="9" t="inlineStr">
         <is>
-          <t>Manual inputs survey (v5.2)</t>
+          <t>Methods, chapter Macro and results; LegacyDiff 55</t>
         </is>
       </c>
       <c r="K139" s="9" t="inlineStr">
@@ -9279,7 +9287,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>I53</t>
+          <t>I52</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
@@ -9294,7 +9302,7 @@
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>Manual domestic prices switch on only with a 2021 value</t>
+          <t>ETS inclusion: construction, fuel transformation and other energy use follow the buildings flag</t>
         </is>
       </c>
       <c r="E140" s="10" t="inlineStr">
@@ -9309,13 +9317,13 @@
       </c>
       <c r="G140" s="9" t="inlineStr">
         <is>
-          <t>A manual price row is "Manual" only if its 2021 value is filled (Mitigation F765:F829 test K$764); years without a value fall back to the data year by year. Could be a bug (intent unclear). The prototype does not build manual domestic prices (block placed, not read).</t>
+          <t>Manual inputs V11:X11 read Dashboard Q30 (buildings) for construction, fuel transformation and other energy use: a grouping choice. The prototype types ETS coverage per scenario (MTInputs rows 99-115).</t>
         </is>
       </c>
       <c r="H140" s="9" t="inlineStr"/>
       <c r="I140" s="9" t="inlineStr">
         <is>
-          <t>Conditional: nothing to replicate now (the prototype does not build manual domestic prices). Decided (user 2026-10-19): an issue; replicate legacy when manual domestic prices are built; ask the CPAT team about the intent.</t>
+          <t>Conditional: nothing to replicate now (the prototype types ETS coverage per sector). Decided (user 2026-10-19): replicate the legacy grouping when ETS coverage by Dashboard groups is built.</t>
         </is>
       </c>
       <c r="J140" s="9" t="inlineStr">
@@ -9333,7 +9341,7 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>I58</t>
+          <t>I53</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
@@ -9348,7 +9356,7 @@
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>Power switches tested for the exact "Yes"</t>
+          <t>Manual domestic prices switch on only with a 2021 value</t>
         </is>
       </c>
       <c r="E141" s="10" t="inlineStr">
@@ -9358,28 +9366,28 @@
       </c>
       <c r="F141" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy; queued to replicate</t>
+          <t>Departs from legacy by decision</t>
         </is>
       </c>
       <c r="G141" s="9" t="inlineStr">
         <is>
-          <t>PowerRebates (G261), RenewableSubsidyHydro (row 3150) and AdditionalExcise (F201) count a starred "Yes*" as No. The prototype accepts Yes or Yes* (LEFT 3), as I54 and the other prototype switches.</t>
+          <t>A manual price row is "Manual" only if its 2021 value is filled (Mitigation F765:F829 test K$764); years without a value fall back to the data year by year. Could be a bug (intent unclear). The prototype does not build manual domestic prices (block placed, not read).</t>
         </is>
       </c>
       <c r="H141" s="9" t="inlineStr"/>
       <c r="I141" s="9" t="inlineStr">
         <is>
-          <t>Reclassified as legacy bug L113 (user 2026-10-19).</t>
+          <t>Conditional: nothing to replicate now (the prototype does not build manual domestic prices). Decided (user 2026-10-19): an issue; replicate legacy when manual domestic prices are built; ask the CPAT team about the intent.</t>
         </is>
       </c>
       <c r="J141" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Power; LegacyDiff 77</t>
+          <t>Manual inputs survey (v5.2)</t>
         </is>
       </c>
       <c r="K141" s="9" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="L141" s="9" t="inlineStr"/>
@@ -9387,7 +9395,7 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>I64</t>
+          <t>I58</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
@@ -9397,12 +9405,12 @@
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>Combustion emission factor paths missing (GAINS, proprietary)</t>
+          <t>Power switches tested for the exact "Yes"</t>
         </is>
       </c>
       <c r="E142" s="10" t="inlineStr">
@@ -9417,23 +9425,23 @@
       </c>
       <c r="G142" s="9" t="inlineStr">
         <is>
-          <t>Legacy reads GAINS combustion factor paths by year; in the NoPropData file they are zero (proprietary). The prototype uses the GAINS base and final factors (EF_PM), linear to EFEndYear (2039), flat after (LegacyDiff LD47). Combustion CH4 is scaled to the inventory by the calibration. Data issue: no legacy formula is wrong.</t>
+          <t>PowerRebates (G261), RenewableSubsidyHydro (row 3150) and AdditionalExcise (F201) count a starred "Yes*" as No. The prototype accepts Yes or Yes* (LEFT 3), as I54 and the other prototype switches.</t>
         </is>
       </c>
       <c r="H142" s="9" t="inlineStr"/>
       <c r="I142" s="9" t="inlineStr">
         <is>
-          <t>prototype fill kept (user 2026-10-19). Data request: a legacy file with the GAINS combustion factor paths (high priority, user 2026-10-19).</t>
+          <t>Reclassified as legacy bug L113 (user 2026-10-19).</t>
         </is>
       </c>
       <c r="J142" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Emissions; LegacyDiff</t>
+          <t>Methods, chapter Power; LegacyDiff 77</t>
         </is>
       </c>
       <c r="K142" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="L142" s="9" t="inlineStr"/>
@@ -9441,7 +9449,7 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>I65</t>
+          <t>I64</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
@@ -9456,7 +9464,7 @@
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>Blank VAT cells in the IMF price dataset</t>
+          <t>Combustion emission factor paths missing (GAINS, proprietary)</t>
         </is>
       </c>
       <c r="E143" s="10" t="inlineStr">
@@ -9471,18 +9479,18 @@
       </c>
       <c r="G143" s="9" t="inlineStr">
         <is>
-          <t>Some VAT cells of the IMF price dataset are blank; legacy then uses 0. The prototype fills blank cells with the general VAT rate (VAT_WEO) for residential coal and gas and all-sector oil products, 0 for power, industry and biomass (LegacyDiff LD3). None for Egypt since v0.14 (corrected data fill every VAT cell). Data issue.</t>
+          <t>Legacy reads GAINS combustion factor paths by year; in the NoPropData file they are zero (proprietary). The prototype uses the GAINS base and final factors (EF_PM), linear to EFEndYear (2039), flat after (LegacyDiff LD47). Combustion CH4 is scaled to the inventory by the calibration. Data issue: no legacy formula is wrong.</t>
         </is>
       </c>
       <c r="H143" s="9" t="inlineStr"/>
       <c r="I143" s="9" t="inlineStr">
         <is>
-          <t>prototype fill kept (user 2026-10-19). Data request: raise the blank VAT cells with the data team (high priority, user 2026-10-19); the prototype fill stays until then.</t>
+          <t>prototype fill kept (user 2026-10-19). Data request: a legacy file with the GAINS combustion factor paths (high priority, user 2026-10-19).</t>
         </is>
       </c>
       <c r="J143" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Prices; LegacyDiff</t>
+          <t>Methods, chapter Emissions; LegacyDiff</t>
         </is>
       </c>
       <c r="K143" s="9" t="inlineStr">
@@ -9495,7 +9503,7 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>I67</t>
+          <t>I65</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
@@ -9505,12 +9513,12 @@
       </c>
       <c r="C144" s="9" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>Intensity NDC: China CO2 hard-coded</t>
+          <t>Blank VAT cells in the IMF price dataset</t>
         </is>
       </c>
       <c r="E144" s="10" t="inlineStr">
@@ -9520,28 +9528,28 @@
       </c>
       <c r="F144" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy by decision</t>
+          <t>Departs from legacy; queued to replicate</t>
         </is>
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>Legacy row 18449 H uses 5665 (Mt CO2) for China instead of the data (row 889). The prototype reads sheet GHGHist (or the model where the reference year is modelled); China's latest NDC is a Historical target (ref 2024, modelled), so the value is not used.</t>
+          <t>Some VAT cells of the IMF price dataset are blank; legacy then uses 0. The prototype fills blank cells with the general VAT rate (VAT_WEO) for residential coal and gas and all-sector oil products, 0 for power, industry and biomass (LegacyDiff LD3). None for Egypt since v0.14 (corrected data fill every VAT cell). Data issue.</t>
         </is>
       </c>
       <c r="H144" s="9" t="inlineStr"/>
       <c r="I144" s="9" t="inlineStr">
         <is>
-          <t>v5.7: no hard-coded value; data or model (departure by design, user rule: data not typed).</t>
+          <t>prototype fill kept (user 2026-10-19). Data request: raise the blank VAT cells with the data team (high priority, user 2026-10-19); the prototype fill stays until then.</t>
         </is>
       </c>
       <c r="J144" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Emissions</t>
+          <t>Methods, chapter Prices; LegacyDiff</t>
         </is>
       </c>
       <c r="K144" s="9" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L144" s="9" t="inlineStr"/>
@@ -9549,7 +9557,7 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>I69</t>
+          <t>I67</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
@@ -9559,12 +9567,12 @@
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>Air-pollution co-benefits (health, mortality) not built</t>
+          <t>Intensity NDC: China CO2 hard-coded</t>
         </is>
       </c>
       <c r="E145" s="10" t="inlineStr">
@@ -9574,28 +9582,28 @@
       </c>
       <c r="F145" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: dropped by the user (v6.1)</t>
+          <t>Departs from legacy by decision</t>
         </is>
       </c>
       <c r="G145" s="9" t="inlineStr">
         <is>
-          <t>Legacy computes air-pollution mortality and its valuation from fuel use (sheets AP and the Mitigation co-benefit rows). The prototype keeps local pollutant emissions (section 15) only. Dropped by the user (2026-10-20); the plan stays for reference.</t>
+          <t>Legacy row 18449 H uses 5665 (Mt CO2) for China instead of the data (row 889). The prototype reads sheet GHGHist (or the model where the reference year is modelled); China's latest NDC is a Historical target (ref 2024, modelled), so the value is not used.</t>
         </is>
       </c>
       <c r="H145" s="9" t="inlineStr"/>
       <c r="I145" s="9" t="inlineStr">
         <is>
-          <t>Module dropped by the user (2026-10-20); plan kept for reference.</t>
+          <t>v5.7: no hard-coded value; data or model (departure by design, user rule: data not typed).</t>
         </is>
       </c>
       <c r="J145" s="9" t="inlineStr">
         <is>
-          <t>excel_ai/plans/Air_pollution.md</t>
+          <t>Methods, chapter Emissions</t>
         </is>
       </c>
       <c r="K145" s="9" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="L145" s="9" t="inlineStr"/>
@@ -9603,7 +9611,7 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>I70</t>
+          <t>I69</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
@@ -9618,7 +9626,7 @@
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>Transport externalities (congestion, accidents, road damage) not built</t>
+          <t>Air-pollution co-benefits (health, mortality) not built</t>
         </is>
       </c>
       <c r="E146" s="10" t="inlineStr">
@@ -9633,7 +9641,7 @@
       </c>
       <c r="G146" s="9" t="inlineStr">
         <is>
-          <t>Legacy values the transport externalities of road fuel use and vehicle-km. Not in the prototype. Dropped by the user (2026-10-20); the plan stays for reference.</t>
+          <t>Legacy computes air-pollution mortality and its valuation from fuel use (sheets AP and the Mitigation co-benefit rows). The prototype keeps local pollutant emissions (section 15) only. Dropped by the user (2026-10-20); the plan stays for reference.</t>
         </is>
       </c>
       <c r="H146" s="9" t="inlineStr"/>
@@ -9644,7 +9652,7 @@
       </c>
       <c r="J146" s="9" t="inlineStr">
         <is>
-          <t>excel_ai/plans/Transport_cobenefits.md</t>
+          <t>excel_ai/plans/Air_pollution.md</t>
         </is>
       </c>
       <c r="K146" s="9" t="inlineStr">
@@ -9657,7 +9665,7 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>I75</t>
+          <t>I70</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
@@ -9667,12 +9675,12 @@
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>Legacy code inconsistencies (CPAT code protocol)</t>
+          <t>Transport externalities (congestion, accidents, road damage) not built</t>
         </is>
       </c>
       <c r="E147" s="10" t="inlineStr">
@@ -9682,28 +9690,28 @@
       </c>
       <c r="F147" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy; queued to replicate</t>
+          <t>Departs from legacy: dropped by the user (v6.1)</t>
         </is>
       </c>
       <c r="G147" s="9" t="inlineStr">
         <is>
-          <t>Legacy codes do not follow one protocol: variable names differ by module (trevst vs stockcalc), slots differ in order (fuel.sector and sector.fuel), totals are written all or tot, model letters (.e, .a, .t) end some codes. The prototype follows the protocol from v7.2 (codes R0-R9: legacy variable names, sector before fuel, tot for totals, no model letters); legacy codes that differ are aliases in the crosswalk.</t>
+          <t>Legacy values the transport externalities of road fuel use and vehicle-km. Not in the prototype. Dropped by the user (2026-10-20); the plan stays for reference.</t>
         </is>
       </c>
       <c r="H147" s="9" t="inlineStr"/>
       <c r="I147" s="9" t="inlineStr">
         <is>
-          <t>v7.2 (codes R0-R9): the prototype codes follow the protocol; legacy codes that differ are aliases (crosswalk, LiveOutputs alias column). Open review rows: excel_ai/plans/TODO_Codes.md.</t>
+          <t>Module dropped by the user (2026-10-20); plan kept for reference.</t>
         </is>
       </c>
       <c r="J147" s="9" t="inlineStr">
         <is>
-          <t>Codes_Remediation_Plan_v7_1.md; codes_crosswalk_v7_1.csv; code_renames_v7_2.csv</t>
+          <t>excel_ai/plans/Transport_cobenefits.md</t>
         </is>
       </c>
       <c r="K147" s="9" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="L147" s="9" t="inlineStr"/>
@@ -9711,53 +9719,53 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>I75</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>Issue (replicated)</t>
+          <t>Issue (departure from legacy)</t>
         </is>
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>Price vintage: data prices end in 2022, as legacy</t>
-        </is>
-      </c>
-      <c r="E148" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Legacy code inconsistencies (CPAT code protocol)</t>
+        </is>
+      </c>
+      <c r="E148" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr">
         <is>
-          <t>Kept as legacy, tracked</t>
+          <t>Departs from legacy; queued to replicate</t>
         </is>
       </c>
       <c r="G148" s="9" t="inlineStr">
         <is>
-          <t>The last historical price year is 2022 (Settings C10, v3.7), as legacy, whose prices stay near their 2022 USD level. The IMF dataset also holds 2023-2024, when Egypt prices fell sharply in USD after the devaluation (gasoline 0.60 to 0.34 $/l); with C10 = 2024, fuel use and electricity demand jump in 2023 and the gap to legacy fuel use grows from 17% to 46%. Demand responds to real USD prices, as legacy.</t>
+          <t>Legacy codes do not follow one protocol: variable names differ by module (trevst vs stockcalc), slots differ in order (fuel.sector and sector.fuel), totals are written all or tot, model letters (.e, .a, .t) end some codes. The prototype follows the protocol from v7.2 (codes R0-R9: legacy variable names, sector before fuel, tot for totals, no model letters); legacy codes that differ are aliases in the crosswalk.</t>
         </is>
       </c>
       <c r="H148" s="9" t="inlineStr"/>
       <c r="I148" s="9" t="inlineStr">
         <is>
-          <t>Decided 2026-10-15: 2022 as legacy.</t>
+          <t>v7.2 (codes R0-R9): the prototype codes follow the protocol; legacy codes that differ are aliases (crosswalk, LiveOutputs alias column). Open review rows: excel_ai/plans/TODO_Codes.md.</t>
         </is>
       </c>
       <c r="J148" s="9" t="inlineStr">
         <is>
-          <t>legacy_comparison_v6_4.md; Methods, chapter Prices A7</t>
+          <t>Codes_Remediation_Plan_v7_1.md; codes_crosswalk_v7_1.csv; code_renames_v7_2.csv</t>
         </is>
       </c>
       <c r="K148" s="9" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="L148" s="9" t="inlineStr"/>
@@ -9765,7 +9773,7 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>I17</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
@@ -9780,7 +9788,7 @@
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>Egypt GHG inventory: energy CH4 breaks after 2021</t>
+          <t>Price vintage: data prices end in 2022, as legacy</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
@@ -9795,18 +9803,18 @@
       </c>
       <c r="G149" s="9" t="inlineStr">
         <is>
-          <t>Sheet GHGs (legacy data) gives energy CH4 of 21.9 Mt CO2e in 2021 and 1.9-2.0 in 2022-2024, while the fugitive-emissions memo alone is 20.3 in 2023: the years come from different sources. Section 14 calibrates to the last inventory year (2024, as legacy), so energy CH4 and the fuel-supply methane may be understated by about 19 Mt CO2e.</t>
+          <t>The last historical price year is 2022 (Settings C10, v3.7), as legacy, whose prices stay near their 2022 USD level. The IMF dataset also holds 2023-2024, when Egypt prices fell sharply in USD after the devaluation (gasoline 0.60 to 0.34 $/l); with C10 = 2024, fuel use and electricity demand jump in 2023 and the gap to legacy fuel use grows from 17% to 46%. Demand responds to real USD prices, as legacy.</t>
         </is>
       </c>
       <c r="H149" s="9" t="inlineStr"/>
       <c r="I149" s="9" t="inlineStr">
         <is>
-          <t>Decided 2026-10-15: calibrate to 2024 as legacy.</t>
+          <t>Decided 2026-10-15: 2022 as legacy.</t>
         </is>
       </c>
       <c r="J149" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Emissions (Data); CAVEATS v2.8</t>
+          <t>legacy_comparison_v6_4.md; Methods, chapter Prices A7</t>
         </is>
       </c>
       <c r="K149" s="9" t="inlineStr">
@@ -9819,7 +9827,7 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>I18</t>
+          <t>I17</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
@@ -9829,12 +9837,12 @@
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>GHG totals use energy CO2 without inventory adjustment (resolved v3.2)</t>
+          <t>Egypt GHG inventory: energy CH4 breaks after 2021</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
@@ -9849,23 +9857,23 @@
       </c>
       <c r="G150" s="9" t="inlineStr">
         <is>
-          <t>Energy CO2 in section 14 was section 13 (IIASA EFs, no adjustment to the inventory) plus flaring: 225 Mt in 2022 against 252 Mt in the inventory. v3.2: every CO2 EF is calibrated to the inventory of GHGYear (Settings EFCalib), so 2024 matches; 2022 stays below the 2022 inventory because of the 2021-2022 inventory break (I17).</t>
+          <t>Sheet GHGs (legacy data) gives energy CH4 of 21.9 Mt CO2e in 2021 and 1.9-2.0 in 2022-2024, while the fugitive-emissions memo alone is 20.3 in 2023: the years come from different sources. Section 14 calibrates to the last inventory year (2024, as legacy), so energy CH4 and the fuel-supply methane may be understated by about 19 Mt CO2e.</t>
         </is>
       </c>
       <c r="H150" s="9" t="inlineStr"/>
       <c r="I150" s="9" t="inlineStr">
         <is>
-          <t>v3.2 (switch, off by default as legacy since v3.4).</t>
+          <t>Decided 2026-10-15: calibrate to 2024 as legacy.</t>
         </is>
       </c>
       <c r="J150" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Emissions; CAVEATS v3.2</t>
+          <t>Methods, chapter Emissions (Data); CAVEATS v2.8</t>
         </is>
       </c>
       <c r="K150" s="9" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="L150" s="9" t="inlineStr"/>
@@ -9873,7 +9881,7 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>I19</t>
+          <t>I18</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
@@ -9883,12 +9891,12 @@
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>Jet fuel (replicated v3.11)</t>
+          <t>GHG totals use energy CO2 without inventory adjustment (resolved v3.2)</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
@@ -9903,18 +9911,18 @@
       </c>
       <c r="G151" s="9" t="inlineStr">
         <is>
-          <t>Legacy domestic aviation burns jet fuel (707 ktoe in 2022). Since v3.11 the prototype has the fuel jfu (aviation only, kerosene price build-up, legacy EF row 1011, kerosene carbon-tax coverage switch); the legacy comparison includes it.</t>
+          <t>Energy CO2 in section 14 was section 13 (IIASA EFs, no adjustment to the inventory) plus flaring: 225 Mt in 2022 against 252 Mt in the inventory. v3.2: every CO2 EF is calibrated to the inventory of GHGYear (Settings EFCalib), so 2024 matches; 2022 stays below the 2022 inventory because of the 2021-2022 inventory break (I17).</t>
         </is>
       </c>
       <c r="H151" s="9" t="inlineStr"/>
       <c r="I151" s="9" t="inlineStr">
         <is>
-          <t>v3.11.</t>
+          <t>v3.2 (switch, off by default as legacy since v3.4).</t>
         </is>
       </c>
       <c r="J151" s="9" t="inlineStr">
         <is>
-          <t>Reviews_and_Surveys.md (section Sector_Equations_Survey) D1; CAVEATS v3.11</t>
+          <t>Methods, chapter Emissions; CAVEATS v3.2</t>
         </is>
       </c>
       <c r="K151" s="9" t="inlineStr">
@@ -9927,7 +9935,7 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>I21</t>
+          <t>I19</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
@@ -9942,7 +9950,7 @@
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>ETS: one auctioned share for every sector (replicated v4.15)</t>
+          <t>Jet fuel (replicated v3.11)</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
@@ -9957,23 +9965,23 @@
       </c>
       <c r="G152" s="9" t="inlineStr">
         <is>
-          <t>Legacy allocates by one auctioned share path (MTInputs rows 90-92, default 0: everything allocated free), the same for every sector. The prototype had benchmarks by sector group typed on Constants (v1.02), so an MTInputs auctioned share had no effect; since v4.15 the benchmarks are 1 - the MTInputs share of the scenario (user 2026-10-18), as legacy. Benchmarks by sector (output-based) come later.</t>
+          <t>Legacy domestic aviation burns jet fuel (707 ktoe in 2022). Since v3.11 the prototype has the fuel jfu (aviation only, kerosene price build-up, legacy EF row 1011, kerosene carbon-tax coverage switch); the legacy comparison includes it.</t>
         </is>
       </c>
       <c r="H152" s="9" t="inlineStr"/>
       <c r="I152" s="9" t="inlineStr">
         <is>
-          <t>v4.15 (user 2026-10-18): benchmarks = 1 - the MTInputs auctioned share (rows 90-91, one share for all sectors, as legacy); benchmarks by sector later.</t>
+          <t>v3.11.</t>
         </is>
       </c>
       <c r="J152" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter ETS; Methods, chapter ETS; LegacyDiff</t>
+          <t>Reviews_and_Surveys.md (section Sector_Equations_Survey) D1; CAVEATS v3.11</t>
         </is>
       </c>
       <c r="K152" s="9" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="L152" s="9" t="inlineStr"/>
@@ -9981,7 +9989,7 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>I22</t>
+          <t>I21</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
@@ -9996,7 +10004,7 @@
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>Fuel-use shock of 2023-2024 (replicated v3.11)</t>
+          <t>ETS: one auctioned share for every sector (replicated v4.15)</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
@@ -10011,18 +10019,18 @@
       </c>
       <c r="G153" s="9" t="inlineStr">
         <is>
-          <t>Every legacy fuel row multiplies by (1 + shock), row 2439 = row 483 ("Covid factor"): -20.8% in 2023, +9.2% in 2024, so fuel use is 13.5% lower from 2024 on. Replicated in v3.11 for fuels (header row 11) and power demand, switch Settings C19 on. Open questions kept: the label "Covid factor" does not fit 2023, legacy documents the effect as "Small", and the source of the two values is unknown.</t>
+          <t>Legacy allocates by one auctioned share path (MTInputs rows 90-92, default 0: everything allocated free), the same for every sector. The prototype had benchmarks by sector group typed on Constants (v1.02), so an MTInputs auctioned share had no effect; since v4.15 the benchmarks are 1 - the MTInputs share of the scenario (user 2026-10-18), as legacy. Benchmarks by sector (output-based) come later.</t>
         </is>
       </c>
       <c r="H153" s="9" t="inlineStr"/>
       <c r="I153" s="9" t="inlineStr">
         <is>
-          <t>Replicated v3.11; source of the values to trace.</t>
+          <t>v4.15 (user 2026-10-18): benchmarks = 1 - the MTInputs auctioned share (rows 90-91, one share for all sectors, as legacy); benchmarks by sector later.</t>
         </is>
       </c>
       <c r="J153" s="9" t="inlineStr">
         <is>
-          <t>Reviews_and_Surveys.md (section Sector_Equations_Survey) D2; LegacyDiff</t>
+          <t>Methods, chapter ETS; Methods, chapter ETS; LegacyDiff</t>
         </is>
       </c>
       <c r="K153" s="9" t="inlineStr">
@@ -10035,7 +10043,7 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>I25</t>
+          <t>I22</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
@@ -10050,7 +10058,7 @@
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>Industrial process emissions below legacy, not explained</t>
+          <t>Fuel-use shock of 2023-2024 (replicated v3.11)</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
@@ -10065,23 +10073,23 @@
       </c>
       <c r="G154" s="9" t="inlineStr">
         <is>
-          <t>Both follow increases in industrial energy CO2, yet the prototype is 57.2 against 66.5 Mt CO2e in 2024 and 94.9 against 119.2 in 2040.</t>
+          <t>Every legacy fuel row multiplies by (1 + shock), row 2439 = row 483 ("Covid factor"): -20.8% in 2023, +9.2% in 2024, so fuel use is 13.5% lower from 2024 on. Replicated in v3.11 for fuels (header row 11) and power demand, switch Settings C19 on. Open questions kept: the label "Covid factor" does not fit 2023, legacy documents the effect as "Small", and the source of the two values is unknown.</t>
         </is>
       </c>
       <c r="H154" s="9" t="inlineStr"/>
       <c r="I154" s="9" t="inlineStr">
         <is>
-          <t>Traced (v5.6): legacy process emissions = 2023 inventory x the year-on-year growth of industrial energy CO2 (row 6576; 2024: +16.8%, the rebound after the 2023 demand shock, so 56.9 -&gt; 66.5). The prototype floored that growth at 0 (a departure: removed in v5.6, as legacy). The remaining gap is the industrial energy CO2 path, part of the fuel-use gap (I14).</t>
+          <t>Replicated v3.11; source of the values to trace.</t>
         </is>
       </c>
       <c r="J154" s="9" t="inlineStr">
         <is>
-          <t>legacy_comparison_v6_4.md; CAVEATS v2.8</t>
+          <t>Reviews_and_Surveys.md (section Sector_Equations_Survey) D2; LegacyDiff</t>
         </is>
       </c>
       <c r="K154" s="9" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="L154" s="9" t="inlineStr"/>
@@ -10089,7 +10097,7 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>I26</t>
+          <t>I25</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
@@ -10099,12 +10107,12 @@
       </c>
       <c r="C155" s="9" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>GHG defaults not yet checked against legacy</t>
+          <t>Industrial process emissions below legacy, not explained</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
@@ -10119,18 +10127,18 @@
       </c>
       <c r="G155" s="9" t="inlineStr">
         <is>
-          <t>Oil, gas and coal production held at the base year (fuel supply methane) and energy N2O moving with energy CO2 were applied as defaults in v2.8; their legacy counterparts are not yet checked.</t>
+          <t>Both follow increases in industrial energy CO2, yet the prototype is 57.2 against 66.5 Mt CO2e in 2024 and 94.9 against 119.2 in 2040.</t>
         </is>
       </c>
       <c r="H155" s="9" t="inlineStr"/>
       <c r="I155" s="9" t="inlineStr">
         <is>
-          <t>Checked (v5.6): energy N2O moves with energy CO2 as legacy (row 7549 = previous x CO2 ratio). Production for fuel-supply methane differs: now issue I66.</t>
+          <t>Traced (v5.6): legacy process emissions = 2023 inventory x the year-on-year growth of industrial energy CO2 (row 6576; 2024: +16.8%, the rebound after the 2023 demand shock, so 56.9 -&gt; 66.5). The prototype floored that growth at 0 (a departure: removed in v5.6, as legacy). The remaining gap is the industrial energy CO2 path, part of the fuel-use gap (I14).</t>
         </is>
       </c>
       <c r="J155" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Emissions; CAVEATS v2.8</t>
+          <t>legacy_comparison_v6_4.md; CAVEATS v2.8</t>
         </is>
       </c>
       <c r="K155" s="9" t="inlineStr">
@@ -10143,7 +10151,7 @@
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>I28</t>
+          <t>I26</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
@@ -10158,7 +10166,7 @@
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>Engineer road model: calibration open</t>
+          <t>GHG defaults not yet checked against legacy</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
@@ -10173,23 +10181,23 @@
       </c>
       <c r="G156" s="9" t="inlineStr">
         <is>
-          <t>Off by default (TrModel = Elasticity, as the legacy Egypt run). Range anxiety is legacy's stored values (Egypt 2025 passenger EV share 0.09% against 0.15% actual); the ownership decline limit (10% a year) is a placeholder.</t>
+          <t>Oil, gas and coal production held at the base year (fuel supply methane) and energy N2O moving with energy CO2 were applied as defaults in v2.8; their legacy counterparts are not yet checked.</t>
         </is>
       </c>
       <c r="H156" s="9" t="inlineStr"/>
       <c r="I156" s="9" t="inlineStr">
         <is>
-          <t>Parked, then dropped by the user (2026-10-20).</t>
+          <t>Checked (v5.6): energy N2O moves with energy CO2 as legacy (row 7549 = previous x CO2 ratio). Production for fuel-supply methane differs: now issue I66.</t>
         </is>
       </c>
       <c r="J156" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Transport</t>
+          <t>Methods, chapter Emissions; CAVEATS v2.8</t>
         </is>
       </c>
       <c r="K156" s="9" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="L156" s="9" t="inlineStr"/>
@@ -10197,7 +10205,7 @@
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>I31</t>
+          <t>I28</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
@@ -10207,12 +10215,12 @@
       </c>
       <c r="C157" s="9" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D157" s="9" t="inlineStr">
         <is>
-          <t>Average prices mix price and composition changes</t>
+          <t>Engineer road model: calibration open</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
@@ -10227,23 +10235,23 @@
       </c>
       <c r="G157" s="9" t="inlineStr">
         <is>
-          <t>Legacy F5b-c averages the after-tax price of each fuel over sectors with each scenario's own consumption of the year (a unit value) and reports the policy / baseline ratio and an index 2022 = 100 as price changes (Egypt 2030: gas +71%, oil +104%). A shift of consumption between sectors with different prices moves the "price change" with no price moving. Survey v4.15: coal and gas are averaged over power generation, residential and the 8 industry subsectors with baseline quantities (a Laspeyres index), electricity with each scenario's own consumption, oil products are single prices. v4.15 replicates legacy as the default (Settings C54 Legacy*; pav.leg, pav.lidx, pav.idx), the prototype's Laspeyres index over all final uses as the option.</t>
+          <t>Off by default (TrModel = Elasticity, as the legacy Egypt run). Range anxiety is legacy's stored values (Egypt 2025 passenger EV share 0.09% against 0.15% actual); the ownership decline limit (10% a year) is a placeholder.</t>
         </is>
       </c>
       <c r="H157" s="9" t="inlineStr"/>
       <c r="I157" s="9" t="inlineStr">
         <is>
-          <t>v4.15 (user 2026-10-18): legacy averages are the default (pav.leg, pav.lidx, pav.idx; Settings C54 Legacy*), the Laspeyres index kept as an option.</t>
+          <t>Parked, then dropped by the user (2026-10-20).</t>
         </is>
       </c>
       <c r="J157" s="9" t="inlineStr">
         <is>
-          <t>Reviews_and_Surveys.md (section Downstream_Survey) F5; PriceProjection_Method</t>
+          <t>Methods, chapter Transport</t>
         </is>
       </c>
       <c r="K157" s="9" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="L157" s="9" t="inlineStr"/>
@@ -10251,7 +10259,7 @@
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>I32</t>
+          <t>I31</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
@@ -10266,7 +10274,7 @@
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>Energy CO2 calibration to the inventory: as legacy since v4.11</t>
+          <t>Average prices mix price and composition changes</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
@@ -10281,18 +10289,18 @@
       </c>
       <c r="G158" s="9" t="inlineStr">
         <is>
-          <t>Legacy row 7520 ("Adjust EFs to match energy-related CO2 to UNFCCC inventories?", Yes* by default) multiplies every CO2 EF by the inventory energy CO2 of the year before the base year over the estimate from the base-year energy balance (Egypt: 2021 inventory against 2022, 0.930), so CO2 is about 7% below uncalibrated EFs in every sector. The inventory has a break between 2021 and 2022 (I17: 211 to 252 Mt), which legacy carries into the factor. v4.11 replicates legacy (user 2026-10-18: go with legacy); before, the prototype calibrated in 2024 and kept the switch off (user decisions v3.2, v3.4).</t>
+          <t>Legacy F5b-c averages the after-tax price of each fuel over sectors with each scenario's own consumption of the year (a unit value) and reports the policy / baseline ratio and an index 2022 = 100 as price changes (Egypt 2030: gas +71%, oil +104%). A shift of consumption between sectors with different prices moves the "price change" with no price moving. Survey v4.15: coal and gas are averaged over power generation, residential and the 8 industry subsectors with baseline quantities (a Laspeyres index), electricity with each scenario's own consumption, oil products are single prices. v4.15 replicates legacy as the default (Settings C54 Legacy*; pav.leg, pav.lidx, pav.idx), the prototype's Laspeyres index over all final uses as the option.</t>
         </is>
       </c>
       <c r="H158" s="9" t="inlineStr"/>
       <c r="I158" s="9" t="inlineStr">
         <is>
-          <t>Replicated in v4.11 (user 2026-10-18: go with legacy); the inventory break (I17) stays in the factor, as legacy.</t>
+          <t>v4.15 (user 2026-10-18): legacy averages are the default (pav.leg, pav.lidx, pav.idx; Settings C54 Legacy*), the Laspeyres index kept as an option.</t>
         </is>
       </c>
       <c r="J158" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Macro and results; Methods, chapter Emissions; CAVEATS v4.11</t>
+          <t>Reviews_and_Surveys.md (section Downstream_Survey) F5; PriceProjection_Method</t>
         </is>
       </c>
       <c r="K158" s="9" t="inlineStr">
@@ -10305,7 +10313,7 @@
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>I34</t>
+          <t>I32</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
@@ -10315,12 +10323,12 @@
       </c>
       <c r="C159" s="9" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>CH4 of the air-pollution input table: methane sources by convention</t>
+          <t>Energy CO2 calibration to the inventory: as legacy since v4.11</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
@@ -10335,18 +10343,18 @@
       </c>
       <c r="G159" s="9" t="inlineStr">
         <is>
-          <t>Legacy rows 7283-7307 feed the air-pollution module CH4 by sector: oil and gas extraction methane under "other", agriculture and waste methane under "food &amp; forestry" (waste is not food or forestry), no combustion CH4 (no factors in legacy). v3.12 replicates the allocation and adds the combustion CH4 of each sector (GAINS factors, section 14), with all fossil fuel supply methane (extraction, downstream gas, coal mining, biomass) under "other".</t>
+          <t>Legacy row 7520 ("Adjust EFs to match energy-related CO2 to UNFCCC inventories?", Yes* by default) multiplies every CO2 EF by the inventory energy CO2 of the year before the base year over the estimate from the base-year energy balance (Egypt: 2021 inventory against 2022, 0.930), so CO2 is about 7% below uncalibrated EFs in every sector. The inventory has a break between 2021 and 2022 (I17: 211 to 252 Mt), which legacy carries into the factor. v4.11 replicates legacy (user 2026-10-18: go with legacy); before, the prototype calibrated in 2024 and kept the switch off (user decisions v3.2, v3.4).</t>
         </is>
       </c>
       <c r="H159" s="9" t="inlineStr"/>
       <c r="I159" s="9" t="inlineStr">
         <is>
-          <t>As legacy (v3.12); to confirm: combustion CH4 added, all fuel supply methane under other.</t>
+          <t>Replicated in v4.11 (user 2026-10-18: go with legacy); the inventory break (I17) stays in the factor, as legacy.</t>
         </is>
       </c>
       <c r="J159" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Emissions; CAVEATS v3.12</t>
+          <t>Methods, chapter Macro and results; Methods, chapter Emissions; CAVEATS v4.11</t>
         </is>
       </c>
       <c r="K159" s="9" t="inlineStr">
@@ -10359,7 +10367,7 @@
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>I36</t>
+          <t>I34</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
@@ -10374,7 +10382,7 @@
       </c>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>Effective carbon rate counts VAT and subsidies</t>
+          <t>CH4 of the air-pollution input table: methane sources by convention</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
@@ -10389,18 +10397,18 @@
       </c>
       <c r="G160" s="9" t="inlineStr">
         <is>
-          <t>Legacy's effective carbon rate (row 16647) and total carbon price (F5d) divide revenue net of subsidies, VAT included, by CO2; the OECD effective carbon rate counts carbon taxes, fuel excises and permit prices only. The prototype replicates the legacy definition (section 17, v3.15) and says so in the note; Egypt has negative rates (subsidies exceed taxes).</t>
+          <t>Legacy rows 7283-7307 feed the air-pollution module CH4 by sector: oil and gas extraction methane under "other", agriculture and waste methane under "food &amp; forestry" (waste is not food or forestry), no combustion CH4 (no factors in legacy). v3.12 replicates the allocation and adds the combustion CH4 of each sector (GAINS factors, section 14), with all fossil fuel supply methane (extraction, downstream gas, coal mining, biomass) under "other".</t>
         </is>
       </c>
       <c r="H160" s="9" t="inlineStr"/>
       <c r="I160" s="9" t="inlineStr">
         <is>
-          <t>As legacy (v3.15); an OECD-style rate (carbon taxes, excises, permits) could be added as a memo.</t>
+          <t>As legacy (v3.12); to confirm: combustion CH4 added, all fuel supply methane under other.</t>
         </is>
       </c>
       <c r="J160" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Macro and results; CAVEATS v3.15</t>
+          <t>Methods, chapter Emissions; CAVEATS v3.12</t>
         </is>
       </c>
       <c r="K160" s="9" t="inlineStr">
@@ -10413,7 +10421,7 @@
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>I37</t>
+          <t>I36</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
@@ -10428,7 +10436,7 @@
       </c>
       <c r="D161" s="9" t="inlineStr">
         <is>
-          <t>Primary energy of renewables: efficiencies not exactly 1</t>
+          <t>Effective carbon rate counts VAT and subsidies</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
@@ -10443,18 +10451,18 @@
       </c>
       <c r="G161" s="9" t="inlineStr">
         <is>
-          <t>Legacy power data give wind, solar and hydro efficiencies of 1.004, 1.026 and 0.937, so their primary energy (generation / efficiency) differs from the physical energy content convention (1); solar shows more output than input. It enters total primary energy supply (Kaya, v3.18) and the power fuel totals; about 0.1% of TPES for Egypt.</t>
+          <t>Legacy's effective carbon rate (row 16647) and total carbon price (F5d) divide revenue net of subsidies, VAT included, by CO2; the OECD effective carbon rate counts carbon taxes, fuel excises and permit prices only. The prototype replicates the legacy definition (section 17, v3.15) and says so in the note; Egypt has negative rates (subsidies exceed taxes).</t>
         </is>
       </c>
       <c r="H161" s="9" t="inlineStr"/>
       <c r="I161" s="9" t="inlineStr">
         <is>
-          <t>As legacy (v3.18); set the renewable efficiencies to 1 if the data are confirmed.</t>
+          <t>As legacy (v3.15); an OECD-style rate (carbon taxes, excises, permits) could be added as a memo.</t>
         </is>
       </c>
       <c r="J161" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Macro and results</t>
+          <t>Methods, chapter Macro and results; CAVEATS v3.15</t>
         </is>
       </c>
       <c r="K161" s="9" t="inlineStr">
@@ -10467,7 +10475,7 @@
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>I38</t>
+          <t>I37</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
@@ -10482,7 +10490,7 @@
       </c>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>Legacy's stored run: wind and solar capex time factors 2039-2041 differ from its Power tab</t>
+          <t>Primary energy of renewables: efficiencies not exactly 1</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
@@ -10497,18 +10505,18 @@
       </c>
       <c r="G162" s="9" t="inlineStr">
         <is>
-          <t>Legacy Mitigation reads the capital cost time factors of wind and solar from the Power tab; its cached values for 2039-2041 (wind 0.920, 0.915, 0.909) disagree with the cached Power cells they reference (0.923, 0.920, 0.918), apparently a stale cache in the distributed file. Since v4.7 the prototype computes the factors from the Power tab by formula, so its power results (new capacity and investment of solar, wind and gas, then power fuel use and emissions) depart from legacy's stored run from 2039; nothing changes before 2039.</t>
+          <t>Legacy power data give wind, solar and hydro efficiencies of 1.004, 1.026 and 0.937, so their primary energy (generation / efficiency) differs from the physical energy content convention (1); solar shows more output than input. It enters total primary energy supply (Kaya, v3.18) and the power fuel totals; about 0.1% of TPES for Egypt.</t>
         </is>
       </c>
       <c r="H162" s="9" t="inlineStr"/>
       <c r="I162" s="9" t="inlineStr">
         <is>
-          <t>v4.7: the formula follows the Power tab; recheck against a fresh legacy run.</t>
+          <t>As legacy (v3.18); set the renewable efficiencies to 1 if the data are confirmed.</t>
         </is>
       </c>
       <c r="J162" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Data tabs; CAVEATS v4.7</t>
+          <t>Methods, chapter Macro and results</t>
         </is>
       </c>
       <c r="K162" s="9" t="inlineStr">
@@ -10521,7 +10529,7 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>I39</t>
+          <t>I38</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
@@ -10536,7 +10544,7 @@
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>VAT on oil products charged on the household share only (replicated v4.12)</t>
+          <t>Legacy's stored run: wind and solar capex time factors 2039-2041 differ from its Power tab</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
@@ -10551,18 +10559,18 @@
       </c>
       <c r="G163" s="9" t="inlineStr">
         <is>
-          <t>Legacy multiplies the VAT rate of gasoline, diesel, LPG and kerosene by the household share of the product (sheet OilProductShares; Egypt: gasoline 1, diesel 0.03, LPG 0.99, kerosene 0.39), on the view that firms reclaim VAT. The share is one value for all sectors, so household diesel is under-taxed and firms' gasoline over-taxed; road diesel of households is small, so the effect is mainly on gasoline. Replicated in v4.12 (LD5; user 2026-10-18: an issue, not a bug).</t>
+          <t>Legacy Mitigation reads the capital cost time factors of wind and solar from the Power tab; its cached values for 2039-2041 (wind 0.920, 0.915, 0.909) disagree with the cached Power cells they reference (0.923, 0.920, 0.918), apparently a stale cache in the distributed file. Since v4.7 the prototype computes the factors from the Power tab by formula, so its power results (new capacity and investment of solar, wind and gas, then power fuel use and emissions) depart from legacy's stored run from 2039; nothing changes before 2039.</t>
         </is>
       </c>
       <c r="H163" s="9" t="inlineStr"/>
       <c r="I163" s="9" t="inlineStr">
         <is>
-          <t>Replicated v4.12 (user 2026-10-18); a share by sector would need data by sector.</t>
+          <t>v4.7: the formula follows the Power tab; recheck against a fresh legacy run.</t>
         </is>
       </c>
       <c r="J163" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Prices 5; LegacyDiff</t>
+          <t>Methods, chapter Data tabs; CAVEATS v4.7</t>
         </is>
       </c>
       <c r="K163" s="9" t="inlineStr">
@@ -10575,7 +10583,7 @@
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>I40</t>
+          <t>I39</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
@@ -10590,7 +10598,7 @@
       </c>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>Road biofuels: feebate CO2 per liter scaled by the fossil share (replicated v4.12)</t>
+          <t>VAT on oil products charged on the household share only (replicated v4.12)</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
@@ -10605,18 +10613,18 @@
       </c>
       <c r="G164" s="9" t="inlineStr">
         <is>
-          <t>Legacy scales the CO2 per liter of gasoline and diesel in the vehicle feebate by the fossil share of road gasoline + bioethanol and diesel + biodiesel (E2146:E2147), as if the model's liters were blends; but road gasoline and diesel exclude the biofuels, which follow them as separate rows (5436-5438). Where biofuels are blended the feebate per liter is lower than the CO2 of the fossil liter. Replicated in v4.12 (LD62; user 2026-10-18). None for Egypt.</t>
+          <t>Legacy multiplies the VAT rate of gasoline, diesel, LPG and kerosene by the household share of the product (sheet OilProductShares; Egypt: gasoline 1, diesel 0.03, LPG 0.99, kerosene 0.39), on the view that firms reclaim VAT. The share is one value for all sectors, so household diesel is under-taxed and firms' gasoline over-taxed; road diesel of households is small, so the effect is mainly on gasoline. Replicated in v4.12 (LD5; user 2026-10-18: an issue, not a bug).</t>
         </is>
       </c>
       <c r="H164" s="9" t="inlineStr"/>
       <c r="I164" s="9" t="inlineStr">
         <is>
-          <t>Replicated v4.12 (user 2026-10-18); revisit if road fuels are modelled as blends.</t>
+          <t>Replicated v4.12 (user 2026-10-18); a share by sector would need data by sector.</t>
         </is>
       </c>
       <c r="J164" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Transport; LegacyDiff</t>
+          <t>Methods, chapter Prices 5; LegacyDiff</t>
         </is>
       </c>
       <c r="K164" s="9" t="inlineStr">
@@ -10629,7 +10637,7 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>I41</t>
+          <t>I40</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
@@ -10639,12 +10647,12 @@
       </c>
       <c r="C165" s="9" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D165" s="9" t="inlineStr">
         <is>
-          <t>GDP effects: the impulse is the change in revenue over this year's GDP (replicated v4.15)</t>
+          <t>Road biofuels: feebate CO2 per liter scaled by the fossil share (replicated v4.12)</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
@@ -10659,18 +10667,18 @@
       </c>
       <c r="G165" s="9" t="inlineStr">
         <is>
-          <t>Legacy row 14341 takes the yearly change of the revenue gain in USD over the current GDP, not the change of the gain as a share of GDP: with GDP growing, a constant share of GDP keeps giving impulses (Egypt: impulses sum to 4.9% of GDP against a final fiscal space of 3.5%). Replicated in v4.15 (user 2026-10-18: replicate legacy, note issues).</t>
+          <t>Legacy scales the CO2 per liter of gasoline and diesel in the vehicle feebate by the fossil share of road gasoline + bioethanol and diesel + biodiesel (E2146:E2147), as if the model's liters were blends; but road gasoline and diesel exclude the biofuels, which follow them as separate rows (5436-5438). Where biofuels are blended the feebate per liter is lower than the CO2 of the fossil liter. Replicated in v4.12 (LD62; user 2026-10-18). None for Egypt.</t>
         </is>
       </c>
       <c r="H165" s="9" t="inlineStr"/>
       <c r="I165" s="9" t="inlineStr">
         <is>
-          <t>Replicated v4.15 (user 2026-10-18); the prototype form (change of the GDP share) is one line.</t>
+          <t>Replicated v4.12 (user 2026-10-18); revisit if road fuels are modelled as blends.</t>
         </is>
       </c>
       <c r="J165" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Macro and results; LegacyDiff</t>
+          <t>Methods, chapter Transport; LegacyDiff</t>
         </is>
       </c>
       <c r="K165" s="9" t="inlineStr">
@@ -10683,7 +10691,7 @@
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>I42</t>
+          <t>I41</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
@@ -10693,12 +10701,12 @@
       </c>
       <c r="C166" s="9" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>GDP effects: impulses only from GDPStartYear (replicated v4.15)</t>
+          <t>GDP effects: the impulse is the change in revenue over this year's GDP (replicated v4.15)</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
@@ -10713,18 +10721,18 @@
       </c>
       <c r="G166" s="9" t="inlineStr">
         <is>
-          <t>Legacy cohorts start in GDPStartYear (MTInputs row 236, Egypt 2025): revenue gained before it never acts on GDP, and the first cohort holds only the change of that year. Replicated in v4.15 (impulse 0 before GDPStartYear).</t>
+          <t>Legacy row 14341 takes the yearly change of the revenue gain in USD over the current GDP, not the change of the gain as a share of GDP: with GDP growing, a constant share of GDP keeps giving impulses (Egypt: impulses sum to 4.9% of GDP against a final fiscal space of 3.5%). Replicated in v4.15 (user 2026-10-18: replicate legacy, note issues).</t>
         </is>
       </c>
       <c r="H166" s="9" t="inlineStr"/>
       <c r="I166" s="9" t="inlineStr">
         <is>
-          <t>Replicated v4.15.</t>
+          <t>Replicated v4.15 (user 2026-10-18); the prototype form (change of the GDP share) is one line.</t>
         </is>
       </c>
       <c r="J166" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Macro and results</t>
+          <t>Methods, chapter Macro and results; LegacyDiff</t>
         </is>
       </c>
       <c r="K166" s="9" t="inlineStr">
@@ -10737,7 +10745,7 @@
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>I43</t>
+          <t>I42</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
@@ -10752,7 +10760,7 @@
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>GDP effects: revenue uses 0 before the carbon price starts (not replicated)</t>
+          <t>GDP effects: impulses only from GDPStartYear (replicated v4.15)</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
@@ -10767,13 +10775,13 @@
       </c>
       <c r="G167" s="9" t="inlineStr">
         <is>
-          <t>Legacy rows 96-100 set the revenue-use shares to 0 before CPIntro, so an impulse of those years counts only as an excise drag. The prototype applies the shares in every year (per-cohort shares would need one share row per cohort). Tiny for Egypt (the revenue gain before CPIntro is nearly 0).</t>
+          <t>Legacy cohorts start in GDPStartYear (MTInputs row 236, Egypt 2025): revenue gained before it never acts on GDP, and the first cohort holds only the change of that year. Replicated in v4.15 (impulse 0 before GDPStartYear).</t>
         </is>
       </c>
       <c r="H167" s="9" t="inlineStr"/>
       <c r="I167" s="9" t="inlineStr">
         <is>
-          <t>Replicated v5.7: rows fis.impp and fis.lagp (impulse 0 before CPIntro) feed every revenue use but the excise drag, as legacy rows 96-100.</t>
+          <t>Replicated v4.15.</t>
         </is>
       </c>
       <c r="J167" s="9" t="inlineStr">
@@ -10783,7 +10791,7 @@
       </c>
       <c r="K167" s="9" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="L167" s="9" t="inlineStr"/>
@@ -10791,7 +10799,7 @@
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>I44</t>
+          <t>I43</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
@@ -10806,7 +10814,7 @@
       </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>Multipliers: the income-group spread added to manual and country multipliers (replicated v4.15)</t>
+          <t>GDP effects: revenue uses 0 before the carbon price starts (not replicated)</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
@@ -10821,13 +10829,13 @@
       </c>
       <c r="G168" s="9" t="inlineStr">
         <is>
-          <t>Legacy Low / High (FmAdj) adds -/+ the standard deviation of the income group to every source, also to manual and country-estimated multipliers. Replicated in v4.15 (Inputs_mult est and man columns).</t>
+          <t>Legacy rows 96-100 set the revenue-use shares to 0 before CPIntro, so an impulse of those years counts only as an excise drag. The prototype applies the shares in every year (per-cohort shares would need one share row per cohort). Tiny for Egypt (the revenue gain before CPIntro is nearly 0).</t>
         </is>
       </c>
       <c r="H168" s="9" t="inlineStr"/>
       <c r="I168" s="9" t="inlineStr">
         <is>
-          <t>Replicated v4.15.</t>
+          <t>Replicated v5.7: rows fis.impp and fis.lagp (impulse 0 before CPIntro) feed every revenue use but the excise drag, as legacy rows 96-100.</t>
         </is>
       </c>
       <c r="J168" s="9" t="inlineStr">
@@ -10837,7 +10845,7 @@
       </c>
       <c r="K168" s="9" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="L168" s="9" t="inlineStr"/>
@@ -10845,7 +10853,7 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>I45</t>
+          <t>I44</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
@@ -10860,7 +10868,7 @@
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>Multipliers: excise estimates from the "Excise tax" table (replicated v4.15)</t>
+          <t>Multipliers: the income-group spread added to manual and country multipliers (replicated v4.15)</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
@@ -10875,7 +10883,7 @@
       </c>
       <c r="G169" s="9" t="inlineStr">
         <is>
-          <t>Legacy maps the energy excise instrument (EXC) to the "Excise tax" country table (rows 614-812); the "Fuel tax" table (rows 210-408) is never used. Replicated in v4.15.</t>
+          <t>Legacy Low / High (FmAdj) adds -/+ the standard deviation of the income group to every source, also to manual and country-estimated multipliers. Replicated in v4.15 (Inputs_mult est and man columns).</t>
         </is>
       </c>
       <c r="H169" s="9" t="inlineStr"/>
@@ -10899,7 +10907,7 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>I46</t>
+          <t>I45</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
@@ -10909,12 +10917,12 @@
       </c>
       <c r="C170" s="9" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>Revenue by policy: transport and renewable subsidies not modelled</t>
+          <t>Multipliers: excise estimates from the "Excise tax" table (replicated v4.15)</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
@@ -10929,23 +10937,23 @@
       </c>
       <c r="G170" s="9" t="inlineStr">
         <is>
-          <t>Legacy total revenue (row 8012) includes the transport revenues of the engineer road model (customs and VAT on vehicles, feebates, vehicle and charging subsidies, distance tax; rows 7899-7985) and the renewable subsidy cost (from the elasticity power model even where the engineer model is used, rows 7882-7890). The prototype 12e block has both rows at 0 (road engineer revenues parked; no renewable subsidy policy). Egypt: transport +0.04 bn in 2030 against baseline.</t>
+          <t>Legacy maps the energy excise instrument (EXC) to the "Excise tax" country table (rows 614-812); the "Fuel tax" table (rows 210-408) is never used. Replicated in v4.15.</t>
         </is>
       </c>
       <c r="H170" s="9" t="inlineStr"/>
       <c r="I170" s="9" t="inlineStr">
         <is>
-          <t>Renewable subsidies: in the power model since v5.4 (prrns), counted in rsub, rtot and block 12e row rpol.ren, as legacy rows 7882-7890. Transport revenues: dropped with the engineer road model (I61, user 2026-10-20); row rpol.trs stays 0.</t>
+          <t>Replicated v4.15.</t>
         </is>
       </c>
       <c r="J170" s="9" t="inlineStr">
         <is>
-          <t>LegacyDiff 37</t>
+          <t>Methods, chapter Macro and results</t>
         </is>
       </c>
       <c r="K170" s="9" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="L170" s="9" t="inlineStr"/>
@@ -10953,7 +10961,7 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>I48</t>
+          <t>I46</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
@@ -10963,12 +10971,12 @@
       </c>
       <c r="C171" s="9" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>Price-control phase-out uses the consumer subsidy share (replicated v4.16)</t>
+          <t>Revenue by policy: transport and renewable subsidies not modelled</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
@@ -10983,23 +10991,23 @@
       </c>
       <c r="G171" s="9" t="inlineStr">
         <is>
-          <t>Legacy rows 2216-2217 take the floor and slope of the price-control factor from the consumer subsidy share (I2201): there is no price-control share, and a baseline price-control phase-out (share 0) has no effect. The phase-out also scales a floating tax, not only a floating subsidy. Replicated in v4.16 (po.sh.pc).</t>
+          <t>Legacy total revenue (row 8012) includes the transport revenues of the engineer road model (customs and VAT on vehicles, feebates, vehicle and charging subsidies, distance tax; rows 7899-7985) and the renewable subsidy cost (from the elasticity power model even where the engineer model is used, rows 7882-7890). The prototype 12e block has both rows at 0 (road engineer revenues parked; no renewable subsidy policy). Egypt: transport +0.04 bn in 2030 against baseline.</t>
         </is>
       </c>
       <c r="H171" s="9" t="inlineStr"/>
       <c r="I171" s="9" t="inlineStr">
         <is>
-          <t>Replicated v4.16; a price-control share would need an MTInputs row.</t>
+          <t>Renewable subsidies: in the power model since v5.4 (prrns), counted in rsub, rtot and block 12e row rpol.ren, as legacy rows 7882-7890. Transport revenues: dropped with the engineer road model (I61, user 2026-10-20); row rpol.trs stays 0.</t>
         </is>
       </c>
       <c r="J171" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Prices 6</t>
+          <t>LegacyDiff 37</t>
         </is>
       </c>
       <c r="K171" s="9" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="L171" s="9" t="inlineStr"/>
@@ -11007,7 +11015,7 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>I49</t>
+          <t>I48</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
@@ -11022,7 +11030,7 @@
       </c>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>Producer subsidies: fiscal line only, no price effect (not replicated)</t>
+          <t>Price-control phase-out uses the consumer subsidy share (replicated v4.16)</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
@@ -11037,13 +11045,13 @@
       </c>
       <c r="G172" s="9" t="inlineStr">
         <is>
-          <t>Legacy spreads a producer subsidy over world demand (oil) or half world, half domestic demand (coal, gas), and over domestic use (biomass): the per-unit subsidy is then near zero for oil, coal and gas, and enters the supply cost (the pass-through share reaches retail). The prototype has the fiscal line (pros x factor, rpsu) and no price effect; electricity producer subsidies enter the power price in legacy (power parked). None for Egypt (data 0).</t>
+          <t>Legacy rows 2216-2217 take the floor and slope of the price-control factor from the consumer subsidy share (I2201): there is no price-control share, and a baseline price-control phase-out (share 0) has no effect. The phase-out also scales a floating tax, not only a floating subsidy. Replicated in v4.16 (po.sh.pc).</t>
         </is>
       </c>
       <c r="H172" s="9" t="inlineStr"/>
       <c r="I172" s="9" t="inlineStr">
         <is>
-          <t>v6.1: replicated: rows psd (demand: world oil; half world, half domestic coal and gas; domestic biomass), psu (existing subsidy per unit, held after the last price year) and block row psp ($/GJ) in the supply cost, as legacy rows 825-829, 2455-2708; legacy bugs L124, L125 fixed. v6.2 (user 2026-10-20: reforms separate from the before-tax build-up): the phase-out is the wedge ppsw = psr (= -psu x (1 - psf)) per GJ x pass-through, subsector line psw beside csw and pcw, VAT on it in rsr. Legacy puts it in the supply cost, where the price controls absorb (1 - pass-through) of it, so results equal legacy except where the excise floor binds. Electricity producer subsidies stay with the power model. Egypt: no data (0).</t>
+          <t>Replicated v4.16; a price-control share would need an MTInputs row.</t>
         </is>
       </c>
       <c r="J172" s="9" t="inlineStr">
@@ -11053,7 +11061,7 @@
       </c>
       <c r="K172" s="9" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="L172" s="9" t="inlineStr"/>
@@ -11061,7 +11069,7 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>I50</t>
+          <t>I49</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
@@ -11076,7 +11084,7 @@
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>Residential LPG and kerosene always exempted: all new policy removed (replicated v5.1)</t>
+          <t>Producer subsidies: fiscal line only, no price effect (not replicated)</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr">
@@ -11091,23 +11099,23 @@
       </c>
       <c r="G173" s="9" t="inlineStr">
         <is>
-          <t>AlwaysExemptResLPGKer (MTInputs 268, per scenario) removes the carbon tax, the ETS and the new excise with their VAT from the residential LPG and kerosene price (legacy rows 5546-5547); the shadow price is kept, and ETS-covered emissions still count the fuels.</t>
+          <t>Legacy spreads a producer subsidy over world demand (oil) or half world, half domestic demand (coal, gas), and over domestic use (biomass): the per-unit subsidy is then near zero for oil, coal and gas, and enters the supply cost (the pass-through share reaches retail). The prototype has the fiscal line (pros x factor, rpsu) and no price effect; electricity producer subsidies enter the power price in legacy (power parked). None for Egypt (data 0).</t>
         </is>
       </c>
       <c r="H173" s="9" t="inlineStr"/>
       <c r="I173" s="9" t="inlineStr">
         <is>
-          <t>None (as legacy).</t>
+          <t>v6.1: replicated: rows psd (demand: world oil; half world, half domestic coal and gas; domestic biomass), psu (existing subsidy per unit, held after the last price year) and block row psp ($/GJ) in the supply cost, as legacy rows 825-829, 2455-2708; legacy bugs L124, L125 fixed. v6.2 (user 2026-10-20: reforms separate from the before-tax build-up): the phase-out is the wedge ppsw = psr (= -psu x (1 - psf)) per GJ x pass-through, subsector line psw beside csw and pcw, VAT on it in rsr. Legacy puts it in the supply cost, where the price controls absorb (1 - pass-through) of it, so results equal legacy except where the excise floor binds. Electricity producer subsidies stay with the power model. Egypt: no data (0).</t>
         </is>
       </c>
       <c r="J173" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Prices 5; LegacyDiff 66</t>
+          <t>Methods, chapter Prices 6</t>
         </is>
       </c>
       <c r="K173" s="9" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="L173" s="9" t="inlineStr"/>
@@ -11115,7 +11123,7 @@
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>I51</t>
+          <t>I50</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
@@ -11130,7 +11138,7 @@
       </c>
       <c r="D174" s="9" t="inlineStr">
         <is>
-          <t>Residential leakage: the fossil change is efficiency-weighted (replicated v5.1)</t>
+          <t>Residential LPG and kerosene always exempted: all new policy removed (replicated v5.1)</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
@@ -11145,18 +11153,18 @@
       </c>
       <c r="G174" s="9" t="inlineStr">
         <is>
-          <t>dF = -F x e_m x p, as legacy (p read as a share of useful energy). The alternative dF = -F x p is equally defensible (Egypt, $20 scenario, 2027: about -45 ktoe LPG and +127 ktoe biomass instead of -25 and +71).</t>
+          <t>AlwaysExemptResLPGKer (MTInputs 268, per scenario) removes the carbon tax, the ETS and the new excise with their VAT from the residential LPG and kerosene price (legacy rows 5546-5547); the shadow price is kept, and ETS-covered emissions still count the fuels.</t>
         </is>
       </c>
       <c r="H174" s="9" t="inlineStr"/>
       <c r="I174" s="9" t="inlineStr">
         <is>
-          <t>Decided (user 2026-10-19): keep the efficiency weighting, as legacy.</t>
+          <t>None (as legacy).</t>
         </is>
       </c>
       <c r="J174" s="9" t="inlineStr">
         <is>
-          <t>Equations.md 4a; LegacyDiff 65</t>
+          <t>Methods, chapter Prices 5; LegacyDiff 66</t>
         </is>
       </c>
       <c r="K174" s="9" t="inlineStr">
@@ -11169,7 +11177,7 @@
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>I54</t>
+          <t>I51</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
@@ -11184,7 +11192,7 @@
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>PPAs: phase-out switch only on the exact text "Yes*"; share to phase out typed 1</t>
+          <t>Residential leakage: the fossil change is efficiency-weighted (replicated v5.1)</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr">
@@ -11199,18 +11207,18 @@
       </c>
       <c r="G175" s="9" t="inlineStr">
         <is>
-          <t>Q2190 = IF(Q2189 = "Yes*", 1, 0): a plain "Yes" means no phase-out; the share of PPAs to phase out is typed 1 (Mitigation Q2190, Q2193, row 2218). Replicated with Yes or Yes* (LEFT 3), share 1.</t>
+          <t>dF = -F x e_m x p, as legacy (p read as a share of useful energy). The alternative dF = -F x p is equally defensible (Egypt, $20 scenario, 2027: about -45 ktoe LPG and +127 ktoe biomass instead of -25 and +71).</t>
         </is>
       </c>
       <c r="H175" s="9" t="inlineStr"/>
       <c r="I175" s="9" t="inlineStr">
         <is>
-          <t>None (user decision 2026-10-18).</t>
+          <t>Decided (user 2026-10-19): keep the efficiency weighting, as legacy.</t>
         </is>
       </c>
       <c r="J175" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Power; LegacyDiff 75</t>
+          <t>Equations.md 4a; LegacyDiff 65</t>
         </is>
       </c>
       <c r="K175" s="9" t="inlineStr">
@@ -11223,7 +11231,7 @@
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>I55</t>
+          <t>I54</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
@@ -11238,7 +11246,7 @@
       </c>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>Renewable subsidies: nominal inputs used as real</t>
+          <t>PPAs: phase-out switch only on the exact text "Yes*"; share to phase out typed 1</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
@@ -11253,23 +11261,23 @@
       </c>
       <c r="G176" s="9" t="inlineStr">
         <is>
-          <t>MTInputs 352-353 are labelled $/kWh nominal and enter the real cost and revenue without deflation (Mitigation row 2743). Replicated (rows rnsp, rns).</t>
+          <t>Q2190 = IF(Q2189 = "Yes*", 1, 0): a plain "Yes" means no phase-out; the share of PPAs to phase out is typed 1 (Mitigation Q2190, Q2193, row 2218). Replicated with Yes or Yes* (LEFT 3), share 1.</t>
         </is>
       </c>
       <c r="H176" s="9" t="inlineStr"/>
       <c r="I176" s="9" t="inlineStr">
         <is>
-          <t>Reclassified as legacy bug L114 (user 2026-10-19).</t>
+          <t>None (user decision 2026-10-18).</t>
         </is>
       </c>
       <c r="J176" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Power; LegacyDiff 76</t>
+          <t>Methods, chapter Power; LegacyDiff 75</t>
         </is>
       </c>
       <c r="K176" s="9" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="L176" s="9" t="inlineStr"/>
@@ -11277,7 +11285,7 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>I56</t>
+          <t>I55</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
@@ -11292,7 +11300,7 @@
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>Electricity excise: base-year grid intensity of the energy balance</t>
+          <t>Renewable subsidies: nominal inputs used as real</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr">
@@ -11307,23 +11315,23 @@
       </c>
       <c r="G177" s="9" t="inlineStr">
         <is>
-          <t>The excise per kWh = CO2 of the fuel input to power / power output of the base-year balance x carbon price, the same intensity in every year and scenario (Mitigation C2253, row 2253). Replicated (row exs, PwGInt) with the prototype's calibrated power EFs.</t>
+          <t>MTInputs 352-353 are labelled $/kWh nominal and enter the real cost and revenue without deflation (Mitigation row 2743). Replicated (rows rnsp, rns).</t>
         </is>
       </c>
       <c r="H177" s="9" t="inlineStr"/>
       <c r="I177" s="9" t="inlineStr">
         <is>
-          <t>Decided (user 2026-10-19): legacy kept (base-year intensity); the yearly intensity would be an upgrade.</t>
+          <t>Reclassified as legacy bug L114 (user 2026-10-19).</t>
         </is>
       </c>
       <c r="J177" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Power; LegacyDiff 77</t>
+          <t>Methods, chapter Power; LegacyDiff 76</t>
         </is>
       </c>
       <c r="K177" s="9" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="L177" s="9" t="inlineStr"/>
@@ -11331,7 +11339,7 @@
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>I57</t>
+          <t>I56</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
@@ -11346,7 +11354,7 @@
       </c>
       <c r="D178" s="9" t="inlineStr">
         <is>
-          <t>Final deficit to gas: a typed switch outside MTInputs</t>
+          <t>Electricity excise: base-year grid intensity of the energy balance</t>
         </is>
       </c>
       <c r="E178" s="11" t="inlineStr">
@@ -11361,18 +11369,18 @@
       </c>
       <c r="G178" s="9" t="inlineStr">
         <is>
-          <t>The switch is a typed cell (Mitigation E4248, No), global. Replicated as a global switch on Settings C45 (PwDeficitGas, default No).</t>
+          <t>The excise per kWh = CO2 of the fuel input to power / power output of the base-year balance x carbon price, the same intensity in every year and scenario (Mitigation C2253, row 2253). Replicated (row exs, PwGInt) with the prototype's calibrated power EFs.</t>
         </is>
       </c>
       <c r="H178" s="9" t="inlineStr"/>
       <c r="I178" s="9" t="inlineStr">
         <is>
-          <t>None (user decision: Settings, as legacy).</t>
+          <t>Decided (user 2026-10-19): legacy kept (base-year intensity); the yearly intensity would be an upgrade.</t>
         </is>
       </c>
       <c r="J178" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Power; LegacyDiff 78</t>
+          <t>Methods, chapter Power; LegacyDiff 77</t>
         </is>
       </c>
       <c r="K178" s="9" t="inlineStr">
@@ -11385,7 +11393,7 @@
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>I59</t>
+          <t>I57</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
@@ -11400,7 +11408,7 @@
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>Electricity fuel price reform not applied to electricity prices (not replicated yet)</t>
+          <t>Final deficit to gas: a typed switch outside MTInputs</t>
         </is>
       </c>
       <c r="E179" s="11" t="inlineStr">
@@ -11415,23 +11423,23 @@
       </c>
       <c r="G179" s="9" t="inlineStr">
         <is>
-          <t>Legacy adds the electricity fuel price reform (MTInputs 148/162) to the excise (row 216); the prototype computes fpr.ecy but does not apply it to the electricity price.</t>
+          <t>The switch is a typed cell (Mitigation E4248, No), global. Replicated as a global switch on Settings C45 (PwDeficitGas, default No).</t>
         </is>
       </c>
       <c r="H179" s="9" t="inlineStr"/>
       <c r="I179" s="9" t="inlineStr">
         <is>
-          <t>Replicated in v5.6: the electricity fuel price reform path enters the excise of policy scenarios (row entx).</t>
+          <t>None (user decision: Settings, as legacy).</t>
         </is>
       </c>
       <c r="J179" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Power</t>
+          <t>Methods, chapter Power; LegacyDiff 78</t>
         </is>
       </c>
       <c r="K179" s="9" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="L179" s="9" t="inlineStr"/>
@@ -11439,7 +11447,7 @@
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>I60</t>
+          <t>I59</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
@@ -11454,7 +11462,7 @@
       </c>
       <c r="D180" s="9" t="inlineStr">
         <is>
-          <t>End-user electricity price not floored at MinPostSubsidyPowerPrice (not replicated yet)</t>
+          <t>Electricity fuel price reform not applied to electricity prices (not replicated yet)</t>
         </is>
       </c>
       <c r="E180" s="11" t="inlineStr">
@@ -11469,13 +11477,13 @@
       </c>
       <c r="G180" s="9" t="inlineStr">
         <is>
-          <t>Legacy floors the end-user electricity price at MinPostSubsidyPowerPrice (rows 3617, 3646); the prototype has no floor (MinPostSubsidyPowerPrice is read per scenario since v5.4 but used only where legacy uses it in the cost side).</t>
+          <t>Legacy adds the electricity fuel price reform (MTInputs 148/162) to the excise (row 216); the prototype computes fpr.ecy but does not apply it to the electricity price.</t>
         </is>
       </c>
       <c r="H180" s="9" t="inlineStr"/>
       <c r="I180" s="9" t="inlineStr">
         <is>
-          <t>Replicated in v5.6: end-user electricity prices floored at MinPostSubsidyPowerPrice (row rp).</t>
+          <t>Replicated in v5.6: the electricity fuel price reform path enters the excise of policy scenarios (row entx).</t>
         </is>
       </c>
       <c r="J180" s="9" t="inlineStr">
@@ -11493,7 +11501,7 @@
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>I61</t>
+          <t>I60</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
@@ -11503,12 +11511,12 @@
       </c>
       <c r="C181" s="9" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>Engineer road model: follow-ups parked</t>
+          <t>End-user electricity price not floored at MinPostSubsidyPowerPrice (not replicated yet)</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
@@ -11523,23 +11531,23 @@
       </c>
       <c r="G181" s="9" t="inlineStr">
         <is>
-          <t>The engineer road model (v3.5) replicates legacy with its bugs fixed (L25-L41), but its follow-ups are parked (user 2026-10-18: too many issues, not to be fixed now): review of the engineer run in Excel (TrModel), a goal seek to re-solve range anxiety for the corrected model (LD63; Egypt 2025 passenger EV sales share 0.09% vs 0.15% actual), the elasticity branch of road biofuels (LD62) and vehicle revenues in 12b. The default run uses the elasticity road model, as legacy.</t>
+          <t>Legacy floors the end-user electricity price at MinPostSubsidyPowerPrice (rows 3617, 3646); the prototype has no floor (MinPostSubsidyPowerPrice is read per scenario since v5.4 but used only where legacy uses it in the cost side).</t>
         </is>
       </c>
       <c r="H181" s="9" t="inlineStr"/>
       <c r="I181" s="9" t="inlineStr">
         <is>
-          <t>Parked, then dropped by the user (2026-10-20).</t>
+          <t>Replicated in v5.6: end-user electricity prices floored at MinPostSubsidyPowerPrice (row rp).</t>
         </is>
       </c>
       <c r="J181" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Transport; TODO</t>
+          <t>Methods, chapter Power</t>
         </is>
       </c>
       <c r="K181" s="9" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="L181" s="9" t="inlineStr"/>
@@ -11547,7 +11555,7 @@
     <row r="182">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>I62</t>
+          <t>I61</t>
         </is>
       </c>
       <c r="B182" s="9" t="inlineStr">
@@ -11562,7 +11570,7 @@
       </c>
       <c r="D182" s="9" t="inlineStr">
         <is>
-          <t>Fuel use: no partial-adjustment model</t>
+          <t>Engineer road model: follow-ups parked</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
@@ -11577,23 +11585,23 @@
       </c>
       <c r="G182" s="9" t="inlineStr">
         <is>
-          <t>Fuel use responds to prices and income with constant long-run elasticities, as legacy, with no partial (lagged) adjustment, so the full response comes in the year of the price change. Parked by the user (2026-10-09); was upgrade U12.</t>
+          <t>The engineer road model (v3.5) replicates legacy with its bugs fixed (L25-L41), but its follow-ups are parked (user 2026-10-18: too many issues, not to be fixed now): review of the engineer run in Excel (TrModel), a goal seek to re-solve range anxiety for the corrected model (LD63; Egypt 2025 passenger EV sales share 0.09% vs 0.15% actual), the elasticity branch of road biofuels (LD62) and vehicle revenues in 12b. The default run uses the elasticity road model, as legacy.</t>
         </is>
       </c>
       <c r="H182" s="9" t="inlineStr"/>
       <c r="I182" s="9" t="inlineStr">
         <is>
-          <t>Legacy issue, not a bug: high priority for the CPAT team, not for the prototype (user 2026-10-20); replicated as legacy. Recommendation: add a partial-adjustment option: fuel use moves a share of the way to its long-run level each year (short-run and long-run elasticities), as an upgrade over legacy, switch off = legacy.</t>
+          <t>Parked, then dropped by the user (2026-10-20).</t>
         </is>
       </c>
       <c r="J182" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Prices; TODO</t>
+          <t>Methods, chapter Transport; TODO</t>
         </is>
       </c>
       <c r="K182" s="9" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="L182" s="9" t="inlineStr"/>
@@ -11601,7 +11609,7 @@
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>I63</t>
+          <t>I62</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
@@ -11616,7 +11624,7 @@
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>Demand responds to real USD prices, not real local-currency prices</t>
+          <t>Fuel use: no partial-adjustment model</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
@@ -11631,13 +11639,13 @@
       </c>
       <c r="G183" s="9" t="inlineStr">
         <is>
-          <t>As legacy, fuel and electricity demand respond to prices in real USD. Under a devaluation the two diverge (Egypt gasoline 2022-2024: about -15% in real EGP against -42% in real USD), so demand responds to a price fall households do not see. Parked by the user (2026-10-09); related to I4 and U3.</t>
+          <t>Fuel use responds to prices and income with constant long-run elasticities, as legacy, with no partial (lagged) adjustment, so the full response comes in the year of the price change. Parked by the user (2026-10-09); was upgrade U12.</t>
         </is>
       </c>
       <c r="H183" s="9" t="inlineStr"/>
       <c r="I183" s="9" t="inlineStr">
         <is>
-          <t>Parked, then dropped by the user (2026-10-20).</t>
+          <t>Legacy issue, not a bug: high priority for the CPAT team, not for the prototype (user 2026-10-20); replicated as legacy. Recommendation: add a partial-adjustment option: fuel use moves a share of the way to its long-run level each year (short-run and long-run elasticities), as an upgrade over legacy, switch off = legacy.</t>
         </is>
       </c>
       <c r="J183" s="9" t="inlineStr">
@@ -11647,7 +11655,7 @@
       </c>
       <c r="K183" s="9" t="inlineStr">
         <is>
-          <t>Dropped</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="L183" s="9" t="inlineStr"/>
@@ -11655,7 +11663,7 @@
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>I66</t>
+          <t>I63</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
@@ -11670,7 +11678,7 @@
       </c>
       <c r="D184" s="9" t="inlineStr">
         <is>
-          <t>Fuel production for supply methane held at the base year (not replicated)</t>
+          <t>Demand responds to real USD prices, not real local-currency prices</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
@@ -11685,23 +11693,23 @@
       </c>
       <c r="G184" s="9" t="inlineStr">
         <is>
-          <t>Legacy grows crude oil, natural gas and coal production (rows 6132-6135) from 2024 with the producer-price response to the methane fee (rows 6123-6130: price increase x pass-through, Manual inputs J190:J194 elasticities) and the growth of world demand of the global demand scenario (Prices_int rows 323-333, lagged one year). The prototype holds production at the base year (rows ch4.act og, cm). Found 2026-10-19 checking I26.</t>
+          <t>As legacy, fuel and electricity demand respond to prices in real USD. Under a devaluation the two diverge (Egypt gasoline 2022-2024: about -15% in real EGP against -42% in real USD), so demand responds to a price fall households do not see. Parked by the user (2026-10-09); related to I4 and U3.</t>
         </is>
       </c>
       <c r="H184" s="9" t="inlineStr"/>
       <c r="I184" s="9" t="inlineStr">
         <is>
-          <t>Replicated in v5.6: rows ch4.wd, ch4.fk, ch4.pi, ch4.prd (inventory-year activity = base production, to avoid a loop; legacy holds 2022-2023 at the base anyway). Note: legacy CHOOSE reads the Net Zero row for the third and fourth demand scenarios.</t>
+          <t>Parked, then dropped by the user (2026-10-20).</t>
         </is>
       </c>
       <c r="J184" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Emissions</t>
+          <t>Methods, chapter Prices; TODO</t>
         </is>
       </c>
       <c r="K184" s="9" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="L184" s="9" t="inlineStr"/>
@@ -11709,7 +11717,7 @@
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>I68</t>
+          <t>I66</t>
         </is>
       </c>
       <c r="B185" s="9" t="inlineStr">
@@ -11719,12 +11727,12 @@
       </c>
       <c r="C185" s="9" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>NDC reference years outside the data</t>
+          <t>Fuel production for supply methane held at the base year (not replicated)</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
@@ -11739,13 +11747,13 @@
       </c>
       <c r="G185" s="9" t="inlineStr">
         <is>
-          <t>Historical emissions (sheet GHGHist, legacy GHGs rows 954-1189) cover 1990, 2000, 2005, 2007, 2010, 2013, 2014 and 2017 (CO2 to 2020); real GDP (WEO) starts later. A Historical or Intensity NDC with another reference year, or an Intensity NDC with an early reference year (India 2005), gives N/A (legacy #N/A or a wrong cell, L123). Data to extend when the NDC module is used.</t>
+          <t>Legacy grows crude oil, natural gas and coal production (rows 6132-6135) from 2024 with the producer-price response to the methane fee (rows 6123-6130: price increase x pass-through, Manual inputs J190:J194 elasticities) and the growth of world demand of the global demand scenario (Prices_int rows 323-333, lagged one year). The prototype holds production at the base year (rows ch4.act og, cm). Found 2026-10-19 checking I26.</t>
         </is>
       </c>
       <c r="H185" s="9" t="inlineStr"/>
       <c r="I185" s="9" t="inlineStr">
         <is>
-          <t>v5.7: GDP solved (WEO NGDP_R, 2000-2040). v6.1: reference years 2021-2024 read the GHGs inventory (rows ndc.hc, ndc.hv), 2022 onwards the model. Still open: historical GHGs 2018-2020 (GHGHist ends 2017, CO2 2020): data request.</t>
+          <t>Replicated in v5.6: rows ch4.wd, ch4.fk, ch4.pi, ch4.prd (inventory-year activity = base production, to avoid a loop; legacy holds 2022-2023 at the base anyway). Note: legacy CHOOSE reads the Net Zero row for the third and fourth demand scenarios.</t>
         </is>
       </c>
       <c r="J185" s="9" t="inlineStr">
@@ -11755,7 +11763,7 @@
       </c>
       <c r="K185" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="L185" s="9" t="inlineStr"/>
@@ -11763,7 +11771,7 @@
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>I71</t>
+          <t>I68</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
@@ -11773,12 +11781,12 @@
       </c>
       <c r="C186" s="9" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D186" s="9" t="inlineStr">
         <is>
-          <t>Fuel use grows with total GDP: population gets the income elasticity</t>
+          <t>NDC reference years outside the data</t>
         </is>
       </c>
       <c r="E186" s="11" t="inlineStr">
@@ -11793,23 +11801,23 @@
       </c>
       <c r="G186" s="9" t="inlineStr">
         <is>
-          <t>Legacy updates fuel use each year with GDP growth raised to the income elasticity (x the income factor), next to the price and efficiency terms (CPAT equation 3.3.3; legacy row 2433). Total GDP growth mixes per-capita income growth with population growth, so population growth acts through the income elasticity (typically below 1) instead of an exponent of about 1, and its effect is entangled with the price elasticities in the same multiplicative update. Replicated as legacy. High priority (user 2026-10-20).</t>
+          <t>Historical emissions (sheet GHGHist, legacy GHGs rows 954-1189) cover 1990, 2000, 2005, 2007, 2010, 2013, 2014 and 2017 (CO2 to 2020); real GDP (WEO) starts later. A Historical or Intensity NDC with another reference year, or an Intensity NDC with an early reference year (India 2005), gives N/A (legacy #N/A or a wrong cell, L123). Data to extend when the NDC module is used.</t>
         </is>
       </c>
       <c r="H186" s="9" t="inlineStr"/>
       <c r="I186" s="9" t="inlineStr">
         <is>
-          <t>Legacy issue, not a bug: high priority for the CPAT team, not for the prototype (user 2026-10-20); replicated as legacy. Recommendation: split the driver: fuel use x (1 + population growth)^1 x (1 + per-capita income growth)^income elasticity, keeping the price and efficiency terms separate; switch off = legacy.</t>
+          <t>v5.7: GDP solved (WEO NGDP_R, 2000-2040). v6.1: reference years 2021-2024 read the GHGs inventory (rows ndc.hc, ndc.hv), 2022 onwards the model. Still open: historical GHGs 2018-2020 (GHGHist ends 2017, CO2 2020): data request.</t>
         </is>
       </c>
       <c r="J186" s="9" t="inlineStr">
         <is>
-          <t>Equations.md E53-E56; Methods, chapter Prices</t>
+          <t>Methods, chapter Emissions</t>
         </is>
       </c>
       <c r="K186" s="9" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L186" s="9" t="inlineStr"/>
@@ -11817,7 +11825,7 @@
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>I72</t>
+          <t>I71</t>
         </is>
       </c>
       <c r="B187" s="9" t="inlineStr">
@@ -11832,7 +11840,7 @@
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>GDP feedback timing: same-year effects must never reach same-year demand</t>
+          <t>Fuel use grows with total GDP: population gets the income elasticity</t>
         </is>
       </c>
       <c r="E187" s="11" t="inlineStr">
@@ -11847,23 +11855,23 @@
       </c>
       <c r="G187" s="9" t="inlineStr">
         <is>
-          <t>Legacy and the prototype let revenue of year t move GDP only from year t+1 (legacy row 8761 reads the previous column; prototype gdp.lvl = 1 + last year's gdp.eff), and the fiscal space reads revenue of year t only. This lag is what keeps the model free of circular references whatever the revenue lines read; it is not stated anywhere. Recommendation to the CPAT team: make it an explicit rule of the method and keep it when the GDP block changes. Replicated.</t>
+          <t>Legacy updates fuel use each year with GDP growth raised to the income elasticity (x the income factor), next to the price and efficiency terms (CPAT equation 3.3.3; legacy row 2433). Total GDP growth mixes per-capita income growth with population growth, so population growth acts through the income elasticity (typically below 1) instead of an exponent of about 1, and its effect is entangled with the price elasticities in the same multiplicative update. Replicated as legacy. High priority (user 2026-10-20).</t>
         </is>
       </c>
       <c r="H187" s="9" t="inlineStr"/>
       <c r="I187" s="9" t="inlineStr">
         <is>
-          <t>Stated as a rule (user 2026-10-20): Methods, chapter Macro and results section Timing rule and NORMS (circular references): revenue of year t moves GDP only from year t+1, the fiscal space reads revenue of year t only, and no same-year GDP effect reaches same-year demand. Recommendation to the CPAT team: state it in the legacy method too.</t>
+          <t>Legacy issue, not a bug: high priority for the CPAT team, not for the prototype (user 2026-10-20); replicated as legacy. Recommendation: split the driver: fuel use x (1 + population growth)^1 x (1 + per-capita income growth)^income elasticity, keeping the price and efficiency terms separate; switch off = legacy.</t>
         </is>
       </c>
       <c r="J187" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Macro and results; NORMS (circular references)</t>
+          <t>Equations.md E53-E56; Methods, chapter Prices</t>
         </is>
       </c>
       <c r="K187" s="9" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="L187" s="9" t="inlineStr"/>
@@ -11871,57 +11879,61 @@
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>LD1</t>
+          <t>I72</t>
         </is>
       </c>
       <c r="B188" s="9" t="inlineStr">
         <is>
-          <t>LegacyDiff departure</t>
+          <t>Issue (replicated)</t>
         </is>
       </c>
       <c r="C188" s="9" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D188" s="9" t="inlineStr">
         <is>
-          <t>Elasticities: food &amp; forestry</t>
-        </is>
-      </c>
-      <c r="E188" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>GDP feedback timing: same-year effects must never reach same-year demand</t>
+        </is>
+      </c>
+      <c r="E188" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F188" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Services (buildings) elasticities</t>
+          <t>Kept as legacy, tracked</t>
         </is>
       </c>
       <c r="G188" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Industry elasticities (coded EC_SECTORS)</t>
-        </is>
-      </c>
-      <c r="H188" s="9" t="inlineStr">
-        <is>
-          <t>Food &amp; forestry fuel response</t>
-        </is>
-      </c>
-      <c r="I188" s="9" t="inlineStr"/>
+          <t>Legacy and the prototype let revenue of year t move GDP only from year t+1 (legacy row 8761 reads the previous column; prototype gdp.lvl = 1 + last year's gdp.eff), and the fiscal space reads revenue of year t only. This lag is what keeps the model free of circular references whatever the revenue lines read; it is not stated anywhere. Recommendation to the CPAT team: make it an explicit rule of the method and keep it when the GDP block changes. Replicated.</t>
+        </is>
+      </c>
+      <c r="H188" s="9" t="inlineStr"/>
+      <c r="I188" s="9" t="inlineStr">
+        <is>
+          <t>Stated as a rule (user 2026-10-20): Methods, chapter Macro and results section Timing rule and NORMS (circular references): revenue of year t moves GDP only from year t+1, the fiscal space reads revenue of year t only, and no same-year GDP effect reaches same-year demand. Recommendation to the CPAT team: state it in the legacy method too.</t>
+        </is>
+      </c>
       <c r="J188" s="9" t="inlineStr">
         <is>
-          <t>Sheet LegacyDiff</t>
-        </is>
-      </c>
-      <c r="K188" s="9" t="inlineStr"/>
+          <t>Methods, chapter Macro and results; NORMS (circular references)</t>
+        </is>
+      </c>
+      <c r="K188" s="9" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
       <c r="L188" s="9" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>LD2</t>
+          <t>LD1</t>
         </is>
       </c>
       <c r="B189" s="9" t="inlineStr">
@@ -11936,7 +11948,7 @@
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>Other oil products: pass-through and margin</t>
+          <t>Elasticities: food &amp; forestry</t>
         </is>
       </c>
       <c r="E189" s="10" t="inlineStr">
@@ -11946,17 +11958,17 @@
       </c>
       <c r="F189" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: From the IMF dataset like the other oil products (Egypt 0 and 7.95 $/bbl)</t>
+          <t>Departs from legacy: Services (buildings) elasticities</t>
         </is>
       </c>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Hardcoded 1 and 0</t>
+          <t>Legacy: Industry elasticities (coded EC_SECTORS)</t>
         </is>
       </c>
       <c r="H189" s="9" t="inlineStr">
         <is>
-          <t>Large: other oil products, total fuel use</t>
+          <t>Food &amp; forestry fuel response</t>
         </is>
       </c>
       <c r="I189" s="9" t="inlineStr"/>
@@ -11971,7 +11983,7 @@
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>LD3</t>
+          <t>LD2</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
@@ -11981,12 +11993,12 @@
       </c>
       <c r="C190" s="9" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="D190" s="9" t="inlineStr">
         <is>
-          <t>VAT rate where the dataset is blank</t>
+          <t>Other oil products: pass-through and margin</t>
         </is>
       </c>
       <c r="E190" s="10" t="inlineStr">
@@ -11996,17 +12008,17 @@
       </c>
       <c r="F190" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: General VAT rate VAT_WEO for residential coal and gas and all-sector oil products; 0 for power, industry, biomass. Only for blank cells (v0.14)</t>
+          <t>Departs from legacy: From the IMF dataset like the other oil products (Egypt 0 and 7.95 $/bbl)</t>
         </is>
       </c>
       <c r="G190" s="9" t="inlineStr">
         <is>
-          <t>Legacy: 0</t>
+          <t>Legacy: Hardcoded 1 and 0</t>
         </is>
       </c>
       <c r="H190" s="9" t="inlineStr">
         <is>
-          <t>None for Egypt since v0.14 (corrected data fill every VAT cell)</t>
+          <t>Large: other oil products, total fuel use</t>
         </is>
       </c>
       <c r="I190" s="9" t="inlineStr"/>
@@ -12021,7 +12033,7 @@
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>LD4</t>
+          <t>LD3</t>
         </is>
       </c>
       <c r="B191" s="9" t="inlineStr">
@@ -12036,7 +12048,7 @@
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>Egypt price data</t>
+          <t>VAT rate where the dataset is blank</t>
         </is>
       </c>
       <c r="E191" s="10" t="inlineStr">
@@ -12046,17 +12058,17 @@
       </c>
       <c r="F191" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Corrected Egypt block supplied by the user (2026-10-09; 291 cells, years 2019-2020 added); changed cells bright yellow in Prices_dom</t>
+          <t>Departs from legacy: General VAT rate VAT_WEO for residential coal and gas and all-sector oil products; 0 for power, industry, biomass. Only for blank cells (v0.14)</t>
         </is>
       </c>
       <c r="G191" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Price block in the legacy release</t>
+          <t>Legacy: 0</t>
         </is>
       </c>
       <c r="H191" s="9" t="inlineStr">
         <is>
-          <t>Taxes and subsidies of gas and oil products; small supply-cost changes</t>
+          <t>None for Egypt since v0.14 (corrected data fill every VAT cell)</t>
         </is>
       </c>
       <c r="I191" s="9" t="inlineStr"/>
@@ -12071,7 +12083,7 @@
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>LD10</t>
+          <t>LD4</t>
         </is>
       </c>
       <c r="B192" s="9" t="inlineStr">
@@ -12081,12 +12093,12 @@
       </c>
       <c r="C192" s="9" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D192" s="9" t="inlineStr">
         <is>
-          <t>Policy paths after the target year</t>
+          <t>Egypt price data</t>
         </is>
       </c>
       <c r="E192" s="10" t="inlineStr">
@@ -12096,17 +12108,17 @@
       </c>
       <c r="F192" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Linear continuation for fuel price reform and feebates; carbon price keeps the switch; ETS benchmarks constant; ETS cap per MTInputs switch</t>
+          <t>Departs from legacy: Corrected Egypt block supplied by the user (2026-10-09; 291 cells, years 2019-2020 added); changed cells bright yellow in Prices_dom</t>
         </is>
       </c>
       <c r="G192" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Per instrument (carbon price: MTInputs switch)</t>
+          <t>Legacy: Price block in the legacy release</t>
         </is>
       </c>
       <c r="H192" s="9" t="inlineStr">
         <is>
-          <t>Post-target years</t>
+          <t>Taxes and subsidies of gas and oil products; small supply-cost changes</t>
         </is>
       </c>
       <c r="I192" s="9" t="inlineStr"/>
@@ -12121,7 +12133,7 @@
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>LD13</t>
+          <t>LD10</t>
         </is>
       </c>
       <c r="B193" s="9" t="inlineStr">
@@ -12136,7 +12148,7 @@
       </c>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>Biomass carbon-tax coverage</t>
+          <t>Policy paths after the target year</t>
         </is>
       </c>
       <c r="E193" s="10" t="inlineStr">
@@ -12146,17 +12158,17 @@
       </c>
       <c r="F193" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: TRUE (EF 0)</t>
+          <t>Departs from legacy: Linear continuation for fuel price reform and feebates; carbon price keeps the switch; ETS benchmarks constant; ETS cap per MTInputs switch</t>
         </is>
       </c>
       <c r="G193" s="9" t="inlineStr">
         <is>
-          <t>Legacy: No switch</t>
+          <t>Legacy: Per instrument (carbon price: MTInputs switch)</t>
         </is>
       </c>
       <c r="H193" s="9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Post-target years</t>
         </is>
       </c>
       <c r="I193" s="9" t="inlineStr"/>
@@ -12171,7 +12183,7 @@
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>LD14</t>
+          <t>LD13</t>
         </is>
       </c>
       <c r="B194" s="9" t="inlineStr">
@@ -12186,7 +12198,7 @@
       </c>
       <c r="D194" s="9" t="inlineStr">
         <is>
-          <t>Sign of subsidies</t>
+          <t>Biomass carbon-tax coverage</t>
         </is>
       </c>
       <c r="E194" s="10" t="inlineStr">
@@ -12196,17 +12208,17 @@
       </c>
       <c r="F194" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Subsidies negative: esub, esubpu, rsub, prsub, sgap, rgap; net existing revenue rnet = rtx + rsub</t>
+          <t>Departs from legacy: TRUE (EF 0)</t>
         </is>
       </c>
       <c r="G194" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Subsidy cost reported as a positive number</t>
+          <t>Legacy: No switch</t>
         </is>
       </c>
       <c r="H194" s="9" t="inlineStr">
         <is>
-          <t>Sign of the subsidy rows only</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I194" s="9" t="inlineStr"/>
@@ -12221,7 +12233,7 @@
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>LD15</t>
+          <t>LD14</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
@@ -12236,7 +12248,7 @@
       </c>
       <c r="D195" s="9" t="inlineStr">
         <is>
-          <t>Constants and row pointers</t>
+          <t>Sign of subsidies</t>
         </is>
       </c>
       <c r="E195" s="10" t="inlineStr">
@@ -12246,17 +12258,17 @@
       </c>
       <c r="F195" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Looked up: named constants and policy assumptions on sheet Constants, MTInputs rows on Mapping (by NameOfParameter or label), baseline CO2 on sheet BaselineCO2</t>
+          <t>Departs from legacy: Subsidies negative: esub, esubpu, rsub, prsub, sgap, rgap; net existing revenue rnet = rtx + rsub</t>
         </is>
       </c>
       <c r="G195" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Typed in cells and formulas (e.g. 8760, 8.76, 1000, 0.01, MTInputs row numbers, baseline values)</t>
+          <t>Legacy: Subsidy cost reported as a positive number</t>
         </is>
       </c>
       <c r="H195" s="9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Sign of the subsidy rows only</t>
         </is>
       </c>
       <c r="I195" s="9" t="inlineStr"/>
@@ -12271,7 +12283,7 @@
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>LD16</t>
+          <t>LD15</t>
         </is>
       </c>
       <c r="B196" s="9" t="inlineStr">
@@ -12281,12 +12293,12 @@
       </c>
       <c r="C196" s="9" t="inlineStr">
         <is>
-          <t>To check (bucket 5)</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="D196" s="9" t="inlineStr">
         <is>
-          <t>Margins and production costs</t>
+          <t>Constants and row pointers</t>
         </is>
       </c>
       <c r="E196" s="10" t="inlineStr">
@@ -12296,17 +12308,17 @@
       </c>
       <c r="F196" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: x CPI index of the base year</t>
+          <t>Departs from legacy: Looked up: named constants and policy assumptions on sheet Constants, MTInputs rows on Mapping (by NameOfParameter or label), baseline CO2 on sheet BaselineCO2</t>
         </is>
       </c>
       <c r="G196" s="9" t="inlineStr">
         <is>
-          <t>Legacy: coded applies no inflation conversion</t>
+          <t>Legacy: Typed in cells and formulas (e.g. 8760, 8.76, 1000, 0.01, MTInputs row numbers, baseline values)</t>
         </is>
       </c>
       <c r="H196" s="9" t="inlineStr">
         <is>
-          <t>Coal and gas supply cost level</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I196" s="9" t="inlineStr"/>
@@ -12321,7 +12333,7 @@
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>LD19</t>
+          <t>LD16</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -12331,12 +12343,12 @@
       </c>
       <c r="C197" s="9" t="inlineStr">
         <is>
-          <t>Simplification</t>
+          <t>To check (bucket 5)</t>
         </is>
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>Producer subsidies</t>
+          <t>Margins and production costs</t>
         </is>
       </c>
       <c r="E197" s="10" t="inlineStr">
@@ -12346,17 +12358,17 @@
       </c>
       <c r="F197" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Fiscal line by fuel (v4.16, LD19): producer subsidies (Prices_dom mit.pros, USD m real) x phase-out factor, in total revenue (rpsu), 12e and the fiscal space; no price effect</t>
+          <t>Departs from legacy: x CPI index of the base year</t>
         </is>
       </c>
       <c r="G197" s="9" t="inlineStr">
         <is>
-          <t>Legacy: In the supply cost</t>
+          <t>Legacy: coded applies no inflation conversion</t>
         </is>
       </c>
       <c r="H197" s="9" t="inlineStr">
         <is>
-          <t>None for Egypt (no producer subsidy data)</t>
+          <t>Coal and gas supply cost level</t>
         </is>
       </c>
       <c r="I197" s="9" t="inlineStr"/>
@@ -12371,7 +12383,7 @@
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>LD28</t>
+          <t>LD19</t>
         </is>
       </c>
       <c r="B198" s="9" t="inlineStr">
@@ -12386,7 +12398,7 @@
       </c>
       <c r="D198" s="9" t="inlineStr">
         <is>
-          <t>Power: features not built</t>
+          <t>Producer subsidies</t>
         </is>
       </c>
       <c r="E198" s="10" t="inlineStr">
@@ -12396,17 +12408,17 @@
       </c>
       <c r="F198" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Dropped (user decisions 4 and 5 of the power plan; the rebate covers the demand-side feebate). Built: v5.4 PPAs, deficit to gas, renewable subsidies, rebate, electricity excise, every power input by scenario; v5.6 manual capacity and investment (P3: rows mancap, mani, needm; Manual inputs 349-357 scenario 1, 363-371 other scenarios; legacy bug L118 fixed: logit investment sized on the need net of manual investment)</t>
+          <t>Departs from legacy: Fiscal line by fuel (v4.16, LD19): producer subsidies (Prices_dom mit.pros, USD m real) x phase-out factor, in total revenue (rpsu), 12e and the fiscal space; no price effect</t>
         </is>
       </c>
       <c r="G198" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Power demand from the elasticity model, carbon price on power use (feebate on demand)</t>
+          <t>Legacy: In the supply cost</t>
         </is>
       </c>
       <c r="H198" s="9" t="inlineStr">
         <is>
-          <t>None for Egypt</t>
+          <t>None for Egypt (no producer subsidy data)</t>
         </is>
       </c>
       <c r="I198" s="9" t="inlineStr"/>
@@ -12421,7 +12433,7 @@
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>LD33</t>
+          <t>LD28</t>
         </is>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -12431,12 +12443,12 @@
       </c>
       <c r="C199" s="9" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Simplification</t>
         </is>
       </c>
       <c r="D199" s="9" t="inlineStr">
         <is>
-          <t>Power: historical electricity prices and VAT</t>
+          <t>Power: features not built</t>
         </is>
       </c>
       <c r="E199" s="10" t="inlineStr">
@@ -12446,17 +12458,17 @@
       </c>
       <c r="F199" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Corrected Egypt block (residential 0.054, 0.048, 0.043 $/kWh nominal 2022-2024; VAT 0)</t>
+          <t>Departs from legacy: Dropped (user decisions 4 and 5 of the power plan; the rebate covers the demand-side feebate). Built: v5.4 PPAs, deficit to gas, renewable subsidies, rebate, electricity excise, every power input by scenario; v5.6 manual capacity and investment (P3: rows mancap, mani, needm; Manual inputs 349-357 scenario 1, 363-371 other scenarios; legacy bug L118 fixed: logit investment sized on the need net of manual investment)</t>
         </is>
       </c>
       <c r="G199" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Legacy vintage (residential 0.112 $/kWh incl. 15.6% VAT in 2022)</t>
+          <t>Legacy: Power demand from the elasticity model, carbon price on power use (feebate on demand)</t>
         </is>
       </c>
       <c r="H199" s="9" t="inlineStr">
         <is>
-          <t>Electricity price levels</t>
+          <t>None for Egypt</t>
         </is>
       </c>
       <c r="I199" s="9" t="inlineStr"/>
@@ -12471,7 +12483,7 @@
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
         <is>
-          <t>LD40</t>
+          <t>LD33</t>
         </is>
       </c>
       <c r="B200" s="9" t="inlineStr">
@@ -12481,12 +12493,12 @@
       </c>
       <c r="C200" s="9" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D200" s="9" t="inlineStr">
         <is>
-          <t>Horizon and indices</t>
+          <t>Power: historical electricity prices and VAT</t>
         </is>
       </c>
       <c r="E200" s="10" t="inlineStr">
@@ -12496,17 +12508,17 @@
       </c>
       <c r="F200" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: To 2041 (v2.3; the last year is the LAMBDA year); same indices; values after 2030 not a legacy target</t>
+          <t>Departs from legacy: Corrected Egypt block (residential 0.054, 0.048, 0.043 $/kWh nominal 2022-2024; VAT 0)</t>
         </is>
       </c>
       <c r="G200" s="9" t="inlineStr">
         <is>
-          <t>Legacy: To 2050 (power block to 2041); CPI held flat after 2031</t>
+          <t>Legacy: Legacy vintage (residential 0.112 $/kWh incl. 15.6% VAT in 2022)</t>
         </is>
       </c>
       <c r="H200" s="9" t="inlineStr">
         <is>
-          <t>Post-2030</t>
+          <t>Electricity price levels</t>
         </is>
       </c>
       <c r="I200" s="9" t="inlineStr"/>
@@ -12521,7 +12533,7 @@
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>LD41</t>
+          <t>LD40</t>
         </is>
       </c>
       <c r="B201" s="9" t="inlineStr">
@@ -12531,12 +12543,12 @@
       </c>
       <c r="C201" s="9" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="D201" s="9" t="inlineStr">
         <is>
-          <t>Data vintage</t>
+          <t>Horizon and indices</t>
         </is>
       </c>
       <c r="E201" s="10" t="inlineStr">
@@ -12546,17 +12558,17 @@
       </c>
       <c r="F201" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: NoPropData extracts; energy use via kernel v1.6; IIASA EFs without inventory adjustment</t>
+          <t>Departs from legacy: To 2041 (v2.3; the last year is the LAMBDA year); same indices; values after 2030 not a legacy target</t>
         </is>
       </c>
       <c r="G201" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Proprietary price forecasts; IEA balances</t>
+          <t>Legacy: To 2050 (power block to 2041); CPI held flat after 2031</t>
         </is>
       </c>
       <c r="H201" s="9" t="inlineStr">
         <is>
-          <t>Levels; legacy price forecasts #N/A</t>
+          <t>Post-2030</t>
         </is>
       </c>
       <c r="I201" s="9" t="inlineStr"/>
@@ -12571,7 +12583,7 @@
     <row r="202">
       <c r="A202" s="9" t="inlineStr">
         <is>
-          <t>LD47</t>
+          <t>LD41</t>
         </is>
       </c>
       <c r="B202" s="9" t="inlineStr">
@@ -12586,7 +12598,7 @@
       </c>
       <c r="D202" s="9" t="inlineStr">
         <is>
-          <t>GHGs: combustion emission factors (v2.8)</t>
+          <t>Data vintage</t>
         </is>
       </c>
       <c r="E202" s="10" t="inlineStr">
@@ -12596,17 +12608,17 @@
       </c>
       <c r="F202" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: GAINS base and final factor (EF_PM FE in, FE fin), linear to EFEndYear (2039), flat after</t>
+          <t>Departs from legacy: NoPropData extracts; energy use via kernel v1.6; IIASA EFs without inventory adjustment</t>
         </is>
       </c>
       <c r="G202" s="9" t="inlineStr">
         <is>
-          <t>Legacy: GAINS factor paths by year (proprietary; zero in the NoPropData file)</t>
+          <t>Legacy: Proprietary price forecasts; IEA balances</t>
         </is>
       </c>
       <c r="H202" s="9" t="inlineStr">
         <is>
-          <t>Combustion CH4 (scaled by the calibration to the inventory)</t>
+          <t>Levels; legacy price forecasts #N/A</t>
         </is>
       </c>
       <c r="I202" s="9" t="inlineStr"/>
@@ -12621,7 +12633,7 @@
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>LD58</t>
+          <t>LD47</t>
         </is>
       </c>
       <c r="B203" s="9" t="inlineStr">
@@ -12636,7 +12648,7 @@
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>GDP effects: legacy values (v3.1)</t>
+          <t>GHGs: combustion emission factors (v2.8)</t>
         </is>
       </c>
       <c r="E203" s="10" t="inlineStr">
@@ -12646,17 +12658,17 @@
       </c>
       <c r="F203" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Computed</t>
+          <t>Departs from legacy: GAINS base and final factor (EF_PM FE in, FE fin), linear to EFEndYear (2039), flat after</t>
         </is>
       </c>
       <c r="G203" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Baseline GDP effect rows 8280-8287 are 0 (live formulas, IFNA(INDEX(...),0); the baseline has no policy); the policy rows 14584-14607 hold cached values of its carbon-tax run (GDP effect 2030 -0.07%, 2035 +0.34%, 2040 +1.22%; legacy carbon price Linear* to about 175 $/t in 2041)</t>
+          <t>Legacy: GAINS factor paths by year (proprietary; zero in the NoPropData file)</t>
         </is>
       </c>
       <c r="H203" s="9" t="inlineStr">
         <is>
-          <t>A benchmark for the GDP block once a scenario with the legacy carbon price path is run</t>
+          <t>Combustion CH4 (scaled by the calibration to the inventory)</t>
         </is>
       </c>
       <c r="I203" s="9" t="inlineStr"/>
@@ -12671,7 +12683,7 @@
     <row r="204">
       <c r="A204" s="9" t="inlineStr">
         <is>
-          <t>LD59</t>
+          <t>LD58</t>
         </is>
       </c>
       <c r="B204" s="9" t="inlineStr">
@@ -12681,12 +12693,12 @@
       </c>
       <c r="C204" s="9" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D204" s="9" t="inlineStr">
         <is>
-          <t>Road transport: engineer model (v3.5)</t>
+          <t>GDP effects: legacy values (v3.1)</t>
         </is>
       </c>
       <c r="E204" s="10" t="inlineStr">
@@ -12696,17 +12708,17 @@
       </c>
       <c r="F204" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Section 5b of every scenario group, every row live (Methods, chapter Transport); TrModel default Elasticity, Engineer by switch; the 17 legacy bugs of Methods, chapter Transport section 3 fixed (B1-B23)</t>
+          <t>Departs from legacy: Computed</t>
         </is>
       </c>
       <c r="G204" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Key inputs 15 and section 5 (rows 2017-5378), switch TrModel (MTInputs F340; template default Engineer, Egypt run Elasticity)</t>
+          <t>Legacy: Baseline GDP effect rows 8280-8287 are 0 (live formulas, IFNA(INDEX(...),0); the baseline has no policy); the policy rows 14584-14607 hold cached values of its carbon-tax run (GDP effect 2030 -0.07%, 2035 +0.34%, 2040 +1.22%; legacy carbon price Linear* to about 175 $/t in 2041)</t>
         </is>
       </c>
       <c r="H204" s="9" t="inlineStr">
         <is>
-          <t>None by default; with Engineer: road fuel use and EV shares as in Methods, chapter Transport section 4</t>
+          <t>A benchmark for the GDP block once a scenario with the legacy carbon price path is run</t>
         </is>
       </c>
       <c r="I204" s="9" t="inlineStr"/>
@@ -12721,7 +12733,7 @@
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>LD60</t>
+          <t>LD59</t>
         </is>
       </c>
       <c r="B205" s="9" t="inlineStr">
@@ -12736,7 +12748,7 @@
       </c>
       <c r="D205" s="9" t="inlineStr">
         <is>
-          <t>Road transport: policy inputs (v3.5)</t>
+          <t>Road transport: engineer model (v3.5)</t>
         </is>
       </c>
       <c r="E205" s="10" t="inlineStr">
@@ -12746,17 +12758,17 @@
       </c>
       <c r="F205" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Policies: MTInputs rows 418-479 after the template (scenario-specific, legacy Dashboard defaults, all off); parameters and hardcoded literals (Gompertz constant, gas liters per GJ, PHEV kWh per liter, insurance factor, BEV distance caps, price elasticities): sheets TransportParams, TransportPaths and named constants</t>
+          <t>Departs from legacy: Section 5b of every scenario group, every row live (Methods, chapter Transport); TrModel default Elasticity, Engineer by switch; the 17 legacy bugs of Methods, chapter Transport section 3 fixed (B1-B23)</t>
         </is>
       </c>
       <c r="G205" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Dashboard rows 61-98 and 540-559 (outside MTInputs)</t>
+          <t>Legacy: Key inputs 15 and section 5 (rows 2017-5378), switch TrModel (MTInputs F340; template default Engineer, Egypt run Elasticity)</t>
         </is>
       </c>
       <c r="H205" s="9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None by default; with Engineer: road fuel use and EV shares as in Methods, chapter Transport section 4</t>
         </is>
       </c>
       <c r="I205" s="9" t="inlineStr"/>
@@ -12771,7 +12783,7 @@
     <row r="206">
       <c r="A206" s="9" t="inlineStr">
         <is>
-          <t>LD61</t>
+          <t>LD60</t>
         </is>
       </c>
       <c r="B206" s="9" t="inlineStr">
@@ -12781,12 +12793,12 @@
       </c>
       <c r="C206" s="9" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="D206" s="9" t="inlineStr">
         <is>
-          <t>Road transport: inputs from the rest of the model (v3.5)</t>
+          <t>Road transport: policy inputs (v3.5)</t>
         </is>
       </c>
       <c r="E206" s="10" t="inlineStr">
@@ -12796,17 +12808,17 @@
       </c>
       <c r="F206" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Section 5 road after-tax prices x GJ per liter (gas $/GJ / gas liters per GJ); industrial gas: section 2 price + road new policies; power prices of section 3 G (last year); GDP growth of row 7 (last year); population and real GDP after the feedback; carbon price x road feebate coverage; 2-3 wheelers: the gasoline price incl. new policies (legacy row 4438: before new policies); VAT on vehicles: VAT_WEO of the customs year (Egypt 0.14; legacy 0.1531)</t>
+          <t>Departs from legacy: Policies: MTInputs rows 418-479 after the template (scenario-specific, legacy Dashboard defaults, all off); parameters and hardcoded literals (Gompertz constant, gas liters per GJ, PHEV kWh per liter, insurance factor, BEV distance caps, price elasticities): sheets TransportParams, TransportPaths and named constants</t>
         </is>
       </c>
       <c r="G206" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Legacy rows of the price, power and macro blocks</t>
+          <t>Legacy: Dashboard rows 61-98 and 540-559 (outside MTInputs)</t>
         </is>
       </c>
       <c r="H206" s="9" t="inlineStr">
         <is>
-          <t>Small: 2-3 wheeler fuel use under carbon pricing; vehicle prices after VAT</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I206" s="9" t="inlineStr"/>
@@ -12821,7 +12833,7 @@
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>LD62</t>
+          <t>LD61</t>
         </is>
       </c>
       <c r="B207" s="9" t="inlineStr">
@@ -12831,12 +12843,12 @@
       </c>
       <c r="C207" s="9" t="inlineStr">
         <is>
-          <t>Not yet</t>
+          <t>Assumption</t>
         </is>
       </c>
       <c r="D207" s="9" t="inlineStr">
         <is>
-          <t>Road transport: biofuels (v3.5)</t>
+          <t>Road transport: inputs from the rest of the model (v3.5)</t>
         </is>
       </c>
       <c r="E207" s="10" t="inlineStr">
@@ -12846,17 +12858,17 @@
       </c>
       <c r="F207" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Engineer road model as legacy (v4.12): bioethanol and other biofuels follow road gasoline, biodiesel follows diesel (base year x use / base-year use; Balances or EnergyCons); the feebate CO2 per liter of gasoline and diesel x their fossil share (E2146:E2147). Elasticity road model (the default): road biofuels on their own row with the biomass elasticities; legacy ties bioethanol and biodiesel to gasoline and diesel there too (rows 5404-5405) and gives other biofuels an oil row with bugs (5406, survey D11): not yet built</t>
+          <t>Departs from legacy: Section 5 road after-tax prices x GJ per liter (gas $/GJ / gas liters per GJ); industrial gas: section 2 price + road new policies; power prices of section 3 G (last year); GDP growth of row 7 (last year); population and real GDP after the feedback; carbon price x road feebate coverage; 2-3 wheelers: the gasoline price incl. new policies (legacy row 4438: before new policies); VAT on vehicles: VAT_WEO of the customs year (Egypt 0.14; legacy 0.1531)</t>
         </is>
       </c>
       <c r="G207" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Biofuel shares within road gasoline and diesel (rows 5436-5438, EF adjustment E2146:E2147)</t>
+          <t>Legacy: Legacy rows of the price, power and macro blocks</t>
         </is>
       </c>
       <c r="H207" s="9" t="inlineStr">
         <is>
-          <t>None for Egypt (no road biofuels)</t>
+          <t>Small: 2-3 wheeler fuel use under carbon pricing; vehicle prices after VAT</t>
         </is>
       </c>
       <c r="I207" s="9" t="inlineStr"/>
@@ -12871,7 +12883,7 @@
     <row r="208">
       <c r="A208" s="9" t="inlineStr">
         <is>
-          <t>LD63</t>
+          <t>LD62</t>
         </is>
       </c>
       <c r="B208" s="9" t="inlineStr">
@@ -12886,7 +12898,7 @@
       </c>
       <c r="D208" s="9" t="inlineStr">
         <is>
-          <t>Road transport: range anxiety (v3.5)</t>
+          <t>Road transport: biofuels (v3.5)</t>
         </is>
       </c>
       <c r="E208" s="10" t="inlineStr">
@@ -12896,17 +12908,17 @@
       </c>
       <c r="F208" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Same stored values; fit (calculated - actual EV sales share, data years) reported in rows trraf</t>
+          <t>Departs from legacy: Engineer road model as legacy (v4.12): bioethanol and other biofuels follow road gasoline, biodiesel follows diesel (base year x use / base-year use; Balances or EnergyCons); the feebate CO2 per liter of gasoline and diesel x their fossil share (E2146:E2147). Elasticity road model (the default): road biofuels on their own row with the biomass elasticities; legacy ties bioethanol and biodiesel to gasoline and diesel there too (rows 5404-5405) and gives other biofuels an oil row with bugs (5406, survey D11): not yet built</t>
         </is>
       </c>
       <c r="G208" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Transport3: per-country solver results for the legacy model</t>
+          <t>Legacy: Biofuel shares within road gasoline and diesel (rows 5436-5438, EF adjustment E2146:E2147)</t>
         </is>
       </c>
       <c r="H208" s="9" t="inlineStr">
         <is>
-          <t>Egypt passenger EV sales share 2025: model 0.09%, actual 0.15%</t>
+          <t>None for Egypt (no road biofuels)</t>
         </is>
       </c>
       <c r="I208" s="9" t="inlineStr"/>
@@ -12921,7 +12933,7 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>LD67</t>
+          <t>LD63</t>
         </is>
       </c>
       <c r="B209" s="9" t="inlineStr">
@@ -12936,7 +12948,7 @@
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>Exemption phase-out of uncovered fuels and sectors</t>
+          <t>Road transport: range anxiety (v3.5)</t>
         </is>
       </c>
       <c r="E209" s="10" t="inlineStr">
@@ -12946,17 +12958,17 @@
       </c>
       <c r="F209" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: v5.6: built. The phase-out of uncovered fuels and sectors (rows fc, sc: 1 if covered, else exph) and the initially exempt residential demand of the most-used cooking fuel (section 6b rows lkxp, lkxe, lkxr, lkx, lkxa through lkc; share ExemptCookShare on Settings C83 from HHSurvey; usage elasticity phased in; income factor as the row, L48 fixed)</t>
+          <t>Departs from legacy: Same stored values; fit (calculated - actual EV sales share, data years) reported in rows trraf</t>
         </is>
       </c>
       <c r="G209" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Rows 2259-2288: ExemptPhaseout, YearPha, ExemptPhaseoutPeriod (MTInputs rows 49-51) phase the tax in for fuels and sectors not covered; the initially exempt residential demand split (ExemptMostCook, rows 1784-1795, 5568-5570; L48, L92) is dead code in legacy</t>
+          <t>Legacy: Transport3: per-country solver results for the legacy model</t>
         </is>
       </c>
       <c r="H209" s="9" t="inlineStr">
         <is>
-          <t>None for Egypt (ExemptPhaseout = FALSE, ExemptMostCook = No)</t>
+          <t>Egypt passenger EV sales share 2025: model 0.09%, actual 0.15%</t>
         </is>
       </c>
       <c r="I209" s="9" t="inlineStr"/>
@@ -12971,7 +12983,7 @@
     <row r="210">
       <c r="A210" s="9" t="inlineStr">
         <is>
-          <t>LD69</t>
+          <t>LD67</t>
         </is>
       </c>
       <c r="B210" s="9" t="inlineStr">
@@ -12981,12 +12993,12 @@
       </c>
       <c r="C210" s="9" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Not yet</t>
         </is>
       </c>
       <c r="D210" s="9" t="inlineStr">
         <is>
-          <t>ETS goal-seek settings (v5.2)</t>
+          <t>Exemption phase-out of uncovered fuels and sectors</t>
         </is>
       </c>
       <c r="E210" s="10" t="inlineStr">
@@ -12996,17 +13008,17 @@
       </c>
       <c r="F210" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: The same cells and names, read by the macro SolveETS and ets_goalseek.py (before v5.2: constants in the code); values 20, Continue, 0.005, the prototype error being the worst yearly /covered / cap - 1/; StartFresh starts from the fast estimate ets.est, Continue from the override row if it holds prices</t>
+          <t>Departs from legacy: v5.6: built. The phase-out of uncovered fuels and sectors (rows fc, sc: 1 if covered, else exph) and the initially exempt residential demand of the most-used cooking fuel (section 6b rows lkxp, lkxe, lkxr, lkx, lkxa through lkc; share ExemptCookShare on Settings C83 from HHSurvey; usage elasticity phased in; income factor as the row, L48 fixed)</t>
         </is>
       </c>
       <c r="G210" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Manual inputs E10:E12 (names ETSMaxIterations 30, ETSStartFreshContinue 'Continue', ETSErrorTolerance 0.001), read by the VBA goal seek (SolveFast)</t>
+          <t>Legacy: Rows 2259-2288: ExemptPhaseout, YearPha, ExemptPhaseoutPeriod (MTInputs rows 49-51) phase the tax in for fuels and sectors not covered; the initially exempt residential demand split (ExemptMostCook, rows 1784-1795, 5568-5570; L48, L92) is dead code in legacy</t>
         </is>
       </c>
       <c r="H210" s="9" t="inlineStr">
         <is>
-          <t>None (values unchanged)</t>
+          <t>None for Egypt (ExemptPhaseout = FALSE, ExemptMostCook = No)</t>
         </is>
       </c>
       <c r="I210" s="9" t="inlineStr"/>
@@ -13021,7 +13033,7 @@
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>LD74</t>
+          <t>LD69</t>
         </is>
       </c>
       <c r="B211" s="9" t="inlineStr">
@@ -13036,7 +13048,7 @@
       </c>
       <c r="D211" s="9" t="inlineStr">
         <is>
-          <t>Power: inputs by scenario (v5.4, P2)</t>
+          <t>ETS goal-seek settings (v5.2)</t>
         </is>
       </c>
       <c r="E211" s="10" t="inlineStr">
@@ -13046,17 +13058,17 @@
       </c>
       <c r="F211" s="9" t="inlineStr">
         <is>
-          <t>Departs from legacy: Every MTInputs power input (rows 242, 262, 342-415, 482) read in the scenario's own column (section-1 rows; section 3 sub-table A0 applies them to the power data); scenario 1 is the baseline of every scenario, so a technical input changed in a policy scenario changes that scenario only</t>
+          <t>Departs from legacy: The same cells and names, read by the macro SolveETS and ets_goalseek.py (before v5.2: constants in the code); values 20, Continue, 0.005, the prototype error being the worst yearly /covered / cap - 1/; StartFresh starts from the fast estimate ets.est, Continue from the override row if it holds prices</t>
         </is>
       </c>
       <c r="G211" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Each MTInputs column runs with its own baseline and policy run, so every power input can differ by scenario</t>
+          <t>Legacy: Manual inputs E10:E12 (names ETSMaxIterations 30, ETSStartFreshContinue 'Continue', ETSErrorTolerance 0.001), read by the VBA goal seek (SolveFast)</t>
         </is>
       </c>
       <c r="H211" s="9" t="inlineStr">
         <is>
-          <t>None for the shipped scenarios (defaults)</t>
+          <t>None (values unchanged)</t>
         </is>
       </c>
       <c r="I211" s="9" t="inlineStr"/>
@@ -13071,42 +13083,42 @@
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
-          <t>LD64</t>
+          <t>LD74</t>
         </is>
       </c>
       <c r="B212" s="9" t="inlineStr">
         <is>
-          <t>LegacyDiff, kept as legacy</t>
+          <t>LegacyDiff departure</t>
         </is>
       </c>
       <c r="C212" s="9" t="inlineStr">
         <is>
-          <t>To check (bucket 5)</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="D212" s="9" t="inlineStr">
         <is>
-          <t>Road transport: kept as legacy (v3.5)</t>
-        </is>
-      </c>
-      <c r="E212" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Power: inputs by scenario (v5.4, P2)</t>
+        </is>
+      </c>
+      <c r="E212" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="F212" s="9" t="inlineStr">
         <is>
-          <t>Kept as legacy: Kept (freight distance, data years: parameters) or not built (externalities)</t>
+          <t>Departs from legacy: Every MTInputs power input (rows 242, 262, 342-415, 482) read in the scenario's own column (section-1 rows; section 3 sub-table A0 applies them to the power data); scenario 1 is the baseline of every scenario, so a technical input changed in a policy scenario changes that scenario only</t>
         </is>
       </c>
       <c r="G212" s="9" t="inlineStr">
         <is>
-          <t>Legacy: Freight distance (survey B14), data years of customs, VAT and import shares, the externality sheet Transport</t>
+          <t>Legacy: Each MTInputs column runs with its own baseline and policy run, so every power input can differ by scenario</t>
         </is>
       </c>
       <c r="H212" s="9" t="inlineStr">
         <is>
-          <t>None by default</t>
+          <t>None for the shipped scenarios (defaults)</t>
         </is>
       </c>
       <c r="I212" s="9" t="inlineStr"/>
@@ -13121,61 +13133,57 @@
     <row r="213">
       <c r="A213" s="9" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>LD64</t>
         </is>
       </c>
       <c r="B213" s="9" t="inlineStr">
         <is>
-          <t>Issue of the prototype</t>
+          <t>LegacyDiff, kept as legacy</t>
         </is>
       </c>
       <c r="C213" s="9" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>To check (bucket 5)</t>
         </is>
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>Not yet run in Excel</t>
-        </is>
-      </c>
-      <c r="E213" s="12" t="inlineStr">
-        <is>
-          <t>n/a (no legacy counterpart)</t>
+          <t>Road transport: kept as legacy (v3.5)</t>
+        </is>
+      </c>
+      <c r="E213" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F213" s="9" t="inlineStr">
         <is>
-          <t>Limitation of the workbook and its tooling</t>
+          <t>Kept as legacy: Kept (freight distance, data years: parameters) or not built (externalities)</t>
         </is>
       </c>
       <c r="G213" s="9" t="inlineStr">
         <is>
-          <t>The workbook and its VBA project were generated and tested without Excel (LibreOffice). Open it, enable macros and run CheckBatchRun once; if Excel rejects the VBA project, import CPATScenarios.bas.</t>
-        </is>
-      </c>
-      <c r="H213" s="9" t="inlineStr"/>
-      <c r="I213" s="9" t="inlineStr">
-        <is>
-          <t>Review in Excel 365 (TODO).</t>
-        </is>
-      </c>
+          <t>Legacy: Freight distance (survey B14), data years of customs, VAT and import shares, the externality sheet Transport</t>
+        </is>
+      </c>
+      <c r="H213" s="9" t="inlineStr">
+        <is>
+          <t>None by default</t>
+        </is>
+      </c>
+      <c r="I213" s="9" t="inlineStr"/>
       <c r="J213" s="9" t="inlineStr">
         <is>
-          <t>TODO; Methods, chapter Macro and results</t>
-        </is>
-      </c>
-      <c r="K213" s="9" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+          <t>Sheet LegacyDiff</t>
+        </is>
+      </c>
+      <c r="K213" s="9" t="inlineStr"/>
       <c r="L213" s="9" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="9" t="inlineStr">
         <is>
-          <t>I2</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="B214" s="9" t="inlineStr">
@@ -13185,12 +13193,12 @@
       </c>
       <c r="C214" s="9" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D214" s="9" t="inlineStr">
         <is>
-          <t>Excel versions</t>
+          <t>Not yet run in Excel</t>
         </is>
       </c>
       <c r="E214" s="12" t="inlineStr">
@@ -13205,19 +13213,23 @@
       </c>
       <c r="G214" s="9" t="inlineStr">
         <is>
-          <t>2022-2040 need Excel 2019 or later (MINIFS, AGGREGATE); the last year 2041 is the LAMBDA year and needs Excel 365.</t>
+          <t>The workbook and its VBA project were generated and tested without Excel (LibreOffice). Open it, enable macros and run CheckBatchRun once; if Excel rejects the VBA project, import CPATScenarios.bas.</t>
         </is>
       </c>
       <c r="H214" s="9" t="inlineStr"/>
-      <c r="I214" s="9" t="inlineStr"/>
+      <c r="I214" s="9" t="inlineStr">
+        <is>
+          <t>Review in Excel 365 (TODO).</t>
+        </is>
+      </c>
       <c r="J214" s="9" t="inlineStr">
         <is>
-          <t>README; NORMS (LAMBDA year)</t>
+          <t>TODO; Methods, chapter Macro and results</t>
         </is>
       </c>
       <c r="K214" s="9" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L214" s="9" t="inlineStr"/>
@@ -13225,7 +13237,7 @@
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>I3</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="B215" s="9" t="inlineStr">
@@ -13240,7 +13252,7 @@
       </c>
       <c r="D215" s="9" t="inlineStr">
         <is>
-          <t>New sector / fuel pairs need a label</t>
+          <t>Excel versions</t>
         </is>
       </c>
       <c r="E215" s="12" t="inlineStr">
@@ -13255,14 +13267,14 @@
       </c>
       <c r="G215" s="9" t="inlineStr">
         <is>
-          <t>A new pair on Mitigation needs a row in the member-label table on Mapping, or its description shows #N/A (20 spare rows in the defined name).</t>
+          <t>2022-2040 need Excel 2019 or later (MINIFS, AGGREGATE); the last year 2041 is the LAMBDA year and needs Excel 365.</t>
         </is>
       </c>
       <c r="H215" s="9" t="inlineStr"/>
       <c r="I215" s="9" t="inlineStr"/>
       <c r="J215" s="9" t="inlineStr">
         <is>
-          <t>CAVEATS v1.08</t>
+          <t>README; NORMS (LAMBDA year)</t>
         </is>
       </c>
       <c r="K215" s="9" t="inlineStr">
@@ -13275,7 +13287,7 @@
     <row r="216">
       <c r="A216" s="9" t="inlineStr">
         <is>
-          <t>I5</t>
+          <t>I3</t>
         </is>
       </c>
       <c r="B216" s="9" t="inlineStr">
@@ -13290,7 +13302,7 @@
       </c>
       <c r="D216" s="9" t="inlineStr">
         <is>
-          <t>Totals include power since v1.09</t>
+          <t>New sector / fuel pairs need a label</t>
         </is>
       </c>
       <c r="E216" s="12" t="inlineStr">
@@ -13305,14 +13317,14 @@
       </c>
       <c r="G216" s="9" t="inlineStr">
         <is>
-          <t>Fuel use and revenue totals of v1.09 and later include power and are not comparable with v1.08 and earlier outputs.</t>
+          <t>A new pair on Mitigation needs a row in the member-label table on Mapping, or its description shows #N/A (20 spare rows in the defined name).</t>
         </is>
       </c>
       <c r="H216" s="9" t="inlineStr"/>
       <c r="I216" s="9" t="inlineStr"/>
       <c r="J216" s="9" t="inlineStr">
         <is>
-          <t>CAVEATS v1.09</t>
+          <t>CAVEATS v1.08</t>
         </is>
       </c>
       <c r="K216" s="9" t="inlineStr">
@@ -13325,7 +13337,7 @@
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>I9</t>
+          <t>I5</t>
         </is>
       </c>
       <c r="B217" s="9" t="inlineStr">
@@ -13340,7 +13352,7 @@
       </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
-          <t>The LAMBDA year 2041 needs LAMBDA support</t>
+          <t>Totals include power since v1.09</t>
         </is>
       </c>
       <c r="E217" s="12" t="inlineStr">
@@ -13355,14 +13367,14 @@
       </c>
       <c r="G217" s="9" t="inlineStr">
         <is>
-          <t>Every calculated cell of 2041 calls its named LAMBDA. Without LAMBDA support (Excel before 365, LibreOffice) 2041 shows errors, and so does its column in MTOutputs.</t>
+          <t>Fuel use and revenue totals of v1.09 and later include power and are not comparable with v1.08 and earlier outputs.</t>
         </is>
       </c>
       <c r="H217" s="9" t="inlineStr"/>
       <c r="I217" s="9" t="inlineStr"/>
       <c r="J217" s="9" t="inlineStr">
         <is>
-          <t>ReadMe (LAMBDAs, year 2041); NORMS</t>
+          <t>CAVEATS v1.09</t>
         </is>
       </c>
       <c r="K217" s="9" t="inlineStr">
@@ -13375,7 +13387,7 @@
     <row r="218">
       <c r="A218" s="9" t="inlineStr">
         <is>
-          <t>I10</t>
+          <t>I9</t>
         </is>
       </c>
       <c r="B218" s="9" t="inlineStr">
@@ -13390,7 +13402,7 @@
       </c>
       <c r="D218" s="9" t="inlineStr">
         <is>
-          <t>Without LAMBDA support the power model looks ahead without 2041</t>
+          <t>The LAMBDA year 2041 needs LAMBDA support</t>
         </is>
       </c>
       <c r="E218" s="12" t="inlineStr">
@@ -13405,14 +13417,14 @@
       </c>
       <c r="G218" s="9" t="inlineStr">
         <is>
-          <t>The levelised variable cost (D9) uses last year's cost for 2041 (tvcx), and the moving average of fuel prices for power leaves 2041 out of 2039-2040. Power results 2022-2040 then differ slightly from Excel 365 (the check reports the size); stored results are the Excel 365 values.</t>
+          <t>Every calculated cell of 2041 calls its named LAMBDA. Without LAMBDA support (Excel before 365, LibreOffice) 2041 shows errors, and so does its column in MTOutputs.</t>
         </is>
       </c>
       <c r="H218" s="9" t="inlineStr"/>
       <c r="I218" s="9" t="inlineStr"/>
       <c r="J218" s="9" t="inlineStr">
         <is>
-          <t>check report section 1; Methods, chapter Power</t>
+          <t>ReadMe (LAMBDAs, year 2041); NORMS</t>
         </is>
       </c>
       <c r="K218" s="9" t="inlineStr">
@@ -13425,7 +13437,7 @@
     <row r="219">
       <c r="A219" s="9" t="inlineStr">
         <is>
-          <t>I11</t>
+          <t>I10</t>
         </is>
       </c>
       <c r="B219" s="9" t="inlineStr">
@@ -13440,7 +13452,7 @@
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>Changing the last historical price year</t>
+          <t>Without LAMBDA support the power model looks ahead without 2041</t>
         </is>
       </c>
       <c r="E219" s="12" t="inlineStr">
@@ -13455,14 +13467,14 @@
       </c>
       <c r="G219" s="9" t="inlineStr">
         <is>
-          <t>Prices have separate history and projection blocks; changing Settings C10 needs the blocks re-dragged (or the LAMBDA of the row, sheet Lambdas, copied left over the row).</t>
+          <t>The levelised variable cost (D9) uses last year's cost for 2041 (tvcx), and the moving average of fuel prices for power leaves 2041 out of 2039-2040. Power results 2022-2040 then differ slightly from Excel 365 (the check reports the size); stored results are the Excel 365 values.</t>
         </is>
       </c>
       <c r="H219" s="9" t="inlineStr"/>
       <c r="I219" s="9" t="inlineStr"/>
       <c r="J219" s="9" t="inlineStr">
         <is>
-          <t>README</t>
+          <t>check report section 1; Methods, chapter Power</t>
         </is>
       </c>
       <c r="K219" s="9" t="inlineStr">
@@ -13475,7 +13487,7 @@
     <row r="220">
       <c r="A220" s="9" t="inlineStr">
         <is>
-          <t>I12</t>
+          <t>I11</t>
         </is>
       </c>
       <c r="B220" s="9" t="inlineStr">
@@ -13490,7 +13502,7 @@
       </c>
       <c r="D220" s="9" t="inlineStr">
         <is>
-          <t>Values after 2030</t>
+          <t>Changing the last historical price year</t>
         </is>
       </c>
       <c r="E220" s="12" t="inlineStr">
@@ -13505,14 +13517,14 @@
       </c>
       <c r="G220" s="9" t="inlineStr">
         <is>
-          <t>Not a legacy target; the legacy CPI is held flat after 2031.</t>
+          <t>Prices have separate history and projection blocks; changing Settings C10 needs the blocks re-dragged (or the LAMBDA of the row, sheet Lambdas, copied left over the row).</t>
         </is>
       </c>
       <c r="H220" s="9" t="inlineStr"/>
       <c r="I220" s="9" t="inlineStr"/>
       <c r="J220" s="9" t="inlineStr">
         <is>
-          <t>LegacyDiff</t>
+          <t>README</t>
         </is>
       </c>
       <c r="K220" s="9" t="inlineStr">
@@ -13525,7 +13537,7 @@
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>I13</t>
+          <t>I12</t>
         </is>
       </c>
       <c r="B221" s="9" t="inlineStr">
@@ -13535,12 +13547,12 @@
       </c>
       <c r="C221" s="9" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>Data for other countries: proprietary tables are Egypt only</t>
+          <t>Values after 2030</t>
         </is>
       </c>
       <c r="E221" s="12" t="inlineStr">
@@ -13555,23 +13567,19 @@
       </c>
       <c r="G221" s="9" t="inlineStr">
         <is>
-          <t>The model is country-generic (Settings C4) and every public table holds all countries, but the legacy proprietary tables (Balances, EnergyCons, EF_PM, IO_GTAP, HHSurvey, ASPIRE, WHOCooking) of the NoPropData file hold Egypt only. Next: paste the full tables (full legacy file or the CPAT data pipeline), rebuild BaselineCO2 for scenario 1, test a second country end to end (was a TODO item; user 2026-10-19).</t>
+          <t>Not a legacy target; the legacy CPI is held flat after 2031.</t>
         </is>
       </c>
       <c r="H221" s="9" t="inlineStr"/>
-      <c r="I221" s="9" t="inlineStr">
-        <is>
-          <t>Data for other countries (TODO).</t>
-        </is>
-      </c>
+      <c r="I221" s="9" t="inlineStr"/>
       <c r="J221" s="9" t="inlineStr">
         <is>
-          <t>README</t>
+          <t>LegacyDiff</t>
         </is>
       </c>
       <c r="K221" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="L221" s="9" t="inlineStr"/>
@@ -13579,7 +13587,7 @@
     <row r="222">
       <c r="A222" s="9" t="inlineStr">
         <is>
-          <t>I15</t>
+          <t>I13</t>
         </is>
       </c>
       <c r="B222" s="9" t="inlineStr">
@@ -13589,12 +13597,12 @@
       </c>
       <c r="C222" s="9" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D222" s="9" t="inlineStr">
         <is>
-          <t>Subsidy rows changed sign in v2.4</t>
+          <t>Data for other countries: proprietary tables are Egypt only</t>
         </is>
       </c>
       <c r="E222" s="12" t="inlineStr">
@@ -13609,19 +13617,23 @@
       </c>
       <c r="G222" s="9" t="inlineStr">
         <is>
-          <t>esub, esubpu, rsub, prsub, sgap and rgap are negative from v2.4 (net existing revenue rnet = rtx + rsub, unchanged in value). Outputs stored with v2.3 or earlier have the opposite sign in these rows.</t>
+          <t>The model is country-generic (Settings C4) and every public table holds all countries, but the legacy proprietary tables (Balances, EnergyCons, EF_PM, IO_GTAP, HHSurvey, ASPIRE, WHOCooking) of the NoPropData file hold Egypt only. Next: paste the full tables (full legacy file or the CPAT data pipeline), rebuild BaselineCO2 for scenario 1, test a second country end to end (was a TODO item; user 2026-10-19).</t>
         </is>
       </c>
       <c r="H222" s="9" t="inlineStr"/>
-      <c r="I222" s="9" t="inlineStr"/>
+      <c r="I222" s="9" t="inlineStr">
+        <is>
+          <t>Data for other countries (TODO).</t>
+        </is>
+      </c>
       <c r="J222" s="9" t="inlineStr">
         <is>
-          <t>CAVEATS v2.4; NORMS</t>
+          <t>README</t>
         </is>
       </c>
       <c r="K222" s="9" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L222" s="9" t="inlineStr"/>
@@ -13629,7 +13641,7 @@
     <row r="223">
       <c r="A223" s="9" t="inlineStr">
         <is>
-          <t>I16</t>
+          <t>I15</t>
         </is>
       </c>
       <c r="B223" s="9" t="inlineStr">
@@ -13644,7 +13656,7 @@
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>A new block needs its label row</t>
+          <t>Subsidy rows changed sign in v2.4</t>
         </is>
       </c>
       <c r="E223" s="12" t="inlineStr">
@@ -13659,14 +13671,14 @@
       </c>
       <c r="G223" s="9" t="inlineStr">
         <is>
-          <t>Every block of rows on Mitigation has a label row above it (D:G parameter names from Variables G:J). Copy the label row with the block; a new variable needs its labels in Variables G:J.</t>
+          <t>esub, esubpu, rsub, prsub, sgap and rgap are negative from v2.4 (net existing revenue rnet = rtx + rsub, unchanged in value). Outputs stored with v2.3 or earlier have the opposite sign in these rows.</t>
         </is>
       </c>
       <c r="H223" s="9" t="inlineStr"/>
       <c r="I223" s="9" t="inlineStr"/>
       <c r="J223" s="9" t="inlineStr">
         <is>
-          <t>ReadMe (Layout and roll-up)</t>
+          <t>CAVEATS v2.4; NORMS</t>
         </is>
       </c>
       <c r="K223" s="9" t="inlineStr">
@@ -13679,7 +13691,7 @@
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
-          <t>I29</t>
+          <t>I16</t>
         </is>
       </c>
       <c r="B224" s="9" t="inlineStr">
@@ -13694,7 +13706,7 @@
       </c>
       <c r="D224" s="9" t="inlineStr">
         <is>
-          <t>Excel repair prompt (resolved v3.7)</t>
+          <t>A new block needs its label row</t>
         </is>
       </c>
       <c r="E224" s="12" t="inlineStr">
@@ -13709,23 +13721,19 @@
       </c>
       <c r="G224" s="9" t="inlineStr">
         <is>
-          <t>Excel 365 removed the cell formulas calling the LAMBDAs SCALE and SHARE (found by bisection with the repair log); renamed SCALEBY and SHAREOF in v3.7. The quick check opens the file in Excel where Excel is installed.</t>
+          <t>Every block of rows on Mitigation has a label row above it (D:G parameter names from Variables G:J). Copy the label row with the block; a new variable needs its labels in Variables G:J.</t>
         </is>
       </c>
       <c r="H224" s="9" t="inlineStr"/>
-      <c r="I224" s="9" t="inlineStr">
-        <is>
-          <t>v3.7: LAMBDAs renamed; confirm in Excel (quick check on Windows).</t>
-        </is>
-      </c>
+      <c r="I224" s="9" t="inlineStr"/>
       <c r="J224" s="9" t="inlineStr">
         <is>
-          <t>CAVEATS v3.6 (variants entry); check_quick.py</t>
+          <t>ReadMe (Layout and roll-up)</t>
         </is>
       </c>
       <c r="K224" s="9" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="L224" s="9" t="inlineStr"/>
@@ -13733,7 +13741,7 @@
     <row r="225">
       <c r="A225" s="9" t="inlineStr">
         <is>
-          <t>I30</t>
+          <t>I29</t>
         </is>
       </c>
       <c r="B225" s="9" t="inlineStr">
@@ -13748,7 +13756,7 @@
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>ETS goal seek short of the cap in definition 5</t>
+          <t>Excel repair prompt (resolved v3.7)</t>
         </is>
       </c>
       <c r="E225" s="12" t="inlineStr">
@@ -13763,23 +13771,23 @@
       </c>
       <c r="G225" s="9" t="inlineStr">
         <is>
-          <t>With all permits allocated free (benchmarks 1.0, the legacy default) the ETS works at half effectiveness, so definition 5 (cap -5% in 2027 to -20% in 2035) needs about 134 $/t in 2030 and 230 $/t in 2035. The goal seek then oscillates between years: after 20 iterations covered emissions are 3.7% above the cap (2033) or below it (2041); worst gap 6.2% in the stored results.</t>
+          <t>Excel 365 removed the cell formulas calling the LAMBDAs SCALE and SHARE (found by bisection with the repair log); renamed SCALEBY and SHAREOF in v3.7. The quick check opens the file in Excel where Excel is installed.</t>
         </is>
       </c>
       <c r="H225" s="9" t="inlineStr"/>
       <c r="I225" s="9" t="inlineStr">
         <is>
-          <t>Tested separately by the user (2026-10-19); no goal-seek runs in builds or checks (NORMS 5). Last full check (v5.3): worst gap 0.0265 after 20 iterations.</t>
+          <t>v3.7: LAMBDAs renamed; confirm in Excel (quick check on Windows).</t>
         </is>
       </c>
       <c r="J225" s="9" t="inlineStr">
         <is>
-          <t>ets_goalseek.py; CAVEATS v3.7</t>
+          <t>CAVEATS v3.6 (variants entry); check_quick.py</t>
         </is>
       </c>
       <c r="K225" s="9" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="L225" s="9" t="inlineStr"/>
@@ -13787,7 +13795,7 @@
     <row r="226">
       <c r="A226" s="9" t="inlineStr">
         <is>
-          <t>I33</t>
+          <t>I30</t>
         </is>
       </c>
       <c r="B226" s="9" t="inlineStr">
@@ -13802,7 +13810,7 @@
       </c>
       <c r="D226" s="9" t="inlineStr">
         <is>
-          <t>Data step overwrites the corrected Egypt prices</t>
+          <t>ETS goal seek short of the cap in definition 5</t>
         </is>
       </c>
       <c r="E226" s="12" t="inlineStr">
@@ -13817,23 +13825,23 @@
       </c>
       <c r="G226" s="9" t="inlineStr">
         <is>
-          <t>extract_data rewrites every data file from its sources; prices_dom.csv then loses the corrected Egypt block (update_prices_egypt must run after it), and the files come out with CRLF line ends. v3.11 kept only the jet-fuel rows of its run.</t>
+          <t>With all permits allocated free (benchmarks 1.0, the legacy default) the ETS works at half effectiveness, so definition 5 (cap -5% in 2027 to -20% in 2035) needs about 134 $/t in 2030 and 230 $/t in 2035. The goal seek then oscillates between years: after 20 iterations covered emissions are 3.7% above the cap (2033) or below it (2041); worst gap 6.2% in the stored results.</t>
         </is>
       </c>
       <c r="H226" s="9" t="inlineStr"/>
       <c r="I226" s="9" t="inlineStr">
         <is>
-          <t>v5.7: extract_data writes LF line ends and runs update_prices_egypt after the price extraction, so the corrected Egypt block is kept.</t>
+          <t>Tested separately by the user (2026-10-19); no goal-seek runs in builds or checks (NORMS 5). Last full check (v5.3): worst gap 0.0265 after 20 iterations.</t>
         </is>
       </c>
       <c r="J226" s="9" t="inlineStr">
         <is>
-          <t>CAVEATS v3.11</t>
+          <t>ets_goalseek.py; CAVEATS v3.7</t>
         </is>
       </c>
       <c r="K226" s="9" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L226" s="9" t="inlineStr"/>
@@ -13841,7 +13849,7 @@
     <row r="227">
       <c r="A227" s="9" t="inlineStr">
         <is>
-          <t>I73</t>
+          <t>I33</t>
         </is>
       </c>
       <c r="B227" s="9" t="inlineStr">
@@ -13851,12 +13859,12 @@
       </c>
       <c r="C227" s="9" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
-          <t>Scenario-1 lookups must end at the current column</t>
+          <t>Data step overwrites the corrected Egypt prices</t>
         </is>
       </c>
       <c r="E227" s="12" t="inlineStr">
@@ -13871,18 +13879,18 @@
       </c>
       <c r="G227" s="9" t="inlineStr">
         <is>
-          <t>Lookups of the scenario-1 value of the same year (INDEX over a row, MATCH on the year) must not range over later columns: in a recalculation that evaluates the range, a lookup over the whole row reads its own scenario's later years and closes a circular reference (the prototype had one such row, ener.ref, fixed in v6.2; all others end at the current column). Recommendation to the CPAT team: check the legacy lookups the same way.</t>
+          <t>extract_data rewrites every data file from its sources; prices_dom.csv then loses the corrected Egypt block (update_prices_egypt must run after it), and the files come out with CRLF line ends. v3.11 kept only the jet-fuel rows of its run.</t>
         </is>
       </c>
       <c r="H227" s="9" t="inlineStr"/>
       <c r="I227" s="9" t="inlineStr">
         <is>
-          <t>Legacy checked (v6.2 scan of every Mitigation formula for reads of later years): no scenario-1 lookup over whole rows (the policy block reads the baseline block in the same column); the cost breakdown (rows 3509-3517) reads the user's CostBreakdownYear, a report only; the net revenue report rows read the next year: legacy bug L128. prototype: every lookup ends at the current column (ener.ref fixed in v6.2); the quick check tests reads of later years.</t>
+          <t>v5.7: extract_data writes LF line ends and runs update_prices_egypt after the price extraction, so the corrected Egypt block is kept.</t>
         </is>
       </c>
       <c r="J227" s="9" t="inlineStr">
         <is>
-          <t>NORMS (circular references)</t>
+          <t>CAVEATS v3.11</t>
         </is>
       </c>
       <c r="K227" s="9" t="inlineStr">
@@ -13895,7 +13903,7 @@
     <row r="228">
       <c r="A228" s="9" t="inlineStr">
         <is>
-          <t>I74</t>
+          <t>I73</t>
         </is>
       </c>
       <c r="B228" s="9" t="inlineStr">
@@ -13910,7 +13918,7 @@
       </c>
       <c r="D228" s="9" t="inlineStr">
         <is>
-          <t>Methane calibration bases must be data or base-year values</t>
+          <t>Scenario-1 lookups must end at the current column</t>
         </is>
       </c>
       <c r="E228" s="12" t="inlineStr">
@@ -13925,18 +13933,18 @@
       </c>
       <c r="G228" s="9" t="inlineStr">
         <is>
-          <t>Source allocations and intensities of the methane fee must be calibrated on data or base-year activity, never on a later model year: legacy read GHGYear (2024) activity in the earlier years, a read of later years that becomes circular as soon as the fee revenue feeds the GDP effects. The prototype uses data activity since v6.0 and, for the fiscal space, the stored scenario-1 gas and biomass activity (I47). Recommendation to the CPAT team.</t>
+          <t>Lookups of the scenario-1 value of the same year (INDEX over a row, MATCH on the year) must not range over later columns: in a recalculation that evaluates the range, a lookup over the whole row reads its own scenario's later years and closes a circular reference (the prototype had one such row, ener.ref, fixed in v6.2; all others end at the current column). Recommendation to the CPAT team: check the legacy lookups the same way.</t>
         </is>
       </c>
       <c r="H228" s="9" t="inlineStr"/>
       <c r="I228" s="9" t="inlineStr">
         <is>
-          <t>Legacy checked: no bug. The source allocation uses energy-balance data (row 894) and the energy CH4 calibration (row 7548) uses the first two years and applies the factor from the third (it reads only earlier years). The prototype calibrated on GHGYear (2024) in every year (its own design) and now reads stored scenario-1 values; the fiscal space uses the stored scenario-1 activity (I47).</t>
+          <t>Legacy checked (v6.2 scan of every Mitigation formula for reads of later years): no scenario-1 lookup over whole rows (the policy block reads the baseline block in the same column); the cost breakdown (rows 3509-3517) reads the user's CostBreakdownYear, a report only; the net revenue report rows read the next year: legacy bug L128. prototype: every lookup ends at the current column (ener.ref fixed in v6.2); the quick check tests reads of later years.</t>
         </is>
       </c>
       <c r="J228" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Emissions</t>
+          <t>NORMS (circular references)</t>
         </is>
       </c>
       <c r="K228" s="9" t="inlineStr">
@@ -13949,65 +13957,61 @@
     <row r="229">
       <c r="A229" s="9" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>I74</t>
         </is>
       </c>
       <c r="B229" s="9" t="inlineStr">
         <is>
-          <t>Legacy bug (distribution)</t>
+          <t>Issue of the prototype</t>
         </is>
       </c>
       <c r="C229" s="9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
-          <t>Targeted transfer capped at 10 points, not the decile's population share</t>
-        </is>
-      </c>
-      <c r="E229" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Methane calibration bases must be data or base-year values</t>
+        </is>
+      </c>
+      <c r="E229" s="12" t="inlineStr">
+        <is>
+          <t>n/a (no legacy counterpart)</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Limitation of the workbook and its tooling</t>
         </is>
       </c>
       <c r="G229" s="9" t="inlineStr">
         <is>
-          <t>The targeted share of a decile is capped at 10 percentage points instead of its population share: 105.6% of decile 2 receives the transfer.</t>
+          <t>Source allocations and intensities of the methane fee must be calibrated on data or base-year activity, never on a later model year: legacy read GHGYear (2024) activity in the earlier years, a read of later years that becomes circular as soon as the fee revenue feeds the GDP effects. The prototype uses data activity since v6.0 and, for the fiscal space, the stored scenario-1 gas and biomass activity (I47). Recommendation to the CPAT team.</t>
         </is>
       </c>
       <c r="H229" s="9" t="inlineStr"/>
       <c r="I229" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v4.4): capped at the decile's population share.</t>
+          <t>Legacy checked: no bug. The source allocation uses energy-balance data (row 894) and the energy CH4 calibration (row 7548) uses the first two years and applies the factor from the third (it reads only earlier years). The prototype calibrated on GHGYear (2024) in every year (its own design) and now reads stored scenario-1 values; the fiscal space uses the stored scenario-1 activity (I47).</t>
         </is>
       </c>
       <c r="J229" s="9" t="inlineStr">
         <is>
-          <t>Distribution R2562:Z2562</t>
+          <t>Methods, chapter Emissions</t>
         </is>
       </c>
       <c r="K229" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="L229" s="9" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="L229" s="9" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="9" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B230" s="9" t="inlineStr">
@@ -14022,7 +14026,7 @@
       </c>
       <c r="D230" s="9" t="inlineStr">
         <is>
-          <t>Basket uses decile 1's elasticity adjustment and exemption test</t>
+          <t>Targeted transfer capped at 10 points, not the decile's population share</t>
         </is>
       </c>
       <c r="E230" s="10" t="inlineStr">
@@ -14037,18 +14041,18 @@
       </c>
       <c r="G230" s="9" t="inlineStr">
         <is>
-          <t>The all-household basket takes the elasticity adjustment and the exemption test of decile 1.</t>
+          <t>The targeted share of a decile is capped at 10 percentage points instead of its population share: 105.6% of decile 2 receives the transfer.</t>
         </is>
       </c>
       <c r="H230" s="9" t="inlineStr"/>
       <c r="I230" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v4.4): the basket elasticity, never exempt.</t>
+          <t>Fixed (v4.4): capped at the decile's population share.</t>
         </is>
       </c>
       <c r="J230" s="9" t="inlineStr">
         <is>
-          <t>Distribution C.V, C.VI (e.g. Q1607)</t>
+          <t>Distribution R2562:Z2562</t>
         </is>
       </c>
       <c r="K230" s="9" t="inlineStr">
@@ -14065,7 +14069,7 @@
     <row r="231">
       <c r="A231" s="9" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B231" s="9" t="inlineStr">
@@ -14080,7 +14084,7 @@
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
-          <t>Current spending tests the ASPIRE flag of the targeted transfer</t>
+          <t>Basket uses decile 1's elasticity adjustment and exemption test</t>
         </is>
       </c>
       <c r="E231" s="10" t="inlineStr">
@@ -14095,18 +14099,18 @@
       </c>
       <c r="G231" s="9" t="inlineStr">
         <is>
-          <t>Current spending reads the ASPIRE flag of the targeted transfer (I213) instead of its own (I214).</t>
+          <t>The all-household basket takes the elasticity adjustment and the exemption test of decile 1.</t>
         </is>
       </c>
       <c r="H231" s="9" t="inlineStr"/>
       <c r="I231" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v4.4): no flag; the ASPIRE programme of the chosen type, 0 if absent.</t>
+          <t>Fixed (v4.4): the basket elasticity, never exempt.</t>
         </is>
       </c>
       <c r="J231" s="9" t="inlineStr">
         <is>
-          <t>Distribution Q2633</t>
+          <t>Distribution C.V, C.VI (e.g. Q1607)</t>
         </is>
       </c>
       <c r="K231" s="9" t="inlineStr">
@@ -14123,7 +14127,7 @@
     <row r="232">
       <c r="A232" s="9" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B232" s="9" t="inlineStr">
@@ -14138,7 +14142,7 @@
       </c>
       <c r="D232" s="9" t="inlineStr">
         <is>
-          <t>Public investment and current spending vanish with the transfer settings</t>
+          <t>Current spending tests the ASPIRE flag of the targeted transfer</t>
         </is>
       </c>
       <c r="E232" s="10" t="inlineStr">
@@ -14153,18 +14157,18 @@
       </c>
       <c r="G232" s="9" t="inlineStr">
         <is>
-          <t>Public investment and current spending are 0 when the transfer coverage or percentile is 0.</t>
+          <t>Current spending reads the ASPIRE flag of the targeted transfer (I213) instead of its own (I214).</t>
         </is>
       </c>
       <c r="H232" s="9" t="inlineStr"/>
       <c r="I232" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v4.4): independent of the transfer settings.</t>
+          <t>Fixed (v4.4): no flag; the ASPIRE programme of the chosen type, 0 if absent.</t>
         </is>
       </c>
       <c r="J232" s="9" t="inlineStr">
         <is>
-          <t>Distribution rows 2701-2707</t>
+          <t>Distribution Q2633</t>
         </is>
       </c>
       <c r="K232" s="9" t="inlineStr">
@@ -14181,7 +14185,7 @@
     <row r="233">
       <c r="A233" s="9" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B233" s="9" t="inlineStr">
@@ -14196,7 +14200,7 @@
       </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
-          <t>Targeted exemption capped by all revenue; urban and rural not per capita</t>
+          <t>Public investment and current spending vanish with the transfer settings</t>
         </is>
       </c>
       <c r="E233" s="10" t="inlineStr">
@@ -14211,18 +14215,18 @@
       </c>
       <c r="G233" s="9" t="inlineStr">
         <is>
-          <t>The targeted exemption is capped by all carbon-pricing revenue (I154) instead of the PIT share (I163); urban and rural values are not per capita.</t>
+          <t>Public investment and current spending are 0 when the transfer coverage or percentile is 0.</t>
         </is>
       </c>
       <c r="H233" s="9" t="inlineStr"/>
       <c r="I233" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v4.4): capped by the PIT revenue; per capita in every sample.</t>
+          <t>Fixed (v4.4): independent of the transfer settings.</t>
         </is>
       </c>
       <c r="J233" s="9" t="inlineStr">
         <is>
-          <t>Distribution Q2749</t>
+          <t>Distribution rows 2701-2707</t>
         </is>
       </c>
       <c r="K233" s="9" t="inlineStr">
@@ -14239,7 +14243,7 @@
     <row r="234">
       <c r="A234" s="9" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B234" s="9" t="inlineStr">
@@ -14254,7 +14258,7 @@
       </c>
       <c r="D234" s="9" t="inlineStr">
         <is>
-          <t>Urban and rural compensation shares on overall weights</t>
+          <t>Targeted exemption capped by all revenue; urban and rural not per capita</t>
         </is>
       </c>
       <c r="E234" s="10" t="inlineStr">
@@ -14269,18 +14273,18 @@
       </c>
       <c r="G234" s="9" t="inlineStr">
         <is>
-          <t>The urban and rural compensation shares divide by overall consumption weights (they sum to 52 and 47).</t>
+          <t>The targeted exemption is capped by all carbon-pricing revenue (I154) instead of the PIT share (I163); urban and rural values are not per capita.</t>
         </is>
       </c>
       <c r="H234" s="9" t="inlineStr"/>
       <c r="I234" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v4.4): each sample's own weights, each summing to 100.</t>
+          <t>Fixed (v4.4): capped by the PIT revenue; per capita in every sample.</t>
         </is>
       </c>
       <c r="J234" s="9" t="inlineStr">
         <is>
-          <t>Distribution Q3259, Q3263</t>
+          <t>Distribution Q2749</t>
         </is>
       </c>
       <c r="K234" s="9" t="inlineStr">
@@ -14297,7 +14301,7 @@
     <row r="235">
       <c r="A235" s="9" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B235" s="9" t="inlineStr">
@@ -14312,7 +14316,7 @@
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
-          <t>Deadweight loss in mixed units</t>
+          <t>Urban and rural compensation shares on overall weights</t>
         </is>
       </c>
       <c r="E235" s="10" t="inlineStr">
@@ -14327,18 +14331,18 @@
       </c>
       <c r="G235" s="9" t="inlineStr">
         <is>
-          <t>The deadweight loss is a price fraction subtracted from a % of consumption.</t>
+          <t>The urban and rural compensation shares divide by overall consumption weights (they sum to 52 and 47).</t>
         </is>
       </c>
       <c r="H235" s="9" t="inlineStr"/>
       <c r="I235" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v4.4): DWLTri x (1 - factor) x the effect, in the same units.</t>
+          <t>Fixed (v4.4): each sample's own weights, each summing to 100.</t>
         </is>
       </c>
       <c r="J235" s="9" t="inlineStr">
         <is>
-          <t>Distribution rows 859-883</t>
+          <t>Distribution Q3259, Q3263</t>
         </is>
       </c>
       <c r="K235" s="9" t="inlineStr">
@@ -14355,7 +14359,7 @@
     <row r="236">
       <c r="A236" s="9" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="B236" s="9" t="inlineStr">
@@ -14370,7 +14374,7 @@
       </c>
       <c r="D236" s="9" t="inlineStr">
         <is>
-          <t>Analysis year and statistic read MTInputs column D</t>
+          <t>Deadweight loss in mixed units</t>
         </is>
       </c>
       <c r="E236" s="10" t="inlineStr">
@@ -14385,18 +14389,18 @@
       </c>
       <c r="G236" s="9" t="inlineStr">
         <is>
-          <t>dist.year and dist.stat read MTInputs column D, which is 0 in dashboard mode.</t>
+          <t>The deadweight loss is a price fraction subtracted from a % of consumption.</t>
         </is>
       </c>
       <c r="H236" s="9" t="inlineStr"/>
       <c r="I236" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v4.4): the analysis year and statistic of the scenario group.</t>
+          <t>Fixed (v4.4): DWLTri x (1 - factor) x the effect, in the same units.</t>
         </is>
       </c>
       <c r="J236" s="9" t="inlineStr">
         <is>
-          <t>MTOutputs rows 1001-1002</t>
+          <t>Distribution rows 859-883</t>
         </is>
       </c>
       <c r="K236" s="9" t="inlineStr">
@@ -14413,7 +14417,7 @@
     <row r="237">
       <c r="A237" s="9" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="B237" s="9" t="inlineStr">
@@ -14428,7 +14432,7 @@
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>Rural rows labelled Urban; fuel code oil vs oop</t>
+          <t>Analysis year and statistic read MTInputs column D</t>
         </is>
       </c>
       <c r="E237" s="10" t="inlineStr">
@@ -14443,18 +14447,18 @@
       </c>
       <c r="G237" s="9" t="inlineStr">
         <is>
-          <t>Post-CP consumption rows of the rural sample carry the urban label; the elasticity and price rows of other oil products use different codes and are paired by row position only.</t>
+          <t>dist.year and dist.stat read MTInputs column D, which is 0 in dashboard mode.</t>
         </is>
       </c>
       <c r="H237" s="9" t="inlineStr"/>
       <c r="I237" s="9" t="inlineStr">
         <is>
-          <t>Fixed in the prototype (v5.1 register; own labels, rural and urban rows by key; one code oop paired by code).</t>
+          <t>Fixed (v4.4): the analysis year and statistic of the scenario group.</t>
         </is>
       </c>
       <c r="J237" s="9" t="inlineStr">
         <is>
-          <t>Distribution H2417, H2422 (456 numbering; DeepDive cites 2416, 2421): '... - Urban Sample' on rows computed from the rural rows 2402, 2407, 2412; C.II row 746 code 'oil' against price rows 774 and 804 'oop'</t>
+          <t>MTOutputs rows 1001-1002</t>
         </is>
       </c>
       <c r="K237" s="9" t="inlineStr">
@@ -14471,7 +14475,7 @@
     <row r="238">
       <c r="A238" s="9" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="B238" s="9" t="inlineStr">
@@ -14486,7 +14490,7 @@
       </c>
       <c r="D238" s="9" t="inlineStr">
         <is>
-          <t>ASPIRE transfer pays out more than the revenue</t>
+          <t>Rural rows labelled Urban; fuel code oil vs oop</t>
         </is>
       </c>
       <c r="E238" s="10" t="inlineStr">
@@ -14501,18 +14505,18 @@
       </c>
       <c r="G238" s="9" t="inlineStr">
         <is>
-          <t>Per capita = scale x benefit x [decile targeted], with the scale computed over actual receivers: partly targeted deciles get the full benefit, leakage deciles none; 125-129% of the funds are paid out for Egypt.</t>
+          <t>Post-CP consumption rows of the rural sample carry the urban label; the elasticity and price rows of other oil products use different codes and are paired by row position only.</t>
         </is>
       </c>
       <c r="H238" s="9" t="inlineStr"/>
       <c r="I238" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): transfer = revenue x benefit x share receiving / sum over deciles (payout = revenue).</t>
+          <t>Fixed in the prototype (v5.1 register; own labels, rural and urban rows by key; one code oop paired by code).</t>
         </is>
       </c>
       <c r="J238" s="9" t="inlineStr">
         <is>
-          <t>Distribution row 2629 (-&gt; 2697-2699)</t>
+          <t>Distribution H2417, H2422 (456 numbering; DeepDive cites 2416, 2421): '... - Urban Sample' on rows computed from the rural rows 2402, 2407, 2412; C.II row 746 code 'oil' against price rows 774 and 804 'oop'</t>
         </is>
       </c>
       <c r="K238" s="9" t="inlineStr">
@@ -14529,7 +14533,7 @@
     <row r="239">
       <c r="A239" s="9" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="B239" s="9" t="inlineStr">
@@ -14544,7 +14548,7 @@
       </c>
       <c r="D239" s="9" t="inlineStr">
         <is>
-          <t>ASPIRE program without country data: the transfer vanishes</t>
+          <t>ASPIRE transfer pays out more than the revenue</t>
         </is>
       </c>
       <c r="E239" s="10" t="inlineStr">
@@ -14559,18 +14563,18 @@
       </c>
       <c r="G239" s="9" t="inlineStr">
         <is>
-          <t>A program with no data gives a zero scale, so the transfer share of revenue silently disappears (no IFERROR).</t>
+          <t>Per capita = scale x benefit x [decile targeted], with the scale computed over actual receivers: partly targeted deciles get the full benefit, leakage deciles none; 125-129% of the funds are paid out for Egypt.</t>
         </is>
       </c>
       <c r="H239" s="9" t="inlineStr"/>
       <c r="I239" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): cash used and the settings check says so.</t>
+          <t>Fixed (v6.0): transfer = revenue x benefit x share receiving / sum over deciles (payout = revenue).</t>
         </is>
       </c>
       <c r="J239" s="9" t="inlineStr">
         <is>
-          <t>Distribution row 2617, I213</t>
+          <t>Distribution row 2629 (-&gt; 2697-2699)</t>
         </is>
       </c>
       <c r="K239" s="9" t="inlineStr">
@@ -14587,7 +14591,7 @@
     <row r="240">
       <c r="A240" s="9" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B240" s="9" t="inlineStr">
@@ -14602,7 +14606,7 @@
       </c>
       <c r="D240" s="9" t="inlineStr">
         <is>
-          <t>ASPIRE branch skips the median flag and the zero-coverage test</t>
+          <t>ASPIRE program without country data: the transfer vanishes</t>
         </is>
       </c>
       <c r="E240" s="10" t="inlineStr">
@@ -14617,18 +14621,18 @@
       </c>
       <c r="G240" s="9" t="inlineStr">
         <is>
-          <t>Parenthesisation: the ASPIRE branch is outside the flag and the coverage/percentile test.</t>
+          <t>A program with no data gives a zero scale, so the transfer share of revenue silently disappears (no IFERROR).</t>
         </is>
       </c>
       <c r="H240" s="9" t="inlineStr"/>
       <c r="I240" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): one formula for every targeting mode.</t>
+          <t>Fixed (v6.0): cash used and the settings check says so.</t>
         </is>
       </c>
       <c r="J240" s="9" t="inlineStr">
         <is>
-          <t>Distribution row 2697</t>
+          <t>Distribution row 2617, I213</t>
         </is>
       </c>
       <c r="K240" s="9" t="inlineStr">
@@ -14645,7 +14649,7 @@
     <row r="241">
       <c r="A241" s="9" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="B241" s="9" t="inlineStr">
@@ -14660,7 +14664,7 @@
       </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
-          <t>Public investment and current spending use the targeted-transfer median flag</t>
+          <t>ASPIRE branch skips the median flag and the zero-coverage test</t>
         </is>
       </c>
       <c r="E241" s="10" t="inlineStr">
@@ -14675,18 +14679,18 @@
       </c>
       <c r="G241" s="9" t="inlineStr">
         <is>
-          <t>Under the median statistic, public investment for deciles 5-10 is zeroed by the transfer flag.</t>
+          <t>Parenthesisation: the ASPIRE branch is outside the flag and the coverage/percentile test.</t>
         </is>
       </c>
       <c r="H241" s="9" t="inlineStr"/>
       <c r="I241" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): the flag applies to the targeted transfer only.</t>
+          <t>Fixed (v6.0): one formula for every targeting mode.</t>
         </is>
       </c>
       <c r="J241" s="9" t="inlineStr">
         <is>
-          <t>Distribution rows 2701-2707</t>
+          <t>Distribution row 2697</t>
         </is>
       </c>
       <c r="K241" s="9" t="inlineStr">
@@ -14703,7 +14707,7 @@
     <row r="242">
       <c r="A242" s="9" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="B242" s="9" t="inlineStr">
@@ -14718,7 +14722,7 @@
       </c>
       <c r="D242" s="9" t="inlineStr">
         <is>
-          <t>Poverty targeting: share receiving ignores targeting, coverage and leakage</t>
+          <t>Public investment and current spending use the targeted-transfer median flag</t>
         </is>
       </c>
       <c r="E242" s="10" t="inlineStr">
@@ -14733,18 +14737,18 @@
       </c>
       <c r="G242" s="9" t="inlineStr">
         <is>
-          <t>The share receiving is the share below the line, while the amounts use receivers x poor.</t>
+          <t>Under the median statistic, public investment for deciles 5-10 is zeroed by the transfer flag.</t>
         </is>
       </c>
       <c r="H242" s="9" t="inlineStr"/>
       <c r="I242" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): share receiving = receiving x below the line.</t>
+          <t>Fixed (v6.0): the flag applies to the targeted transfer only.</t>
         </is>
       </c>
       <c r="J242" s="9" t="inlineStr">
         <is>
-          <t>Distribution row 2679</t>
+          <t>Distribution rows 2701-2707</t>
         </is>
       </c>
       <c r="K242" s="9" t="inlineStr">
@@ -14761,7 +14765,7 @@
     <row r="243">
       <c r="A243" s="9" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="B243" s="9" t="inlineStr">
@@ -14776,7 +14780,7 @@
       </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
-          <t>Poverty targeting: urban and rural pay out about half of the funds</t>
+          <t>Poverty targeting: share receiving ignores targeting, coverage and leakage</t>
         </is>
       </c>
       <c r="E243" s="10" t="inlineStr">
@@ -14791,18 +14795,18 @@
       </c>
       <c r="G243" s="9" t="inlineStr">
         <is>
-          <t>Sample poverty shares x the overall receiving share x the overall amount: urban plus rural recipients are about 52% of the overall ones.</t>
+          <t>The share receiving is the share below the line, while the amounts use receivers x poor.</t>
         </is>
       </c>
       <c r="H243" s="9" t="inlineStr"/>
       <c r="I243" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): urban and rural per capita = the overall per capita (issue DI4).</t>
+          <t>Fixed (v6.0): share receiving = receiving x below the line.</t>
         </is>
       </c>
       <c r="J243" s="9" t="inlineStr">
         <is>
-          <t>Distribution rows 2650-2674</t>
+          <t>Distribution row 2679</t>
         </is>
       </c>
       <c r="K243" s="9" t="inlineStr">
@@ -14819,7 +14823,7 @@
     <row r="244">
       <c r="A244" s="9" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="B244" s="9" t="inlineStr">
@@ -14834,7 +14838,7 @@
       </c>
       <c r="D244" s="9" t="inlineStr">
         <is>
-          <t>Poverty share x 10 assumes deciles of 10%</t>
+          <t>Poverty targeting: urban and rural pay out about half of the funds</t>
         </is>
       </c>
       <c r="E244" s="10" t="inlineStr">
@@ -14849,18 +14853,18 @@
       </c>
       <c r="G244" s="9" t="inlineStr">
         <is>
-          <t>Decile 2 gives 111% (capped at 100 by MIN).</t>
+          <t>Sample poverty shares x the overall receiving share x the overall amount: urban plus rural recipients are about 52% of the overall ones.</t>
         </is>
       </c>
       <c r="H244" s="9" t="inlineStr"/>
       <c r="I244" s="9" t="inlineStr">
         <is>
-          <t>Kept with the cap (data limitation; noted).</t>
+          <t>Fixed (v6.0): urban and rural per capita = the overall per capita (issue DI4).</t>
         </is>
       </c>
       <c r="J244" s="9" t="inlineStr">
         <is>
-          <t>Distribution row 2649</t>
+          <t>Distribution rows 2650-2674</t>
         </is>
       </c>
       <c r="K244" s="9" t="inlineStr">
@@ -14877,7 +14881,7 @@
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
         <is>
-          <t>D17</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="B245" s="9" t="inlineStr">
@@ -14892,7 +14896,7 @@
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
-          <t>ASPIRE values converted without a PPP factor</t>
+          <t>Poverty share x 10 assumes deciles of 10%</t>
         </is>
       </c>
       <c r="E245" s="10" t="inlineStr">
@@ -14907,18 +14911,18 @@
       </c>
       <c r="G245" s="9" t="inlineStr">
         <is>
-          <t>PPP $ per day become "real LCU" by a deflator ratio only; the data year is unused. Displays only (the scale cancels).</t>
+          <t>Decile 2 gives 111% (capped at 100 by MIN).</t>
         </is>
       </c>
       <c r="H245" s="9" t="inlineStr"/>
       <c r="I245" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): rows labelled PPP $ per day; no conversion.</t>
+          <t>Kept with the cap (data limitation; noted).</t>
         </is>
       </c>
       <c r="J245" s="9" t="inlineStr">
         <is>
-          <t>Distribution row 2618, I220-I223</t>
+          <t>Distribution row 2649</t>
         </is>
       </c>
       <c r="K245" s="9" t="inlineStr">
@@ -14935,7 +14939,7 @@
     <row r="246">
       <c r="A246" s="9" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D17</t>
         </is>
       </c>
       <c r="B246" s="9" t="inlineStr">
@@ -14950,7 +14954,7 @@
       </c>
       <c r="D246" s="9" t="inlineStr">
         <is>
-          <t>Horizontal p25/p75 effects inflated</t>
+          <t>ASPIRE values converted without a PPP factor</t>
         </is>
       </c>
       <c r="E246" s="10" t="inlineStr">
@@ -14965,18 +14969,18 @@
       </c>
       <c r="G246" s="9" t="inlineStr">
         <is>
-          <t>Effect x (1 + effect / other effect): Egypt decile 1 p75 -3.09 becomes -6.77.</t>
+          <t>PPP $ per day become "real LCU" by a deflator ratio only; the data year is unused. Displays only (the scale cancels).</t>
         </is>
       </c>
       <c r="H246" s="9" t="inlineStr"/>
       <c r="I246" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): effect = price factors x the budget shares of the percentile x loss scale.</t>
+          <t>Fixed (v6.0): rows labelled PPP $ per day; no conversion.</t>
         </is>
       </c>
       <c r="J246" s="9" t="inlineStr">
         <is>
-          <t>Distribution rows 3188-3206</t>
+          <t>Distribution row 2618, I220-I223</t>
         </is>
       </c>
       <c r="K246" s="9" t="inlineStr">
@@ -14993,7 +14997,7 @@
     <row r="247">
       <c r="A247" s="9" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="B247" s="9" t="inlineStr">
@@ -15008,7 +15012,7 @@
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>Horizontal "chosen statistic" recycling divides by median consumption</t>
+          <t>Horizontal p25/p75 effects inflated</t>
         </is>
       </c>
       <c r="E247" s="10" t="inlineStr">
@@ -15023,18 +15027,18 @@
       </c>
       <c r="G247" s="9" t="inlineStr">
         <is>
-          <t>Hard-coded .median.</t>
+          <t>Effect x (1 + effect / other effect): Egypt decile 1 p75 -3.09 becomes -6.77.</t>
         </is>
       </c>
       <c r="H247" s="9" t="inlineStr"/>
       <c r="I247" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): the recycling row of the chosen statistic.</t>
+          <t>Fixed (v6.0): effect = price factors x the budget shares of the percentile x loss scale.</t>
         </is>
       </c>
       <c r="J247" s="9" t="inlineStr">
         <is>
-          <t>Distribution rows 3193, 3201, 3209</t>
+          <t>Distribution rows 3188-3206</t>
         </is>
       </c>
       <c r="K247" s="9" t="inlineStr">
@@ -15051,7 +15055,7 @@
     <row r="248">
       <c r="A248" s="9" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="B248" s="9" t="inlineStr">
@@ -15066,7 +15070,7 @@
       </c>
       <c r="D248" s="9" t="inlineStr">
         <is>
-          <t>Decile brackets always divided by 1000</t>
+          <t>Horizontal "chosen statistic" recycling divides by median consumption</t>
         </is>
       </c>
       <c r="E248" s="10" t="inlineStr">
@@ -15081,18 +15085,18 @@
       </c>
       <c r="G248" s="9" t="inlineStr">
         <is>
-          <t>Relative reference instead of $G$2771.</t>
+          <t>Hard-coded .median.</t>
         </is>
       </c>
       <c r="H248" s="9" t="inlineStr"/>
       <c r="I248" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): no scaling; brackets in local currency.</t>
+          <t>Fixed (v6.0): the recycling row of the chosen statistic.</t>
         </is>
       </c>
       <c r="J248" s="9" t="inlineStr">
         <is>
-          <t>Distribution row 2774</t>
+          <t>Distribution rows 3193, 3201, 3209</t>
         </is>
       </c>
       <c r="K248" s="9" t="inlineStr">
@@ -15109,7 +15113,7 @@
     <row r="249">
       <c r="A249" s="9" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="B249" s="9" t="inlineStr">
@@ -15124,7 +15128,7 @@
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>Decile bracket labels unusable</t>
+          <t>Decile brackets always divided by 1000</t>
         </is>
       </c>
       <c r="E249" s="10" t="inlineStr">
@@ -15139,18 +15143,18 @@
       </c>
       <c r="G249" s="9" t="inlineStr">
         <is>
-          <t>Appends "0" when not in thousands; one significant digit gives "10k-10k"; survey-year values.</t>
+          <t>Relative reference instead of $G$2771.</t>
         </is>
       </c>
       <c r="H249" s="9" t="inlineStr"/>
       <c r="I249" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): real local currency of the analysis year (survey value x consumption adjustment), full numbers.</t>
+          <t>Fixed (v6.0): no scaling; brackets in local currency.</t>
         </is>
       </c>
       <c r="J249" s="9" t="inlineStr">
         <is>
-          <t>Distribution rows 2775-2784</t>
+          <t>Distribution row 2774</t>
         </is>
       </c>
       <c r="K249" s="9" t="inlineStr">
@@ -15167,7 +15171,7 @@
     <row r="250">
       <c r="A250" s="9" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B250" s="9" t="inlineStr">
@@ -15182,7 +15186,7 @@
       </c>
       <c r="D250" s="9" t="inlineStr">
         <is>
-          <t>Sector table "ordered by demand" sorts each column independently</t>
+          <t>Decile bracket labels unusable</t>
         </is>
       </c>
       <c r="E250" s="10" t="inlineStr">
@@ -15197,18 +15201,18 @@
       </c>
       <c r="G250" s="9" t="inlineStr">
         <is>
-          <t>LARGE per column: output and exports do not belong to the sector named.</t>
+          <t>Appends "0" when not in thousands; one significant digit gives "10k-10k"; survey-year values.</t>
         </is>
       </c>
       <c r="H250" s="9" t="inlineStr"/>
       <c r="I250" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): one rank per sector; values read by rank.</t>
+          <t>Fixed (v6.0): real local currency of the analysis year (survey value x consumption adjustment), full numbers.</t>
         </is>
       </c>
       <c r="J250" s="9" t="inlineStr">
         <is>
-          <t>Distribution rows 3300-3310</t>
+          <t>Distribution rows 2775-2784</t>
         </is>
       </c>
       <c r="K250" s="9" t="inlineStr">
@@ -15225,7 +15229,7 @@
     <row r="251">
       <c r="A251" s="9" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B251" s="9" t="inlineStr">
@@ -15240,7 +15244,7 @@
       </c>
       <c r="D251" s="9" t="inlineStr">
         <is>
-          <t>Ordered sector tables show 11 of 12 sectors</t>
+          <t>Sector table "ordered by demand" sorts each column independently</t>
         </is>
       </c>
       <c r="E251" s="10" t="inlineStr">
@@ -15255,18 +15259,18 @@
       </c>
       <c r="G251" s="9" t="inlineStr">
         <is>
-          <t>11 rows for 12 sectors.</t>
+          <t>LARGE per column: output and exports do not belong to the sector named.</t>
         </is>
       </c>
       <c r="H251" s="9" t="inlineStr"/>
       <c r="I251" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): every sector listed.</t>
+          <t>Fixed (v6.0): one rank per sector; values read by rank.</t>
         </is>
       </c>
       <c r="J251" s="9" t="inlineStr">
         <is>
-          <t>Distribution rows 3300-3323</t>
+          <t>Distribution rows 3300-3310</t>
         </is>
       </c>
       <c r="K251" s="9" t="inlineStr">
@@ -15283,7 +15287,7 @@
     <row r="252">
       <c r="A252" s="9" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>D23</t>
         </is>
       </c>
       <c r="B252" s="9" t="inlineStr">
@@ -15298,7 +15302,7 @@
       </c>
       <c r="D252" s="9" t="inlineStr">
         <is>
-          <t>Chemicals and power missing from the CPAT-sector table</t>
+          <t>Ordered sector tables show 11 of 12 sectors</t>
         </is>
       </c>
       <c r="E252" s="10" t="inlineStr">
@@ -15313,18 +15317,18 @@
       </c>
       <c r="G252" s="9" t="inlineStr">
         <is>
-          <t>The most affected sector (chemicals) drops out of the CPAT-sector charts and shares.</t>
+          <t>11 rows for 12 sectors.</t>
         </is>
       </c>
       <c r="H252" s="9" t="inlineStr"/>
       <c r="I252" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): 14 sectors, chemicals and power included.</t>
+          <t>Fixed (v6.0): every sector listed.</t>
         </is>
       </c>
       <c r="J252" s="9" t="inlineStr">
         <is>
-          <t>Distribution rows 3285-3296</t>
+          <t>Distribution rows 3300-3323</t>
         </is>
       </c>
       <c r="K252" s="9" t="inlineStr">
@@ -15341,7 +15345,7 @@
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
         <is>
-          <t>D25</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="B253" s="9" t="inlineStr">
@@ -15356,7 +15360,7 @@
       </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
-          <t>Chart 19 labels ranked separately from their values; ties</t>
+          <t>Chemicals and power missing from the CPAT-sector table</t>
         </is>
       </c>
       <c r="E253" s="10" t="inlineStr">
@@ -15371,18 +15375,18 @@
       </c>
       <c r="G253" s="9" t="inlineStr">
         <is>
-          <t>Labels ranked by one column, values by another; MATCH on equal values returns the first sector twice.</t>
+          <t>The most affected sector (chemicals) drops out of the CPAT-sector charts and shares.</t>
         </is>
       </c>
       <c r="H253" s="9" t="inlineStr"/>
       <c r="I253" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): one ranking; ties broken by order.</t>
+          <t>Fixed (v6.0): 14 sectors, chemicals and power included.</t>
         </is>
       </c>
       <c r="J253" s="9" t="inlineStr">
         <is>
-          <t>Distribution row 3313</t>
+          <t>Distribution rows 3285-3296</t>
         </is>
       </c>
       <c r="K253" s="9" t="inlineStr">
@@ -15399,7 +15403,7 @@
     <row r="254">
       <c r="A254" s="9" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>D25</t>
         </is>
       </c>
       <c r="B254" s="9" t="inlineStr">
@@ -15414,7 +15418,7 @@
       </c>
       <c r="D254" s="9" t="inlineStr">
         <is>
-          <t>Pass-through coefficients one row off</t>
+          <t>Chart 19 labels ranked separately from their values; ties</t>
         </is>
       </c>
       <c r="E254" s="10" t="inlineStr">
@@ -15429,18 +15433,18 @@
       </c>
       <c r="G254" s="9" t="inlineStr">
         <is>
-          <t>Every sector gets the coefficient of the next row; power has none.</t>
+          <t>Labels ranked by one column, values by another; MATCH on equal values returns the first sector twice.</t>
         </is>
       </c>
       <c r="H254" s="9" t="inlineStr"/>
       <c r="I254" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): coefficient of the sector's own row; power 1.</t>
+          <t>Fixed (v6.0): one ranking; ties broken by order.</t>
         </is>
       </c>
       <c r="J254" s="9" t="inlineStr">
         <is>
-          <t>Distribution G659:BR659</t>
+          <t>Distribution row 3313</t>
         </is>
       </c>
       <c r="K254" s="9" t="inlineStr">
@@ -15457,7 +15461,7 @@
     <row r="255">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D26</t>
         </is>
       </c>
       <c r="B255" s="9" t="inlineStr">
@@ -15472,7 +15476,7 @@
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>MTOutputs outpriin labels do not match their values</t>
+          <t>Pass-through coefficients one row off</t>
         </is>
       </c>
       <c r="E255" s="10" t="inlineStr">
@@ -15487,18 +15491,18 @@
       </c>
       <c r="G255" s="9" t="inlineStr">
         <is>
-          <t>Fixed labels read the sorted rows (outpriin.avi = iron and steel's value).</t>
+          <t>Every sector gets the coefficient of the next row; power has none.</t>
         </is>
       </c>
       <c r="H255" s="9" t="inlineStr"/>
       <c r="I255" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): outpriin by sector code.</t>
+          <t>Fixed (v6.0): coefficient of the sector's own row; power 1.</t>
         </is>
       </c>
       <c r="J255" s="9" t="inlineStr">
         <is>
-          <t>MTOutputs K1048:L1058</t>
+          <t>Distribution G659:BR659</t>
         </is>
       </c>
       <c r="K255" s="9" t="inlineStr">
@@ -15515,7 +15519,7 @@
     <row r="256">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="B256" s="9" t="inlineStr">
@@ -15530,7 +15534,7 @@
       </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
-          <t>MTOutputs codes without a dot</t>
+          <t>MTOutputs outpriin labels do not match their values</t>
         </is>
       </c>
       <c r="E256" s="10" t="inlineStr">
@@ -15545,18 +15549,18 @@
       </c>
       <c r="G256" s="9" t="inlineStr">
         <is>
-          <t>egydistn.cts..., egydistn.rec...</t>
+          <t>Fixed labels read the sorted rows (outpriin.avi = iron and steel's value).</t>
         </is>
       </c>
       <c r="H256" s="9" t="inlineStr"/>
       <c r="I256" s="9" t="inlineStr">
         <is>
-          <t>Not replicated: the prototype writes the right codes.</t>
+          <t>Fixed (v6.0): outpriin by sector code.</t>
         </is>
       </c>
       <c r="J256" s="9" t="inlineStr">
         <is>
-          <t>MTOutputs E1006, E1013</t>
+          <t>MTOutputs K1048:L1058</t>
         </is>
       </c>
       <c r="K256" s="9" t="inlineStr">
@@ -15573,7 +15577,7 @@
     <row r="257">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="B257" s="9" t="inlineStr">
@@ -15588,7 +15592,7 @@
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>MTOutputs ppic.fuel empty</t>
+          <t>MTOutputs codes without a dot</t>
         </is>
       </c>
       <c r="E257" s="10" t="inlineStr">
@@ -15603,18 +15607,18 @@
       </c>
       <c r="G257" s="9" t="inlineStr">
         <is>
-          <t>Blank cell.</t>
+          <t>egydistn.cts..., egydistn.rec...</t>
         </is>
       </c>
       <c r="H257" s="9" t="inlineStr"/>
       <c r="I257" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): the fuel transformation sector is read (0).</t>
+          <t>Not replicated: the prototype writes the right codes.</t>
         </is>
       </c>
       <c r="J257" s="9" t="inlineStr">
         <is>
-          <t>MTOutputs K1046</t>
+          <t>MTOutputs E1006, E1013</t>
         </is>
       </c>
       <c r="K257" s="9" t="inlineStr">
@@ -15631,7 +15635,7 @@
     <row r="258">
       <c r="A258" s="9" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="B258" s="9" t="inlineStr">
@@ -15646,7 +15650,7 @@
       </c>
       <c r="D258" s="9" t="inlineStr">
         <is>
-          <t>Lorenz equality line in 10% steps</t>
+          <t>MTOutputs ppic.fuel empty</t>
         </is>
       </c>
       <c r="E258" s="10" t="inlineStr">
@@ -15661,18 +15665,18 @@
       </c>
       <c r="G258" s="9" t="inlineStr">
         <is>
-          <t>The x-axis is the actual cumulative population share.</t>
+          <t>Blank cell.</t>
         </is>
       </c>
       <c r="H258" s="9" t="inlineStr"/>
       <c r="I258" s="9" t="inlineStr">
         <is>
-          <t>Fixed (v6.0): equality line = cumulative population share.</t>
+          <t>Fixed (v6.0): the fuel transformation sector is read (0).</t>
         </is>
       </c>
       <c r="J258" s="9" t="inlineStr">
         <is>
-          <t>Distribution rows 2455-2457, 3109</t>
+          <t>MTOutputs K1046</t>
         </is>
       </c>
       <c r="K258" s="9" t="inlineStr">
@@ -15689,7 +15693,7 @@
     <row r="259">
       <c r="A259" s="9" t="inlineStr">
         <is>
-          <t>D31</t>
+          <t>D30</t>
         </is>
       </c>
       <c r="B259" s="9" t="inlineStr">
@@ -15704,7 +15708,7 @@
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>Absolute overall rows carry wrong codes</t>
+          <t>Lorenz equality line in 10% steps</t>
         </is>
       </c>
       <c r="E259" s="10" t="inlineStr">
@@ -15719,18 +15723,18 @@
       </c>
       <c r="G259" s="9" t="inlineStr">
         <is>
-          <t>Codes bsh.ely.dec.rur... on overall rows (labels only).</t>
+          <t>The x-axis is the actual cumulative population share.</t>
         </is>
       </c>
       <c r="H259" s="9" t="inlineStr"/>
       <c r="I259" s="9" t="inlineStr">
         <is>
-          <t>Not replicated: the prototype builds codes from the row ids.</t>
+          <t>Fixed (v6.0): equality line = cumulative population share.</t>
         </is>
       </c>
       <c r="J259" s="9" t="inlineStr">
         <is>
-          <t>Distribution L3036:L3043</t>
+          <t>Distribution rows 2455-2457, 3109</t>
         </is>
       </c>
       <c r="K259" s="9" t="inlineStr">
@@ -15747,53 +15751,65 @@
     <row r="260">
       <c r="A260" s="9" t="inlineStr">
         <is>
-          <t>DI1</t>
+          <t>D31</t>
         </is>
       </c>
       <c r="B260" s="9" t="inlineStr">
         <is>
-          <t>Issue (distribution)</t>
-        </is>
-      </c>
-      <c r="C260" s="9" t="inlineStr"/>
+          <t>Legacy bug (distribution)</t>
+        </is>
+      </c>
+      <c r="C260" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="D260" s="9" t="inlineStr">
         <is>
-          <t>Spending in the base year</t>
-        </is>
-      </c>
-      <c r="E260" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Absolute overall rows carry wrong codes</t>
+        </is>
+      </c>
+      <c r="E260" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>Replicated</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G260" s="9" t="inlineStr">
         <is>
-          <t>Fuel spending is taken in the base year (legacy: the first calculation year), with the price changes of the analysis year.</t>
+          <t>Codes bsh.ely.dec.rur... on overall rows (labels only).</t>
         </is>
       </c>
       <c r="H260" s="9" t="inlineStr"/>
-      <c r="I260" s="9" t="inlineStr"/>
+      <c r="I260" s="9" t="inlineStr">
+        <is>
+          <t>Not replicated: the prototype builds codes from the row ids.</t>
+        </is>
+      </c>
       <c r="J260" s="9" t="inlineStr">
         <is>
-          <t>Methods, chapter Distribution</t>
+          <t>Distribution L3036:L3043</t>
         </is>
       </c>
       <c r="K260" s="9" t="inlineStr">
         <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="L260" s="9" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L260" s="9" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>DI2</t>
+          <t>DI1</t>
         </is>
       </c>
       <c r="B261" s="9" t="inlineStr">
@@ -15804,7 +15820,7 @@
       <c r="C261" s="9" t="inlineStr"/>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>GTAP values converted with the local GDP deflator</t>
+          <t>Spending in the base year</t>
         </is>
       </c>
       <c r="E261" s="11" t="inlineStr">
@@ -15819,7 +15835,7 @@
       </c>
       <c r="G261" s="9" t="inlineStr">
         <is>
-          <t>The GTAP input-output values are converted with the local GDP deflator (legacy I244).</t>
+          <t>Fuel spending is taken in the base year (legacy: the first calculation year), with the price changes of the analysis year.</t>
         </is>
       </c>
       <c r="H261" s="9" t="inlineStr"/>
@@ -15839,7 +15855,7 @@
     <row r="262">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>DI3</t>
+          <t>DI2</t>
         </is>
       </c>
       <c r="B262" s="9" t="inlineStr">
@@ -15850,7 +15866,7 @@
       <c r="C262" s="9" t="inlineStr"/>
       <c r="D262" s="9" t="inlineStr">
         <is>
-          <t>Elasticities always overall, mean</t>
+          <t>GTAP values converted with the local GDP deflator</t>
         </is>
       </c>
       <c r="E262" s="11" t="inlineStr">
@@ -15865,7 +15881,7 @@
       </c>
       <c r="G262" s="9" t="inlineStr">
         <is>
-          <t>The data have no other statistics or samples.</t>
+          <t>The GTAP input-output values are converted with the local GDP deflator (legacy I244).</t>
         </is>
       </c>
       <c r="H262" s="9" t="inlineStr"/>
@@ -15885,7 +15901,7 @@
     <row r="263">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>DI4</t>
+          <t>DI3</t>
         </is>
       </c>
       <c r="B263" s="9" t="inlineStr">
@@ -15896,7 +15912,7 @@
       <c r="C263" s="9" t="inlineStr"/>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>Recycled amounts per capita from the overall sample</t>
+          <t>Elasticities always overall, mean</t>
         </is>
       </c>
       <c r="E263" s="11" t="inlineStr">
@@ -15911,7 +15927,7 @@
       </c>
       <c r="G263" s="9" t="inlineStr">
         <is>
-          <t>Applied to urban and rural consumption alike.</t>
+          <t>The data have no other statistics or samples.</t>
         </is>
       </c>
       <c r="H263" s="9" t="inlineStr"/>
@@ -15931,7 +15947,7 @@
     <row r="264">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>DI5</t>
+          <t>DI4</t>
         </is>
       </c>
       <c r="B264" s="9" t="inlineStr">
@@ -15942,7 +15958,7 @@
       <c r="C264" s="9" t="inlineStr"/>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>Gini from a fitted Lorenz curve</t>
+          <t>Recycled amounts per capita from the overall sample</t>
         </is>
       </c>
       <c r="E264" s="11" t="inlineStr">
@@ -15957,7 +15973,7 @@
       </c>
       <c r="G264" s="9" t="inlineStr">
         <is>
-          <t>The Gini comes from the fitted curve, not the trapezoid rule.</t>
+          <t>Applied to urban and rural consumption alike.</t>
         </is>
       </c>
       <c r="H264" s="9" t="inlineStr"/>
@@ -15977,7 +15993,7 @@
     <row r="265">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>DI6</t>
+          <t>DI5</t>
         </is>
       </c>
       <c r="B265" s="9" t="inlineStr">
@@ -15988,7 +16004,7 @@
       <c r="C265" s="9" t="inlineStr"/>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>Carbon-pricing revenue stands for the revenue to recycle</t>
+          <t>Gini from a fitted Lorenz curve</t>
         </is>
       </c>
       <c r="E265" s="11" t="inlineStr">
@@ -16003,7 +16019,7 @@
       </c>
       <c r="G265" s="9" t="inlineStr">
         <is>
-          <t>Revenue from new policies (rnew: carbon tax, VAT on it, auctioned ETS) is the revenue recycled, as legacy's carbon-pricing revenue.</t>
+          <t>The Gini comes from the fitted curve, not the trapezoid rule.</t>
         </is>
       </c>
       <c r="H265" s="9" t="inlineStr"/>
@@ -16023,7 +16039,7 @@
     <row r="266">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>DI7</t>
+          <t>DI6</t>
         </is>
       </c>
       <c r="B266" s="9" t="inlineStr">
@@ -16034,7 +16050,7 @@
       <c r="C266" s="9" t="inlineStr"/>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>ASPIRE-targeted transfers (TransferType other than Cash)</t>
+          <t>Carbon-pricing revenue stands for the revenue to recycle</t>
         </is>
       </c>
       <c r="E266" s="11" t="inlineStr">
@@ -16044,12 +16060,12 @@
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>Replicated (v6.0)</t>
+          <t>Replicated</t>
         </is>
       </c>
       <c r="G266" s="9" t="inlineStr">
         <is>
-          <t>Modelled v6.0: the transfer follows the program's incidence by quintile (legacy rows 2617-2629; bugs D10-D12 fixed).</t>
+          <t>Revenue from new policies (rnew: carbon tax, VAT on it, auctioned ETS) is the revenue recycled, as legacy's carbon-pricing revenue.</t>
         </is>
       </c>
       <c r="H266" s="9" t="inlineStr"/>
@@ -16069,7 +16085,7 @@
     <row r="267">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>DI8</t>
+          <t>DI7</t>
         </is>
       </c>
       <c r="B267" s="9" t="inlineStr">
@@ -16080,7 +16096,7 @@
       <c r="C267" s="9" t="inlineStr"/>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>Poverty-line targeting (TargetBelow, with Cash only)</t>
+          <t>ASPIRE-targeted transfers (TransferType other than Cash)</t>
         </is>
       </c>
       <c r="E267" s="11" t="inlineStr">
@@ -16095,7 +16111,7 @@
       </c>
       <c r="G267" s="9" t="inlineStr">
         <is>
-          <t>Modelled v6.0: the transfer weights each decile by its share below the line (HHSurvey pct_belowpl_*, mean as legacy; bugs D14-D16).</t>
+          <t>Modelled v6.0: the transfer follows the program's incidence by quintile (legacy rows 2617-2629; bugs D10-D12 fixed).</t>
         </is>
       </c>
       <c r="H267" s="9" t="inlineStr"/>
@@ -16115,7 +16131,7 @@
     <row r="268">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>DI9</t>
+          <t>DI8</t>
         </is>
       </c>
       <c r="B268" s="9" t="inlineStr">
@@ -16126,7 +16142,7 @@
       <c r="C268" s="9" t="inlineStr"/>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>Pass-through switch wired into the production-sector prices only</t>
+          <t>Poverty-line targeting (TargetBelow, with Cash only)</t>
         </is>
       </c>
       <c r="E268" s="11" t="inlineStr">
@@ -16141,7 +16157,7 @@
       </c>
       <c r="G268" s="9" t="inlineStr">
         <is>
-          <t>PassthroughDist scales the sector price changes (legacy D.VI, bug D26 fixed), not the household effects, as legacy.</t>
+          <t>Modelled v6.0: the transfer weights each decile by its share below the line (HHSurvey pct_belowpl_*, mean as legacy; bugs D14-D16).</t>
         </is>
       </c>
       <c r="H268" s="9" t="inlineStr"/>
@@ -16161,7 +16177,7 @@
     <row r="269">
       <c r="A269" s="9" t="inlineStr">
         <is>
-          <t>DI10</t>
+          <t>DI9</t>
         </is>
       </c>
       <c r="B269" s="9" t="inlineStr">
@@ -16172,7 +16188,7 @@
       <c r="C269" s="9" t="inlineStr"/>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>Median statistic: the targeted transfer only reaches deciles where more than half receive</t>
+          <t>Pass-through switch wired into the production-sector prices only</t>
         </is>
       </c>
       <c r="E269" s="11" t="inlineStr">
@@ -16187,7 +16203,7 @@
       </c>
       <c r="G269" s="9" t="inlineStr">
         <is>
-          <t>Modelled v6.0 (legacy row 2685): the money not paid is not redistributed, as legacy.</t>
+          <t>PassthroughDist scales the sector price changes (legacy D.VI, bug D26 fixed), not the household effects, as legacy.</t>
         </is>
       </c>
       <c r="H269" s="9" t="inlineStr"/>
@@ -16207,49 +16223,45 @@
     <row r="270">
       <c r="A270" s="9" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>DI10</t>
         </is>
       </c>
       <c r="B270" s="9" t="inlineStr">
         <is>
-          <t>Prototype bug</t>
+          <t>Issue (distribution)</t>
         </is>
       </c>
       <c r="C270" s="9" t="inlineStr"/>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>Version-log rows rewritten with the current version</t>
-        </is>
-      </c>
-      <c r="E270" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>Median statistic: the targeted transfer only reaches deciles where more than half receive</t>
+        </is>
+      </c>
+      <c r="E270" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Replicated (v6.0)</t>
         </is>
       </c>
       <c r="G270" s="9" t="inlineStr">
         <is>
-          <t>The builders wrote earlier version-log rows with the current version number.</t>
+          <t>Modelled v6.0 (legacy row 2685): the money not paid is not redistributed, as legacy.</t>
         </is>
       </c>
       <c r="H270" s="9" t="inlineStr"/>
-      <c r="I270" s="9" t="inlineStr">
-        <is>
-          <t>Each row has its own version; old workbooks left as shipped.</t>
-        </is>
-      </c>
+      <c r="I270" s="9" t="inlineStr"/>
       <c r="J270" s="9" t="inlineStr">
         <is>
-          <t>prototype v0.3-v0.4 / v0.5</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K270" s="9" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L270" s="9" t="inlineStr"/>
@@ -16257,7 +16269,7 @@
     <row r="271">
       <c r="A271" s="9" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B271" s="9" t="inlineStr">
@@ -16268,7 +16280,7 @@
       <c r="C271" s="9" t="inlineStr"/>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>Power: VAT left out on the policy term</t>
+          <t>Version-log rows rewritten with the current version</t>
         </is>
       </c>
       <c r="E271" s="12" t="inlineStr">
@@ -16283,18 +16295,18 @@
       </c>
       <c r="G271" s="9" t="inlineStr">
         <is>
-          <t>The end-user price added the policy cost without VAT; legacy row 3614 charges VAT.</t>
+          <t>The builders wrote earlier version-log rows with the current version number.</t>
         </is>
       </c>
       <c r="H271" s="9" t="inlineStr"/>
       <c r="I271" s="9" t="inlineStr">
         <is>
-          <t>VAT on the policy term as legacy (no effect for Egypt, VAT 0).</t>
+          <t>Each row has its own version; old workbooks left as shipped.</t>
         </is>
       </c>
       <c r="J271" s="9" t="inlineStr">
         <is>
-          <t>prototype v1.05 / v1.06</t>
+          <t>prototype v0.3-v0.4 / v0.5</t>
         </is>
       </c>
       <c r="K271" s="9" t="inlineStr">
@@ -16307,7 +16319,7 @@
     <row r="272">
       <c r="A272" s="9" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B272" s="9" t="inlineStr">
@@ -16318,7 +16330,7 @@
       <c r="C272" s="9" t="inlineStr"/>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>Power: long-term storage allocation left out</t>
+          <t>Power: VAT left out on the policy term</t>
         </is>
       </c>
       <c r="E272" s="12" t="inlineStr">
@@ -16333,13 +16345,13 @@
       </c>
       <c r="G272" s="9" t="inlineStr">
         <is>
-          <t>The legacy note "incomplete" was read as "not applied".</t>
+          <t>The end-user price added the policy cost without VAT; legacy row 3614 charges VAT.</t>
         </is>
       </c>
       <c r="H272" s="9" t="inlineStr"/>
       <c r="I272" s="9" t="inlineStr">
         <is>
-          <t>The 33% allocation is applied once.</t>
+          <t>VAT on the policy term as legacy (no effect for Egypt, VAT 0).</t>
         </is>
       </c>
       <c r="J272" s="9" t="inlineStr">
@@ -16357,7 +16369,7 @@
     <row r="273">
       <c r="A273" s="9" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="B273" s="9" t="inlineStr">
@@ -16368,7 +16380,7 @@
       <c r="C273" s="9" t="inlineStr"/>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>Power: VRE share without other renewables</t>
+          <t>Power: long-term storage allocation left out</t>
         </is>
       </c>
       <c r="E273" s="12" t="inlineStr">
@@ -16383,13 +16395,13 @@
       </c>
       <c r="G273" s="9" t="inlineStr">
         <is>
-          <t>Legacy row 3851 also counts other renewables.</t>
+          <t>The legacy note "incomplete" was read as "not applied".</t>
         </is>
       </c>
       <c r="H273" s="9" t="inlineStr"/>
       <c r="I273" s="9" t="inlineStr">
         <is>
-          <t>Follows legacy (other renewables 0 for Egypt).</t>
+          <t>The 33% allocation is applied once.</t>
         </is>
       </c>
       <c r="J273" s="9" t="inlineStr">
@@ -16407,7 +16419,7 @@
     <row r="274">
       <c r="A274" s="9" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="B274" s="9" t="inlineStr">
@@ -16418,7 +16430,7 @@
       <c r="C274" s="9" t="inlineStr"/>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>Defined name clashed with a LAMBDA name</t>
+          <t>Power: VRE share without other renewables</t>
         </is>
       </c>
       <c r="E274" s="12" t="inlineStr">
@@ -16433,18 +16445,18 @@
       </c>
       <c r="G274" s="9" t="inlineStr">
         <is>
-          <t>The defined name ETSSemi equals the LAMBDA ETSSEMI ignoring case and gave #NAME?; the ETS goal seek stopped converging.</t>
+          <t>Legacy row 3851 also counts other renewables.</t>
         </is>
       </c>
       <c r="H274" s="9" t="inlineStr"/>
       <c r="I274" s="9" t="inlineStr">
         <is>
-          <t>Renamed SemiEl; the builder asserts that no defined name equals a LAMBDA name.</t>
+          <t>Follows legacy (other renewables 0 for Egypt).</t>
         </is>
       </c>
       <c r="J274" s="9" t="inlineStr">
         <is>
-          <t>prototype v1.07 build / v1.07</t>
+          <t>prototype v1.05 / v1.06</t>
         </is>
       </c>
       <c r="K274" s="9" t="inlineStr">
@@ -16457,7 +16469,7 @@
     <row r="275">
       <c r="A275" s="9" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="B275" s="9" t="inlineStr">
@@ -16468,7 +16480,7 @@
       <c r="C275" s="9" t="inlineStr"/>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>Power ETS revenue valued at the tax-equivalent price</t>
+          <t>Defined name clashed with a LAMBDA name</t>
         </is>
       </c>
       <c r="E275" s="12" t="inlineStr">
@@ -16483,18 +16495,18 @@
       </c>
       <c r="G275" s="9" t="inlineStr">
         <is>
-          <t>Power new-policy revenue (ccpav x consumption) valued the ETS at the tax-equivalent price, about 10% high at Medium volatility.</t>
+          <t>The defined name ETSSemi equals the LAMBDA ETSSEMI ignoring case and gave #NAME?; the ETS goal seek stopped converging.</t>
         </is>
       </c>
       <c r="H275" s="9" t="inlineStr"/>
       <c r="I275" s="9" t="inlineStr">
         <is>
-          <t>Revenue by generation type (prnew) with the ETS at the permit price; rcarb kept as a memo.</t>
+          <t>Renamed SemiEl; the builder asserts that no defined name equals a LAMBDA name.</t>
         </is>
       </c>
       <c r="J275" s="9" t="inlineStr">
         <is>
-          <t>prototype v1.05 / v1.09</t>
+          <t>prototype v1.07 build / v1.07</t>
         </is>
       </c>
       <c r="K275" s="9" t="inlineStr">
@@ -16507,7 +16519,7 @@
     <row r="276">
       <c r="A276" s="9" t="inlineStr">
         <is>
-          <t>M7</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="B276" s="9" t="inlineStr">
@@ -16518,7 +16530,7 @@
       <c r="C276" s="9" t="inlineStr"/>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>Stale texts in the workbook and notes</t>
+          <t>Power ETS revenue valued at the tax-equivalent price</t>
         </is>
       </c>
       <c r="E276" s="12" t="inlineStr">
@@ -16533,18 +16545,18 @@
       </c>
       <c r="G276" s="9" t="inlineStr">
         <is>
-          <t>Section 12 and 13 notes said power was not included; PowerPaths said interim data; data sheets named old extractors; method notes described earlier versions.</t>
+          <t>Power new-policy revenue (ccpav x consumption) valued the ETS at the tax-equivalent price, about 10% high at Medium volatility.</t>
         </is>
       </c>
       <c r="H276" s="9" t="inlineStr"/>
       <c r="I276" s="9" t="inlineStr">
         <is>
-          <t>Texts updated; the check now scans the workbook texts for stale statements and missing file references.</t>
+          <t>Revenue by generation type (prnew) with the ETS at the permit price; rcarb kept as a memo.</t>
         </is>
       </c>
       <c r="J276" s="9" t="inlineStr">
         <is>
-          <t>prototype v1.08 / v1.09</t>
+          <t>prototype v1.05 / v1.09</t>
         </is>
       </c>
       <c r="K276" s="9" t="inlineStr">
@@ -16557,7 +16569,7 @@
     <row r="277">
       <c r="A277" s="9" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="B277" s="9" t="inlineStr">
@@ -16568,7 +16580,7 @@
       <c r="C277" s="9" t="inlineStr"/>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>LegacyDiff rows out of date</t>
+          <t>Stale texts in the workbook and notes</t>
         </is>
       </c>
       <c r="E277" s="12" t="inlineStr">
@@ -16583,18 +16595,18 @@
       </c>
       <c r="G277" s="9" t="inlineStr">
         <is>
-          <t>Existing carbon pricing was still listed as "Not modelled"; the formula-structure row described the LAMBDA right column of v1.07.</t>
+          <t>Section 12 and 13 notes said power was not included; PowerPaths said interim data; data sheets named old extractors; method notes described earlier versions.</t>
         </is>
       </c>
       <c r="H277" s="9" t="inlineStr"/>
       <c r="I277" s="9" t="inlineStr">
         <is>
-          <t>Rows updated; the check scans for these phrases.</t>
+          <t>Texts updated; the check now scans the workbook texts for stale statements and missing file references.</t>
         </is>
       </c>
       <c r="J277" s="9" t="inlineStr">
         <is>
-          <t>prototype v1.09 / v2.2</t>
+          <t>prototype v1.08 / v1.09</t>
         </is>
       </c>
       <c r="K277" s="9" t="inlineStr">
@@ -16607,7 +16619,7 @@
     <row r="278">
       <c r="A278" s="9" t="inlineStr">
         <is>
-          <t>M9</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="B278" s="9" t="inlineStr">
@@ -16618,7 +16630,7 @@
       <c r="C278" s="9" t="inlineStr"/>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>Legacy comparison note from v1.01</t>
+          <t>LegacyDiff rows out of date</t>
         </is>
       </c>
       <c r="E278" s="12" t="inlineStr">
@@ -16633,18 +16645,18 @@
       </c>
       <c r="G278" s="9" t="inlineStr">
         <is>
-          <t>legacy_comparison described the v1.01 baseline and its script wrote a different file name.</t>
+          <t>Existing carbon pricing was still listed as "Not modelled"; the formula-structure row described the LAMBDA right column of v1.07.</t>
         </is>
       </c>
       <c r="H278" s="9" t="inlineStr"/>
       <c r="I278" s="9" t="inlineStr">
         <is>
-          <t>Re-run on v2.2 (legacy_comparison_v6_4.md).</t>
+          <t>Rows updated; the check scans for these phrases.</t>
         </is>
       </c>
       <c r="J278" s="9" t="inlineStr">
         <is>
-          <t>prototype v1.02-v1.09 / v2.2</t>
+          <t>prototype v1.09 / v2.2</t>
         </is>
       </c>
       <c r="K278" s="9" t="inlineStr">
@@ -16657,7 +16669,7 @@
     <row r="279">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>M9</t>
         </is>
       </c>
       <c r="B279" s="9" t="inlineStr">
@@ -16668,7 +16680,7 @@
       <c r="C279" s="9" t="inlineStr"/>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>Total rows labelled "All subsectors"</t>
+          <t>Legacy comparison note from v1.01</t>
         </is>
       </c>
       <c r="E279" s="12" t="inlineStr">
@@ -16683,18 +16695,18 @@
       </c>
       <c r="G279" s="9" t="inlineStr">
         <is>
-          <t>Since v1.09 the totals (fuel use, CO2, revenues) include power, but the label of the sector code all still said "All subsectors".</t>
+          <t>legacy_comparison described the v1.01 baseline and its script wrote a different file name.</t>
         </is>
       </c>
       <c r="H279" s="9" t="inlineStr"/>
       <c r="I279" s="9" t="inlineStr">
         <is>
-          <t>Label "All sectors".</t>
+          <t>Re-run on v2.2 (legacy_comparison_v6_4.md).</t>
         </is>
       </c>
       <c r="J279" s="9" t="inlineStr">
         <is>
-          <t>prototype v1.09 / v2.3</t>
+          <t>prototype v1.02-v1.09 / v2.2</t>
         </is>
       </c>
       <c r="K279" s="9" t="inlineStr">
@@ -16707,7 +16719,7 @@
     <row r="280">
       <c r="A280" s="9" t="inlineStr">
         <is>
-          <t>M11</t>
+          <t>M10</t>
         </is>
       </c>
       <c r="B280" s="9" t="inlineStr">
@@ -16718,7 +16730,7 @@
       <c r="C280" s="9" t="inlineStr"/>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Macros read 19 year columns</t>
+          <t>Total rows labelled "All subsectors"</t>
         </is>
       </c>
       <c r="E280" s="12" t="inlineStr">
@@ -16733,18 +16745,18 @@
       </c>
       <c r="G280" s="9" t="inlineStr">
         <is>
-          <t>The VBA module had the number of years (NYEARS = 19, 2022-2040) as a constant; with the horizon to 2041 the batch run and CheckBatchRun would have stored and compared one year too few (found by the check).</t>
+          <t>Since v1.09 the totals (fuel use, CO2, revenues) include power, but the label of the sector code all still said "All subsectors".</t>
         </is>
       </c>
       <c r="H280" s="9" t="inlineStr"/>
       <c r="I280" s="9" t="inlineStr">
         <is>
-          <t>NYEARS = 20; the builder now asserts that it equals the number of model years.</t>
+          <t>Label "All sectors".</t>
         </is>
       </c>
       <c r="J280" s="9" t="inlineStr">
         <is>
-          <t>prototype v2.3 build / v2.3</t>
+          <t>prototype v1.09 / v2.3</t>
         </is>
       </c>
       <c r="K280" s="9" t="inlineStr">
@@ -16757,7 +16769,7 @@
     <row r="281">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>M12</t>
+          <t>M11</t>
         </is>
       </c>
       <c r="B281" s="9" t="inlineStr">
@@ -16768,7 +16780,7 @@
       <c r="C281" s="9" t="inlineStr"/>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>Sheet Lambdas: formula texts named merged sheets</t>
+          <t>Macros read 19 year columns</t>
         </is>
       </c>
       <c r="E281" s="12" t="inlineStr">
@@ -16783,18 +16795,18 @@
       </c>
       <c r="G281" s="9" t="inlineStr">
         <is>
-          <t>The tab merge of v3.6 re-pointed every formula but not the formula texts of sheet Lambdas (column F), so the rows reading the power and price inputs named Inputs_power / Inputs_prices, which no longer exist; copied into Mitigation they gave #REF! (found by the full check, variant B).</t>
+          <t>The VBA module had the number of years (NYEARS = 19, 2022-2040) as a constant; with the horizon to 2041 the batch run and CheckBatchRun would have stored and compared one year too few (found by the check).</t>
         </is>
       </c>
       <c r="H281" s="9" t="inlineStr"/>
       <c r="I281" s="9" t="inlineStr">
         <is>
-          <t>merge_tabs re-points the texts too; the full check copies them over every row (variant B).</t>
+          <t>NYEARS = 20; the builder now asserts that it equals the number of model years.</t>
         </is>
       </c>
       <c r="J281" s="9" t="inlineStr">
         <is>
-          <t>prototype v3.6 / v3.13</t>
+          <t>prototype v2.3 build / v2.3</t>
         </is>
       </c>
       <c r="K281" s="9" t="inlineStr">
@@ -16807,7 +16819,7 @@
     <row r="282">
       <c r="A282" s="9" t="inlineStr">
         <is>
-          <t>M13</t>
+          <t>M12</t>
         </is>
       </c>
       <c r="B282" s="9" t="inlineStr">
@@ -16818,7 +16830,7 @@
       <c r="C282" s="9" t="inlineStr"/>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>Road vehicle feebate counted the carbon price twice</t>
+          <t>Sheet Lambdas: formula texts named merged sheets</t>
         </is>
       </c>
       <c r="E282" s="12" t="inlineStr">
@@ -16833,18 +16845,18 @@
       </c>
       <c r="G282" s="9" t="inlineStr">
         <is>
-          <t>The vehicle feebate rate of the engineer road model added the carbon price x road feebate share in every policy scenario, although the carbon tax is in the fuel price already (legacy adds the shadow carbon price, 0 under explicit pricing).</t>
+          <t>The tab merge of v3.6 re-pointed every formula but not the formula texts of sheet Lambdas (column F), so the rows reading the power and price inputs named Inputs_power / Inputs_prices, which no longer exist; copied into Mitigation they gave #REF! (found by the full check, variant B).</t>
         </is>
       </c>
       <c r="H282" s="9" t="inlineStr"/>
       <c r="I282" s="9" t="inlineStr">
         <is>
-          <t>The road regulation shadow price (reg.rod) replaces it; 0 under explicit pricing.</t>
+          <t>merge_tabs re-points the texts too; the full check copies them over every row (variant B).</t>
         </is>
       </c>
       <c r="J282" s="9" t="inlineStr">
         <is>
-          <t>prototype v3.5 / v4.16</t>
+          <t>prototype v3.6 / v3.13</t>
         </is>
       </c>
       <c r="K282" s="9" t="inlineStr">
@@ -16857,7 +16869,7 @@
     <row r="283">
       <c r="A283" s="9" t="inlineStr">
         <is>
-          <t>M14</t>
+          <t>M13</t>
         </is>
       </c>
       <c r="B283" s="9" t="inlineStr">
@@ -16868,7 +16880,7 @@
       <c r="C283" s="9" t="inlineStr"/>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>LAMBDA library texts named a merged-away sheet</t>
+          <t>Road vehicle feebate counted the carbon price twice</t>
         </is>
       </c>
       <c r="E283" s="12" t="inlineStr">
@@ -16883,29 +16895,79 @@
       </c>
       <c r="G283" s="9" t="inlineStr">
         <is>
-          <t>The 21 LAMBDA-library texts of the power pollutant rows (sheet Lambdas, column C) still named the sheet Inputs_power: the v3.13 fix (M12) re-pointed the texts only on sheets that stay in place, and Lambdas is an appended block since v4.2; pasted, they gave #NAME?.</t>
+          <t>The vehicle feebate rate of the engineer road model added the carbon price x road feebate share in every policy scenario, although the carbon tax is in the fuel price already (legacy adds the shadow carbon price, 0 under explicit pricing).</t>
         </is>
       </c>
       <c r="H283" s="9" t="inlineStr"/>
       <c r="I283" s="9" t="inlineStr">
         <is>
+          <t>The road regulation shadow price (reg.rod) replaces it; 0 under explicit pricing.</t>
+        </is>
+      </c>
+      <c r="J283" s="9" t="inlineStr">
+        <is>
+          <t>prototype v3.5 / v4.16</t>
+        </is>
+      </c>
+      <c r="K283" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="L283" s="9" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="9" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="B284" s="9" t="inlineStr">
+        <is>
+          <t>Prototype bug</t>
+        </is>
+      </c>
+      <c r="C284" s="9" t="inlineStr"/>
+      <c r="D284" s="9" t="inlineStr">
+        <is>
+          <t>LAMBDA library texts named a merged-away sheet</t>
+        </is>
+      </c>
+      <c r="E284" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F284" s="9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G284" s="9" t="inlineStr">
+        <is>
+          <t>The 21 LAMBDA-library texts of the power pollutant rows (sheet Lambdas, column C) still named the sheet Inputs_power: the v3.13 fix (M12) re-pointed the texts only on sheets that stay in place, and Lambdas is an appended block since v4.2; pasted, they gave #NAME?.</t>
+        </is>
+      </c>
+      <c r="H284" s="9" t="inlineStr"/>
+      <c r="I284" s="9" t="inlineStr">
+        <is>
           <t>merge_tabs re-points the Lambdas texts of an appended block too (host Mitigation); the full check lists any text naming a merged-away sheet.</t>
         </is>
       </c>
-      <c r="J283" s="9" t="inlineStr">
+      <c r="J284" s="9" t="inlineStr">
         <is>
           <t>prototype v4.2 / v5.3</t>
         </is>
       </c>
-      <c r="K283" s="9" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="L283" s="9" t="inlineStr"/>
+      <c r="K284" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="L284" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L283"/>
+  <autoFilter ref="A3:L284"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>